--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X304"/>
+  <dimension ref="A1:X367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14517,6 +14517,5148 @@
         </is>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F305" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G305" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H305" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I305" s="4" t="inlineStr">
+        <is>
+          <t>15/04/2028</t>
+        </is>
+      </c>
+      <c r="J305" s="4" t="inlineStr"/>
+      <c r="K305" s="4" t="inlineStr"/>
+      <c r="L305" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="M305" s="4" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="N305" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O305" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P305" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q305" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R305" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S305" s="4" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T305" s="4" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U305" s="4" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V305" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W305" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X305" s="4" t="n">
+        <v>1.184</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D306" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E306" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F306" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G306" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H306" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I306" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2028</t>
+        </is>
+      </c>
+      <c r="J306" s="6" t="inlineStr"/>
+      <c r="K306" s="6" t="inlineStr"/>
+      <c r="L306" s="6" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="M306" s="6" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="N306" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O306" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="P306" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q306" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R306" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S306" s="6" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T306" s="6" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U306" s="6" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V306" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W306" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X306" s="6" t="n">
+        <v>1.099</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F307" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G307" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H307" s="4" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I307" s="4" t="inlineStr">
+        <is>
+          <t>19/01/2028</t>
+        </is>
+      </c>
+      <c r="J307" s="4" t="inlineStr"/>
+      <c r="K307" s="4" t="inlineStr"/>
+      <c r="L307" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M307" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N307" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="O307" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="P307" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q307" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R307" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S307" s="4" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T307" s="4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U307" s="4" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V307" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W307" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X307" s="4" t="n">
+        <v>1.165</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D308" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E308" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F308" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G308" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H308" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I308" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J308" s="6" t="inlineStr"/>
+      <c r="K308" s="6" t="inlineStr"/>
+      <c r="L308" s="6" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="M308" s="6" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="N308" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="O308" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="P308" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R308" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S308" s="6" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T308" s="6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U308" s="6" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V308" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W308" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X308" s="6" t="n">
+        <v>1.082</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="F309" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G309" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H309" s="4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I309" s="4" t="inlineStr">
+        <is>
+          <t>18/09/2027</t>
+        </is>
+      </c>
+      <c r="J309" s="4" t="inlineStr"/>
+      <c r="K309" s="4" t="inlineStr"/>
+      <c r="L309" s="4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="M309" s="4" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="N309" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O309" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="P309" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q309" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R309" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S309" s="4" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T309" s="4" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U309" s="4" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V309" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W309" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X309" s="4" t="n">
+        <v>1.399</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D310" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E310" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F310" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G310" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H310" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="I310" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2027</t>
+        </is>
+      </c>
+      <c r="J310" s="6" t="inlineStr"/>
+      <c r="K310" s="6" t="inlineStr"/>
+      <c r="L310" s="6" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="M310" s="6" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="N310" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O310" s="6" t="n">
+        <v>346</v>
+      </c>
+      <c r="P310" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q310" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R310" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S310" s="6" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T310" s="6" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U310" s="6" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V310" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W310" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X310" s="6" t="n">
+        <v>1.236</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F311" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G311" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H311" s="4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="I311" s="4" t="inlineStr">
+        <is>
+          <t>13/03/2028</t>
+        </is>
+      </c>
+      <c r="J311" s="4" t="inlineStr"/>
+      <c r="K311" s="4" t="inlineStr"/>
+      <c r="L311" s="4" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="M311" s="4" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="N311" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O311" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="P311" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q311" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R311" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S311" s="4" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T311" s="4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U311" s="4" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V311" s="4" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W311" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X311" s="4" t="n">
+        <v>1.301</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D312" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E312" s="6" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F312" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G312" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H312" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I312" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J312" s="6" t="inlineStr"/>
+      <c r="K312" s="6" t="inlineStr"/>
+      <c r="L312" s="6" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="M312" s="6" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="N312" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O312" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="P312" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q312" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R312" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S312" s="6" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T312" s="6" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U312" s="6" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V312" s="6" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W312" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X312" s="6" t="n">
+        <v>1.085</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="n"/>
+      <c r="F313" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G313" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H313" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I313" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J313" s="4" t="inlineStr"/>
+      <c r="K313" s="4" t="inlineStr"/>
+      <c r="L313" s="4" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="M313" s="4" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="N313" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O313" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P313" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q313" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R313" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S313" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T313" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U313" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V313" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W313" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X313" s="4" t="n">
+        <v>0.821</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D314" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E314" s="6" t="n"/>
+      <c r="F314" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G314" s="6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H314" s="6" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="I314" s="6" t="n"/>
+      <c r="J314" s="6" t="inlineStr"/>
+      <c r="K314" s="6" t="inlineStr"/>
+      <c r="L314" s="6" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="M314" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="N314" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O314" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P314" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q314" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R314" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S314" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T314" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U314" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V314" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W314" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X314" s="6" t="n">
+        <v>0.761</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E315" s="4" t="n"/>
+      <c r="F315" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G315" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H315" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I315" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2027</t>
+        </is>
+      </c>
+      <c r="J315" s="4" t="inlineStr"/>
+      <c r="K315" s="4" t="inlineStr"/>
+      <c r="L315" s="4" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="M315" s="4" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="N315" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O315" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P315" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q315" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R315" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S315" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T315" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U315" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V315" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W315" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X315" s="4" t="n">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D316" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E316" s="6" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F316" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G316" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H316" s="6" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="I316" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J316" s="6" t="inlineStr"/>
+      <c r="K316" s="6" t="inlineStr"/>
+      <c r="L316" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M316" s="6" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N316" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O316" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="P316" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q316" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R316" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S316" s="6" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T316" s="6" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U316" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V316" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W316" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X316" s="6" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E317" s="4" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="F317" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G317" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H317" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I317" s="4" t="inlineStr">
+        <is>
+          <t>29/08/2027</t>
+        </is>
+      </c>
+      <c r="J317" s="4" t="inlineStr"/>
+      <c r="K317" s="4" t="inlineStr"/>
+      <c r="L317" s="4" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="M317" s="4" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="N317" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O317" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="P317" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q317" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R317" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S317" s="4" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T317" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U317" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V317" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W317" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X317" s="4" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E318" s="6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F318" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G318" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H318" s="6" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I318" s="6" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
+      <c r="J318" s="6" t="inlineStr"/>
+      <c r="K318" s="6" t="inlineStr"/>
+      <c r="L318" s="6" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="M318" s="6" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="N318" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O318" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="P318" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q318" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R318" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S318" s="6" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T318" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U318" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V318" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W318" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X318" s="6" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E319" s="4" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="F319" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G319" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H319" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I319" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J319" s="4" t="inlineStr"/>
+      <c r="K319" s="4" t="inlineStr"/>
+      <c r="L319" s="4" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M319" s="4" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="N319" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O319" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P319" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q319" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R319" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S319" s="4" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T319" s="4" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U319" s="4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V319" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W319" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X319" s="4" t="n">
+        <v>0.994</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D320" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E320" s="6" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F320" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G320" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H320" s="6" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I320" s="6" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="J320" s="6" t="inlineStr"/>
+      <c r="K320" s="6" t="inlineStr"/>
+      <c r="L320" s="6" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="M320" s="6" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="N320" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O320" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P320" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q320" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R320" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S320" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T320" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U320" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V320" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W320" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X320" s="6" t="n">
+        <v>1.063</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E321" s="4" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F321" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G321" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H321" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I321" s="4" t="n"/>
+      <c r="J321" s="4" t="inlineStr"/>
+      <c r="K321" s="4" t="inlineStr"/>
+      <c r="L321" s="4" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="M321" s="4" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="N321" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O321" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P321" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q321" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R321" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S321" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T321" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U321" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V321" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W321" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X321" s="4" t="n">
+        <v>1.025</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E322" s="6" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="F322" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G322" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H322" s="6" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I322" s="6" t="inlineStr">
+        <is>
+          <t>25/08/2027</t>
+        </is>
+      </c>
+      <c r="J322" s="6" t="inlineStr"/>
+      <c r="K322" s="6" t="inlineStr"/>
+      <c r="L322" s="6" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="M322" s="6" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="N322" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O322" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P322" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q322" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R322" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S322" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T322" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U322" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V322" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W322" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X322" s="6" t="n">
+        <v>0.987</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E323" s="4" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F323" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G323" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H323" s="4" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="I323" s="4" t="inlineStr">
+        <is>
+          <t>20/03/2028</t>
+        </is>
+      </c>
+      <c r="J323" s="4" t="inlineStr"/>
+      <c r="K323" s="4" t="inlineStr"/>
+      <c r="L323" s="4" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M323" s="4" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N323" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O323" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="P323" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q323" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R323" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S323" s="4" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T323" s="4" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U323" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V323" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W323" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X323" s="4" t="n">
+        <v>1.277</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E324" s="6" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F324" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G324" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H324" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I324" s="6" t="inlineStr">
+        <is>
+          <t>29/01/2028</t>
+        </is>
+      </c>
+      <c r="J324" s="6" t="inlineStr"/>
+      <c r="K324" s="6" t="inlineStr"/>
+      <c r="L324" s="6" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M324" s="6" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N324" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="O324" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="P324" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q324" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R324" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S324" s="6" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T324" s="6" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U324" s="6" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V324" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W324" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X324" s="6" t="n">
+        <v>1.186</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F325" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G325" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H325" s="4" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="I325" s="4" t="inlineStr">
+        <is>
+          <t>23/04/2027</t>
+        </is>
+      </c>
+      <c r="J325" s="4" t="inlineStr"/>
+      <c r="K325" s="4" t="inlineStr"/>
+      <c r="L325" s="4" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="M325" s="4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="N325" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O325" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="P325" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q325" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R325" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S325" s="4" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T325" s="4" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U325" s="4" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V325" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W325" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X325" s="4" t="n">
+        <v>0.701</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E326" s="6" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="F326" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G326" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H326" s="6" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I326" s="6" t="inlineStr">
+        <is>
+          <t>10/04/2028</t>
+        </is>
+      </c>
+      <c r="J326" s="6" t="inlineStr"/>
+      <c r="K326" s="6" t="inlineStr"/>
+      <c r="L326" s="6" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="M326" s="6" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N326" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O326" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="P326" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q326" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R326" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S326" s="6" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T326" s="6" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U326" s="6" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V326" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W326" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X326" s="6" t="n">
+        <v>0.616</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F327" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G327" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H327" s="4" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>23/09/2027</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="inlineStr"/>
+      <c r="K327" s="4" t="inlineStr"/>
+      <c r="L327" s="4" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="M327" s="4" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N327" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O327" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="P327" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q327" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R327" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S327" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T327" s="4" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U327" s="4" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V327" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W327" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X327" s="4" t="n">
+        <v>1.376</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F328" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G328" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H328" s="6" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="I328" s="6" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="J328" s="6" t="inlineStr"/>
+      <c r="K328" s="6" t="inlineStr"/>
+      <c r="L328" s="6" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M328" s="6" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="N328" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O328" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="P328" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q328" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R328" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S328" s="6" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T328" s="6" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U328" s="6" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V328" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W328" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X328" s="6" t="n">
+        <v>1.274</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E329" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F329" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G329" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H329" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I329" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J329" s="4" t="inlineStr"/>
+      <c r="K329" s="4" t="inlineStr"/>
+      <c r="L329" s="4" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="M329" s="4" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N329" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O329" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P329" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q329" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R329" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S329" s="4" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T329" s="4" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U329" s="4" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V329" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W329" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X329" s="4" t="n">
+        <v>1.127</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B330" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E330" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F330" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G330" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H330" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I330" s="6" t="inlineStr">
+        <is>
+          <t>09/04/2028</t>
+        </is>
+      </c>
+      <c r="J330" s="6" t="inlineStr"/>
+      <c r="K330" s="6" t="inlineStr"/>
+      <c r="L330" s="6" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="M330" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N330" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O330" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P330" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q330" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R330" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S330" s="6" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T330" s="6" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U330" s="6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V330" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W330" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X330" s="6" t="n">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F331" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G331" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H331" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I331" s="4" t="inlineStr">
+        <is>
+          <t>21/04/2028</t>
+        </is>
+      </c>
+      <c r="J331" s="4" t="inlineStr"/>
+      <c r="K331" s="4" t="inlineStr"/>
+      <c r="L331" s="4" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="M331" s="4" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="N331" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O331" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="P331" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q331" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R331" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S331" s="4" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T331" s="4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U331" s="4" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V331" s="4" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W331" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X331" s="4" t="n">
+        <v>1.042</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D332" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E332" s="6" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F332" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G332" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H332" s="6" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="I332" s="6" t="n"/>
+      <c r="J332" s="6" t="inlineStr"/>
+      <c r="K332" s="6" t="inlineStr"/>
+      <c r="L332" s="6" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="M332" s="6" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="N332" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O332" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="P332" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q332" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R332" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S332" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T332" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U332" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V332" s="6" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W332" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X332" s="6" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 30HD</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F333" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G333" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H333" s="4" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr"/>
+      <c r="K333" s="4" t="inlineStr"/>
+      <c r="L333" s="4" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M333" s="4" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="N333" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O333" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="P333" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q333" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R333" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S333" s="4" t="n">
+        <v>7170</v>
+      </c>
+      <c r="T333" s="4" t="n">
+        <v>3857</v>
+      </c>
+      <c r="U333" s="4" t="n">
+        <v>3903</v>
+      </c>
+      <c r="V333" s="4" t="inlineStr">
+        <is>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W333" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+        </is>
+      </c>
+      <c r="X333" s="4" t="n">
+        <v>2.018</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+        </is>
+      </c>
+      <c r="D334" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E334" s="6" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="F334" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G334" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H334" s="6" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="I334" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J334" s="6" t="inlineStr"/>
+      <c r="K334" s="6" t="inlineStr"/>
+      <c r="L334" s="6" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="M334" s="6" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N334" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O334" s="6" t="n">
+        <v>318</v>
+      </c>
+      <c r="P334" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q334" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R334" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S334" s="6" t="n">
+        <v>6681</v>
+      </c>
+      <c r="T334" s="6" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U334" s="6" t="n">
+        <v>4543</v>
+      </c>
+      <c r="V334" s="6" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+        </is>
+      </c>
+      <c r="W334" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+        </is>
+      </c>
+      <c r="X334" s="6" t="n">
+        <v>3.847</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E335" s="4" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F335" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G335" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H335" s="4" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J335" s="4" t="inlineStr"/>
+      <c r="K335" s="4" t="inlineStr"/>
+      <c r="L335" s="4" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="M335" s="4" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="N335" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O335" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="P335" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q335" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R335" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S335" s="4" t="n">
+        <v>7812</v>
+      </c>
+      <c r="T335" s="4" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U335" s="4" t="n">
+        <v>5312</v>
+      </c>
+      <c r="V335" s="4" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait).</t>
+        </is>
+      </c>
+      <c r="W335" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+        </is>
+      </c>
+      <c r="X335" s="4" t="n">
+        <v>3.396</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E336" s="6" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F336" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G336" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H336" s="6" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="I336" s="6" t="inlineStr">
+        <is>
+          <t>28/11/2027</t>
+        </is>
+      </c>
+      <c r="J336" s="6" t="inlineStr"/>
+      <c r="K336" s="6" t="inlineStr"/>
+      <c r="L336" s="6" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="M336" s="6" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="N336" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="O336" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="P336" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q336" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R336" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S336" s="6" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T336" s="6" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U336" s="6" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V336" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W336" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X336" s="6" t="n">
+        <v>1.176</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F337" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G337" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H337" s="4" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J337" s="4" t="inlineStr"/>
+      <c r="K337" s="4" t="inlineStr"/>
+      <c r="L337" s="4" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="M337" s="4" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N337" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O337" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="P337" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q337" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R337" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S337" s="4" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T337" s="4" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U337" s="4" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V337" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W337" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X337" s="4" t="n">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B338" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D338" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E338" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F338" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G338" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H338" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I338" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J338" s="6" t="inlineStr"/>
+      <c r="K338" s="6" t="inlineStr"/>
+      <c r="L338" s="6" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M338" s="6" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="N338" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="O338" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="P338" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q338" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="R338" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S338" s="6" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T338" s="6" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U338" s="6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V338" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W338" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X338" s="6" t="n">
+        <v>1.578</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E339" s="4" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="F339" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G339" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H339" s="4" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I339" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J339" s="4" t="inlineStr"/>
+      <c r="K339" s="4" t="inlineStr"/>
+      <c r="L339" s="4" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="M339" s="4" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="N339" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="O339" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="P339" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q339" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R339" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S339" s="4" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T339" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U339" s="4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V339" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W339" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X339" s="4" t="n">
+        <v>1.357</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D340" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E340" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F340" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G340" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H340" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I340" s="6" t="inlineStr">
+        <is>
+          <t>17/11/2027</t>
+        </is>
+      </c>
+      <c r="J340" s="6" t="inlineStr"/>
+      <c r="K340" s="6" t="inlineStr"/>
+      <c r="L340" s="6" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="M340" s="6" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="N340" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O340" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="P340" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q340" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R340" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S340" s="6" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T340" s="6" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U340" s="6" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V340" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W340" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X340" s="6" t="n">
+        <v>1.484</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F341" s="4" t="n"/>
+      <c r="G341" s="4" t="n"/>
+      <c r="H341" s="4" t="n"/>
+      <c r="I341" s="4" t="inlineStr"/>
+      <c r="J341" s="4" t="inlineStr"/>
+      <c r="K341" s="4" t="inlineStr"/>
+      <c r="L341" s="4" t="n"/>
+      <c r="M341" s="4" t="n"/>
+      <c r="N341" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="O341" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="P341" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q341" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R341" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S341" s="4" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T341" s="4" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U341" s="4" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V341" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W341" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X341" s="4" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F342" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G342" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H342" s="6" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I342" s="6" t="n"/>
+      <c r="J342" s="6" t="inlineStr"/>
+      <c r="K342" s="6" t="inlineStr"/>
+      <c r="L342" s="6" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M342" s="6" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="N342" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O342" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="P342" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q342" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R342" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S342" s="6" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T342" s="6" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U342" s="6" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V342" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W342" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X342" s="6" t="n">
+        <v>1.369</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E343" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F343" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G343" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H343" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J343" s="4" t="inlineStr"/>
+      <c r="K343" s="4" t="inlineStr"/>
+      <c r="L343" s="4" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M343" s="4" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="N343" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O343" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="P343" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q343" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R343" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S343" s="4" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T343" s="4" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U343" s="4" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V343" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W343" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X343" s="4" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E344" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F344" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G344" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H344" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I344" s="6" t="inlineStr">
+        <is>
+          <t>13/11/2027</t>
+        </is>
+      </c>
+      <c r="J344" s="6" t="inlineStr"/>
+      <c r="K344" s="6" t="inlineStr"/>
+      <c r="L344" s="6" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="M344" s="6" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="N344" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O344" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="P344" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q344" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R344" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S344" s="6" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T344" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U344" s="6" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V344" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W344" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X344" s="6" t="n">
+        <v>1.767</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E345" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F345" s="4" t="n"/>
+      <c r="G345" s="4" t="n"/>
+      <c r="H345" s="4" t="n"/>
+      <c r="I345" s="4" t="inlineStr"/>
+      <c r="J345" s="4" t="inlineStr"/>
+      <c r="K345" s="4" t="inlineStr"/>
+      <c r="L345" s="4" t="n"/>
+      <c r="M345" s="4" t="n"/>
+      <c r="N345" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O345" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="P345" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q345" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R345" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S345" s="4" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T345" s="4" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U345" s="4" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V345" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W345" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X345" s="4" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F346" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G346" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H346" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I346" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J346" s="6" t="inlineStr"/>
+      <c r="K346" s="6" t="inlineStr"/>
+      <c r="L346" s="6" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M346" s="6" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N346" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="O346" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="P346" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q346" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R346" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S346" s="6" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T346" s="6" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U346" s="6" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V346" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W346" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X346" s="6" t="n">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F347" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G347" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H347" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I347" s="4" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
+      <c r="J347" s="4" t="inlineStr"/>
+      <c r="K347" s="4" t="inlineStr"/>
+      <c r="L347" s="4" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="M347" s="4" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N347" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="O347" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="P347" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q347" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R347" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S347" s="4" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T347" s="4" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U347" s="4" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V347" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W347" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X347" s="4" t="n">
+        <v>0.649</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E348" s="6" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F348" s="6" t="n"/>
+      <c r="G348" s="6" t="n"/>
+      <c r="H348" s="6" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="I348" s="6" t="inlineStr"/>
+      <c r="J348" s="6" t="inlineStr"/>
+      <c r="K348" s="6" t="inlineStr"/>
+      <c r="L348" s="6" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="M348" s="6" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="N348" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="O348" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P348" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q348" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R348" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S348" s="6" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T348" s="6" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U348" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V348" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W348" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X348" s="6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E349" s="4" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F349" s="4" t="n"/>
+      <c r="G349" s="4" t="n"/>
+      <c r="H349" s="4" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="I349" s="4" t="inlineStr"/>
+      <c r="J349" s="4" t="inlineStr"/>
+      <c r="K349" s="4" t="inlineStr"/>
+      <c r="L349" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M349" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N349" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="O349" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P349" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q349" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R349" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S349" s="4" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T349" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U349" s="4" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V349" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W349" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X349" s="4" t="n">
+        <v>0.921</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D350" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E350" s="6" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="F350" s="6" t="n"/>
+      <c r="G350" s="6" t="n"/>
+      <c r="H350" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I350" s="6" t="inlineStr"/>
+      <c r="J350" s="6" t="inlineStr"/>
+      <c r="K350" s="6" t="inlineStr"/>
+      <c r="L350" s="6" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="M350" s="6" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="N350" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="O350" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="P350" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q350" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R350" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S350" s="6" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T350" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U350" s="6" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V350" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W350" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X350" s="6" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E351" s="4" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F351" s="4" t="n"/>
+      <c r="G351" s="4" t="n"/>
+      <c r="H351" s="4" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="I351" s="4" t="inlineStr"/>
+      <c r="J351" s="4" t="inlineStr"/>
+      <c r="K351" s="4" t="inlineStr"/>
+      <c r="L351" s="4" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="M351" s="4" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="N351" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="O351" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="P351" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q351" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R351" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S351" s="4" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T351" s="4" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U351" s="4" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V351" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W351" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X351" s="4" t="n">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D352" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E352" s="6" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="F352" s="6" t="n"/>
+      <c r="G352" s="6" t="n"/>
+      <c r="H352" s="6" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="I352" s="6" t="inlineStr"/>
+      <c r="J352" s="6" t="inlineStr"/>
+      <c r="K352" s="6" t="inlineStr"/>
+      <c r="L352" s="6" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="M352" s="6" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="N352" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O352" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="P352" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q352" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R352" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S352" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T352" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U352" s="6" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V352" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W352" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X352" s="6" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E353" s="4" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F353" s="4" t="n"/>
+      <c r="G353" s="4" t="n"/>
+      <c r="H353" s="4" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="I353" s="4" t="inlineStr"/>
+      <c r="J353" s="4" t="inlineStr"/>
+      <c r="K353" s="4" t="inlineStr"/>
+      <c r="L353" s="4" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="M353" s="4" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="N353" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O353" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="P353" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q353" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R353" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S353" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T353" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U353" s="4" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V353" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W353" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X353" s="4" t="n">
+        <v>0.676</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E354" s="6" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="F354" s="6" t="n"/>
+      <c r="G354" s="6" t="n"/>
+      <c r="H354" s="6" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I354" s="6" t="inlineStr"/>
+      <c r="J354" s="6" t="inlineStr"/>
+      <c r="K354" s="6" t="inlineStr"/>
+      <c r="L354" s="6" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="M354" s="6" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="N354" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O354" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="P354" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q354" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R354" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S354" s="6" t="n"/>
+      <c r="T354" s="6" t="n"/>
+      <c r="U354" s="6" t="n"/>
+      <c r="V354" s="6" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W354" s="6" t="inlineStr"/>
+      <c r="X354" s="6" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E355" s="4" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F355" s="4" t="n"/>
+      <c r="G355" s="4" t="n"/>
+      <c r="H355" s="4" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I355" s="4" t="inlineStr"/>
+      <c r="J355" s="4" t="inlineStr"/>
+      <c r="K355" s="4" t="inlineStr"/>
+      <c r="L355" s="4" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="M355" s="4" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="N355" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O355" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="P355" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q355" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R355" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S355" s="4" t="n"/>
+      <c r="T355" s="4" t="n"/>
+      <c r="U355" s="4" t="n"/>
+      <c r="V355" s="4" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W355" s="4" t="inlineStr"/>
+      <c r="X355" s="4" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B356" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E356" s="6" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F356" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G356" s="6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H356" s="6" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="I356" s="6" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J356" s="6" t="inlineStr"/>
+      <c r="K356" s="6" t="inlineStr"/>
+      <c r="L356" s="6" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="M356" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N356" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O356" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="P356" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q356" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R356" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S356" s="6" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T356" s="6" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U356" s="6" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V356" s="6" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W356" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X356" s="6" t="n">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E357" s="4" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="F357" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G357" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H357" s="4" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="I357" s="4" t="inlineStr">
+        <is>
+          <t>23/02/2028</t>
+        </is>
+      </c>
+      <c r="J357" s="4" t="inlineStr"/>
+      <c r="K357" s="4" t="inlineStr"/>
+      <c r="L357" s="4" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="M357" s="4" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="N357" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O357" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="P357" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q357" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R357" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S357" s="4" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T357" s="4" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U357" s="4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V357" s="4" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W357" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X357" s="4" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B358" s="5" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D358" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E358" s="6" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F358" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G358" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H358" s="6" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I358" s="6" t="inlineStr">
+        <is>
+          <t>23/01/2028</t>
+        </is>
+      </c>
+      <c r="J358" s="6" t="inlineStr"/>
+      <c r="K358" s="6" t="inlineStr"/>
+      <c r="L358" s="6" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="M358" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="N358" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O358" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P358" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q358" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R358" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S358" s="6" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T358" s="6" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U358" s="6" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V358" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W358" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X358" s="6" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="F359" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G359" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H359" s="4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I359" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
+      <c r="J359" s="4" t="inlineStr"/>
+      <c r="K359" s="4" t="inlineStr"/>
+      <c r="L359" s="4" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="M359" s="4" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="N359" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O359" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P359" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q359" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R359" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S359" s="4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T359" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U359" s="4" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V359" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W359" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X359" s="4" t="n">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E360" s="6" t="n"/>
+      <c r="F360" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G360" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H360" s="6" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="I360" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J360" s="6" t="inlineStr"/>
+      <c r="K360" s="6" t="inlineStr"/>
+      <c r="L360" s="6" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="M360" s="6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N360" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O360" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="P360" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q360" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R360" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S360" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T360" s="6" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U360" s="6" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V360" s="6" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W360" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X360" s="6" t="n">
+        <v>1.257</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="n"/>
+      <c r="F361" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G361" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H361" s="4" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I361" s="4" t="n"/>
+      <c r="J361" s="4" t="inlineStr"/>
+      <c r="K361" s="4" t="inlineStr"/>
+      <c r="L361" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M361" s="4" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N361" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O361" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="P361" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q361" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R361" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S361" s="4" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T361" s="4" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U361" s="4" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V361" s="4" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W361" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X361" s="4" t="n">
+        <v>0.848</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E362" s="6" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F362" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G362" s="6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H362" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I362" s="6" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J362" s="6" t="inlineStr"/>
+      <c r="K362" s="6" t="inlineStr"/>
+      <c r="L362" s="6" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="M362" s="6" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N362" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O362" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="P362" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q362" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R362" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S362" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T362" s="6" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U362" s="6" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V362" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W362" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X362" s="6" t="n">
+        <v>0.747</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F363" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G363" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H363" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I363" s="4" t="inlineStr">
+        <is>
+          <t>30/10/2027</t>
+        </is>
+      </c>
+      <c r="J363" s="4" t="inlineStr"/>
+      <c r="K363" s="4" t="inlineStr"/>
+      <c r="L363" s="4" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="M363" s="4" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="N363" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O363" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="P363" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q363" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R363" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S363" s="4" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T363" s="4" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U363" s="4" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V363" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W363" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X363" s="4" t="n">
+        <v>0.704</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D364" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E364" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F364" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G364" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H364" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I364" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J364" s="6" t="inlineStr"/>
+      <c r="K364" s="6" t="inlineStr"/>
+      <c r="L364" s="6" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="M364" s="6" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N364" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O364" s="6" t="n">
+        <v>384</v>
+      </c>
+      <c r="P364" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q364" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R364" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S364" s="6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T364" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U364" s="6" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V364" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W364" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X364" s="6" t="n">
+        <v>0.645</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E365" s="4" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="F365" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G365" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H365" s="4" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I365" s="4" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J365" s="4" t="inlineStr"/>
+      <c r="K365" s="4" t="inlineStr"/>
+      <c r="L365" s="4" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="M365" s="4" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="N365" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O365" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P365" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q365" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R365" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S365" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T365" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U365" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V365" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W365" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X365" s="4" t="n">
+        <v>0.461</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B366" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E366" s="6" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F366" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G366" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H366" s="6" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="I366" s="6" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J366" s="6" t="inlineStr"/>
+      <c r="K366" s="6" t="inlineStr"/>
+      <c r="L366" s="6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M366" s="6" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N366" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O366" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="P366" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q366" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R366" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S366" s="6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T366" s="6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U366" s="6" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V366" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W366" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X366" s="6" t="n">
+        <v>0.771</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E367" s="4" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F367" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G367" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H367" s="4" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="I367" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J367" s="4" t="inlineStr"/>
+      <c r="K367" s="4" t="inlineStr"/>
+      <c r="L367" s="4" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M367" s="4" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="N367" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O367" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P367" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q367" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R367" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S367" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T367" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U367" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V367" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W367" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X367" s="4" t="n">
+        <v>0.613</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X367"/>
+  <dimension ref="A1:Y369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -492,6 +492,7 @@
     <col width="80" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -603,6 +604,11 @@
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Coût/3g leucine (€)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
         </is>
       </c>
     </row>
@@ -15207,32 +15213,18 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2kg</t>
         </is>
       </c>
       <c r="E313" s="4" t="n"/>
-      <c r="F313" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G313" s="4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H313" s="4" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="I313" s="4" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
+      <c r="F313" s="4" t="n"/>
+      <c r="G313" s="4" t="n"/>
+      <c r="H313" s="4" t="n"/>
+      <c r="I313" s="4" t="inlineStr"/>
       <c r="J313" s="4" t="inlineStr"/>
       <c r="K313" s="4" t="inlineStr"/>
-      <c r="L313" s="4" t="n">
-        <v>30.49</v>
-      </c>
-      <c r="M313" s="4" t="n">
-        <v>0.915</v>
-      </c>
+      <c r="L313" s="4" t="n"/>
+      <c r="M313" s="4" t="n"/>
       <c r="N313" s="4" t="n">
         <v>74</v>
       </c>
@@ -15267,9 +15259,7 @@
           <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
         </is>
       </c>
-      <c r="X313" s="4" t="n">
-        <v>0.821</v>
-      </c>
+      <c r="X313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -15289,28 +15279,18 @@
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E314" s="6" t="n"/>
-      <c r="F314" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="G314" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H314" s="6" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="I314" s="6" t="n"/>
+      <c r="F314" s="6" t="n"/>
+      <c r="G314" s="6" t="n"/>
+      <c r="H314" s="6" t="n"/>
+      <c r="I314" s="6" t="inlineStr"/>
       <c r="J314" s="6" t="inlineStr"/>
       <c r="K314" s="6" t="inlineStr"/>
-      <c r="L314" s="6" t="n">
-        <v>28.27</v>
-      </c>
-      <c r="M314" s="6" t="n">
-        <v>0.848</v>
-      </c>
+      <c r="L314" s="6" t="n"/>
+      <c r="M314" s="6" t="n"/>
       <c r="N314" s="6" t="n">
         <v>74</v>
       </c>
@@ -15345,9 +15325,7 @@
           <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
         </is>
       </c>
-      <c r="X314" s="6" t="n">
-        <v>0.761</v>
-      </c>
+      <c r="X314" s="6" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -15371,28 +15349,14 @@
         </is>
       </c>
       <c r="E315" s="4" t="n"/>
-      <c r="F315" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G315" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H315" s="4" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="I315" s="4" t="inlineStr">
-        <is>
-          <t>12/12/2027</t>
-        </is>
-      </c>
+      <c r="F315" s="4" t="n"/>
+      <c r="G315" s="4" t="n"/>
+      <c r="H315" s="4" t="n"/>
+      <c r="I315" s="4" t="inlineStr"/>
       <c r="J315" s="4" t="inlineStr"/>
       <c r="K315" s="4" t="inlineStr"/>
-      <c r="L315" s="4" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="M315" s="4" t="n">
-        <v>0.8169999999999999</v>
-      </c>
+      <c r="L315" s="4" t="n"/>
+      <c r="M315" s="4" t="n"/>
       <c r="N315" s="4" t="n">
         <v>74</v>
       </c>
@@ -15427,9 +15391,7 @@
           <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
         </is>
       </c>
-      <c r="X315" s="4" t="n">
-        <v>0.733</v>
-      </c>
+      <c r="X315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -15439,81 +15401,63 @@
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+          <t>EVOWHEY PROTEIN</t>
         </is>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="E316" s="6" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="F316" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G316" s="6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H316" s="6" t="n">
-        <v>24.64</v>
-      </c>
-      <c r="I316" s="6" t="inlineStr">
-        <is>
-          <t>05/02/2028</t>
-        </is>
-      </c>
+          <t>2 Kg</t>
+        </is>
+      </c>
+      <c r="E316" s="6" t="n"/>
+      <c r="F316" s="6" t="n"/>
+      <c r="G316" s="6" t="n"/>
+      <c r="H316" s="6" t="n"/>
+      <c r="I316" s="6" t="inlineStr"/>
       <c r="J316" s="6" t="inlineStr"/>
       <c r="K316" s="6" t="inlineStr"/>
-      <c r="L316" s="6" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="M316" s="6" t="n">
-        <v>0.999</v>
-      </c>
+      <c r="L316" s="6" t="n"/>
+      <c r="M316" s="6" t="n"/>
       <c r="N316" s="6" t="n">
         <v>74</v>
       </c>
       <c r="O316" s="6" t="n">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="P316" s="6" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q316" s="6" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="R316" s="6" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="S316" s="6" t="n">
-        <v>8356</v>
+        <v>8247</v>
       </c>
       <c r="T316" s="6" t="n">
-        <v>4911</v>
+        <v>4702</v>
       </c>
       <c r="U316" s="6" t="n">
-        <v>4544</v>
+        <v>4341</v>
       </c>
       <c r="V316" s="6" t="inlineStr">
         <is>
-          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W316" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
-        </is>
-      </c>
-      <c r="X316" s="6" t="n">
-        <v>0.885</v>
-      </c>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X316" s="6" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -15523,81 +15467,63 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+          <t>EVOWHEY PROTEIN</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
-        </is>
-      </c>
-      <c r="E317" s="4" t="n">
-        <v>43.99</v>
-      </c>
-      <c r="F317" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G317" s="4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H317" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I317" s="4" t="inlineStr">
-        <is>
-          <t>29/08/2027</t>
-        </is>
-      </c>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="E317" s="4" t="n"/>
+      <c r="F317" s="4" t="n"/>
+      <c r="G317" s="4" t="n"/>
+      <c r="H317" s="4" t="n"/>
+      <c r="I317" s="4" t="inlineStr"/>
       <c r="J317" s="4" t="inlineStr"/>
       <c r="K317" s="4" t="inlineStr"/>
-      <c r="L317" s="4" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="M317" s="4" t="n">
-        <v>0.892</v>
-      </c>
+      <c r="L317" s="4" t="n"/>
+      <c r="M317" s="4" t="n"/>
       <c r="N317" s="4" t="n">
         <v>74</v>
       </c>
       <c r="O317" s="4" t="n">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="P317" s="4" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q317" s="4" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="R317" s="4" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="S317" s="4" t="n">
-        <v>8356</v>
+        <v>8247</v>
       </c>
       <c r="T317" s="4" t="n">
-        <v>4911</v>
+        <v>4702</v>
       </c>
       <c r="U317" s="4" t="n">
-        <v>4544</v>
+        <v>4341</v>
       </c>
       <c r="V317" s="4" t="inlineStr">
         <is>
-          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W317" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
-        </is>
-      </c>
-      <c r="X317" s="4" t="n">
-        <v>0.79</v>
-      </c>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -15607,81 +15533,63 @@
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+          <t>EVOWHEY PROTEIN</t>
         </is>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
-        </is>
-      </c>
-      <c r="E318" s="6" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="F318" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G318" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H318" s="6" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="I318" s="6" t="inlineStr">
-        <is>
-          <t>09/12/2027</t>
-        </is>
-      </c>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E318" s="6" t="n"/>
+      <c r="F318" s="6" t="n"/>
+      <c r="G318" s="6" t="n"/>
+      <c r="H318" s="6" t="n"/>
+      <c r="I318" s="6" t="inlineStr"/>
       <c r="J318" s="6" t="inlineStr"/>
       <c r="K318" s="6" t="inlineStr"/>
-      <c r="L318" s="6" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="M318" s="6" t="n">
-        <v>1.318</v>
-      </c>
+      <c r="L318" s="6" t="n"/>
+      <c r="M318" s="6" t="n"/>
       <c r="N318" s="6" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="O318" s="6" t="n">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="Q318" s="6" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="R318" s="6" t="n">
-        <v>1.4</v>
+        <v>0.77</v>
       </c>
       <c r="S318" s="6" t="n">
-        <v>9656</v>
+        <v>8247</v>
       </c>
       <c r="T318" s="6" t="n">
-        <v>5962</v>
+        <v>4702</v>
       </c>
       <c r="U318" s="6" t="n">
-        <v>5290</v>
+        <v>4341</v>
       </c>
       <c r="V318" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W318" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
-        </is>
-      </c>
-      <c r="X318" s="6" t="n">
-        <v>1.16</v>
-      </c>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X318" s="6" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -15691,80 +15599,80 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>63.99</v>
+        <v>12.32</v>
       </c>
       <c r="F319" s="4" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="G319" s="4" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="H319" s="4" t="n">
-        <v>32</v>
+        <v>24.64</v>
       </c>
       <c r="I319" s="4" t="inlineStr">
         <is>
-          <t>19/02/2028</t>
+          <t>05/02/2028</t>
         </is>
       </c>
       <c r="J319" s="4" t="inlineStr"/>
       <c r="K319" s="4" t="inlineStr"/>
       <c r="L319" s="4" t="n">
-        <v>37.65</v>
+        <v>33.3</v>
       </c>
       <c r="M319" s="4" t="n">
-        <v>1.129</v>
+        <v>0.999</v>
       </c>
       <c r="N319" s="4" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="O319" s="4" t="n">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="P319" s="4" t="n">
-        <v>2.2</v>
+        <v>7.9</v>
       </c>
       <c r="Q319" s="4" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="R319" s="4" t="n">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="S319" s="4" t="n">
-        <v>9656</v>
+        <v>8356</v>
       </c>
       <c r="T319" s="4" t="n">
-        <v>5962</v>
+        <v>4911</v>
       </c>
       <c r="U319" s="4" t="n">
-        <v>5290</v>
+        <v>4544</v>
       </c>
       <c r="V319" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
         </is>
       </c>
       <c r="W319" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
         </is>
       </c>
       <c r="X319" s="4" t="n">
-        <v>0.994</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="320">
@@ -15775,80 +15683,80 @@
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>100% WHEY PROTEIN ISOLATE</t>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E320" s="6" t="n">
-        <v>18.59</v>
+        <v>43.99</v>
       </c>
       <c r="F320" s="6" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="G320" s="6" t="n">
-        <v>1.16</v>
+        <v>0.66</v>
       </c>
       <c r="H320" s="6" t="n">
-        <v>37.18</v>
+        <v>22</v>
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>29/08/2027</t>
         </is>
       </c>
       <c r="J320" s="6" t="inlineStr"/>
       <c r="K320" s="6" t="inlineStr"/>
       <c r="L320" s="6" t="n">
-        <v>39.98</v>
+        <v>29.73</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>1.199</v>
+        <v>0.892</v>
       </c>
       <c r="N320" s="6" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="O320" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="Q320" s="6" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="R320" s="6" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="S320" s="6" t="n">
-        <v>10492</v>
+        <v>8356</v>
       </c>
       <c r="T320" s="6" t="n">
-        <v>6592</v>
+        <v>4911</v>
       </c>
       <c r="U320" s="6" t="n">
-        <v>6221</v>
+        <v>4544</v>
       </c>
       <c r="V320" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
         </is>
       </c>
       <c r="W320" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
         </is>
       </c>
       <c r="X320" s="6" t="n">
-        <v>1.063</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="321">
@@ -15859,76 +15767,80 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>100% WHEY PROTEIN ISOLATE</t>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>750g</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E321" s="4" t="n">
-        <v>26.88</v>
+        <v>18.67</v>
       </c>
       <c r="F321" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G321" s="4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H321" s="4" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="I321" s="4" t="n"/>
+        <v>37.34</v>
+      </c>
+      <c r="I321" s="4" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
       <c r="J321" s="4" t="inlineStr"/>
       <c r="K321" s="4" t="inlineStr"/>
       <c r="L321" s="4" t="n">
-        <v>38.54</v>
+        <v>43.93</v>
       </c>
       <c r="M321" s="4" t="n">
-        <v>1.156</v>
+        <v>1.318</v>
       </c>
       <c r="N321" s="4" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="P321" s="4" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q321" s="4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="R321" s="4" t="n">
-        <v>0.45</v>
+        <v>1.4</v>
       </c>
       <c r="S321" s="4" t="n">
-        <v>10492</v>
+        <v>9656</v>
       </c>
       <c r="T321" s="4" t="n">
-        <v>6592</v>
+        <v>5962</v>
       </c>
       <c r="U321" s="4" t="n">
-        <v>6221</v>
+        <v>5290</v>
       </c>
       <c r="V321" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
         </is>
       </c>
       <c r="W321" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
         </is>
       </c>
       <c r="X321" s="4" t="n">
-        <v>1.025</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="322">
@@ -15939,12 +15851,12 @@
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>100% WHEY PROTEIN ISOLATE</t>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
@@ -15953,66 +15865,66 @@
         </is>
       </c>
       <c r="E322" s="6" t="n">
-        <v>69.05</v>
+        <v>63.99</v>
       </c>
       <c r="F322" s="6" t="n">
         <v>67</v>
       </c>
       <c r="G322" s="6" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="H322" s="6" t="n">
-        <v>34.53</v>
+        <v>32</v>
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>25/08/2027</t>
+          <t>19/02/2028</t>
         </is>
       </c>
       <c r="J322" s="6" t="inlineStr"/>
       <c r="K322" s="6" t="inlineStr"/>
       <c r="L322" s="6" t="n">
-        <v>37.13</v>
+        <v>37.65</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>1.114</v>
+        <v>1.129</v>
       </c>
       <c r="N322" s="6" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O322" s="6" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="P322" s="6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q322" s="6" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="R322" s="6" t="n">
-        <v>0.45</v>
+        <v>1.4</v>
       </c>
       <c r="S322" s="6" t="n">
-        <v>10492</v>
+        <v>9656</v>
       </c>
       <c r="T322" s="6" t="n">
-        <v>6592</v>
+        <v>5962</v>
       </c>
       <c r="U322" s="6" t="n">
-        <v>6221</v>
+        <v>5290</v>
       </c>
       <c r="V322" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
         </is>
       </c>
       <c r="W322" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
         </is>
       </c>
       <c r="X322" s="6" t="n">
-        <v>0.987</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="323">
@@ -16023,12 +15935,12 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+          <t>100% WHEY PROTEIN ISOLATE</t>
         </is>
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -16037,66 +15949,66 @@
         </is>
       </c>
       <c r="E323" s="4" t="n">
-        <v>19.92</v>
+        <v>18.59</v>
       </c>
       <c r="F323" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G323" s="4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H323" s="4" t="n">
-        <v>39.84</v>
+        <v>37.18</v>
       </c>
       <c r="I323" s="4" t="inlineStr">
         <is>
-          <t>20/03/2028</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="J323" s="4" t="inlineStr"/>
       <c r="K323" s="4" t="inlineStr"/>
       <c r="L323" s="4" t="n">
-        <v>47.43</v>
+        <v>39.98</v>
       </c>
       <c r="M323" s="4" t="n">
-        <v>1.423</v>
+        <v>1.199</v>
       </c>
       <c r="N323" s="4" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="O323" s="4" t="n">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="P323" s="4" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="Q323" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="R323" s="4" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="S323" s="4" t="n">
-        <v>9358</v>
+        <v>10492</v>
       </c>
       <c r="T323" s="4" t="n">
-        <v>5879</v>
+        <v>6592</v>
       </c>
       <c r="U323" s="4" t="n">
-        <v>5548</v>
+        <v>6221</v>
       </c>
       <c r="V323" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W323" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
         </is>
       </c>
       <c r="X323" s="4" t="n">
-        <v>1.277</v>
+        <v>1.063</v>
       </c>
     </row>
     <row r="324">
@@ -16107,80 +16019,76 @@
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+          <t>100% WHEY PROTEIN ISOLATE</t>
         </is>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>750g</t>
         </is>
       </c>
       <c r="E324" s="6" t="n">
-        <v>73.98999999999999</v>
+        <v>26.88</v>
       </c>
       <c r="F324" s="6" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="G324" s="6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="H324" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="I324" s="6" t="inlineStr">
-        <is>
-          <t>29/01/2028</t>
-        </is>
-      </c>
+        <v>35.84</v>
+      </c>
+      <c r="I324" s="6" t="n"/>
       <c r="J324" s="6" t="inlineStr"/>
       <c r="K324" s="6" t="inlineStr"/>
       <c r="L324" s="6" t="n">
-        <v>44.05</v>
+        <v>38.54</v>
       </c>
       <c r="M324" s="6" t="n">
-        <v>1.321</v>
+        <v>1.156</v>
       </c>
       <c r="N324" s="6" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="O324" s="6" t="n">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="P324" s="6" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="Q324" s="6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="R324" s="6" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="S324" s="6" t="n">
-        <v>9358</v>
+        <v>10492</v>
       </c>
       <c r="T324" s="6" t="n">
-        <v>5879</v>
+        <v>6592</v>
       </c>
       <c r="U324" s="6" t="n">
-        <v>5548</v>
+        <v>6221</v>
       </c>
       <c r="V324" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W324" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
         </is>
       </c>
       <c r="X324" s="6" t="n">
-        <v>1.186</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="325">
@@ -16191,80 +16099,80 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>EVOBASIC WHEY</t>
+          <t>100% WHEY PROTEIN ISOLATE</t>
         </is>
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E325" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="F325" s="4" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G325" s="4" t="n">
-        <v>0.57</v>
+        <v>1.03</v>
       </c>
       <c r="H325" s="4" t="n">
-        <v>19.22</v>
+        <v>34.53</v>
       </c>
       <c r="I325" s="4" t="inlineStr">
         <is>
-          <t>23/04/2027</t>
+          <t>25/08/2027</t>
         </is>
       </c>
       <c r="J325" s="4" t="inlineStr"/>
       <c r="K325" s="4" t="inlineStr"/>
       <c r="L325" s="4" t="n">
-        <v>27.07</v>
+        <v>37.13</v>
       </c>
       <c r="M325" s="4" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.114</v>
       </c>
       <c r="N325" s="4" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O325" s="4" t="n">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="P325" s="4" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="Q325" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R325" s="4" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="S325" s="4" t="n">
-        <v>8224</v>
+        <v>10492</v>
       </c>
       <c r="T325" s="4" t="n">
-        <v>3939</v>
+        <v>6592</v>
       </c>
       <c r="U325" s="4" t="n">
-        <v>4215</v>
+        <v>6221</v>
       </c>
       <c r="V325" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W325" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
         </is>
       </c>
       <c r="X325" s="4" t="n">
-        <v>0.701</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="326">
@@ -16275,80 +16183,80 @@
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>EVOBASIC WHEY</t>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
         </is>
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E326" s="6" t="n">
-        <v>33.78</v>
+        <v>19.92</v>
       </c>
       <c r="F326" s="6" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="G326" s="6" t="n">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="H326" s="6" t="n">
-        <v>16.89</v>
+        <v>39.84</v>
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>10/04/2028</t>
+          <t>20/03/2028</t>
         </is>
       </c>
       <c r="J326" s="6" t="inlineStr"/>
       <c r="K326" s="6" t="inlineStr"/>
       <c r="L326" s="6" t="n">
-        <v>23.79</v>
+        <v>47.43</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>0.714</v>
+        <v>1.423</v>
       </c>
       <c r="N326" s="6" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="O326" s="6" t="n">
-        <v>430</v>
+        <v>364</v>
       </c>
       <c r="P326" s="6" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q326" s="6" t="n">
-        <v>16</v>
+        <v>1.1</v>
       </c>
       <c r="R326" s="6" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="S326" s="6" t="n">
-        <v>8224</v>
+        <v>9358</v>
       </c>
       <c r="T326" s="6" t="n">
-        <v>3939</v>
+        <v>5879</v>
       </c>
       <c r="U326" s="6" t="n">
-        <v>4215</v>
+        <v>5548</v>
       </c>
       <c r="V326" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
         </is>
       </c>
       <c r="W326" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
         </is>
       </c>
       <c r="X326" s="6" t="n">
-        <v>0.616</v>
+        <v>1.277</v>
       </c>
     </row>
     <row r="327">
@@ -16359,80 +16267,80 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>KETO WHEY PROTEIN</t>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
         </is>
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E327" s="4" t="n">
-        <v>16.31</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="F327" s="4" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G327" s="4" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="H327" s="4" t="n">
-        <v>32.62</v>
+        <v>37</v>
       </c>
       <c r="I327" s="4" t="inlineStr">
         <is>
-          <t>23/09/2027</t>
+          <t>29/01/2028</t>
         </is>
       </c>
       <c r="J327" s="4" t="inlineStr"/>
       <c r="K327" s="4" t="inlineStr"/>
       <c r="L327" s="4" t="n">
-        <v>50.18</v>
+        <v>44.05</v>
       </c>
       <c r="M327" s="4" t="n">
-        <v>1.505</v>
+        <v>1.321</v>
       </c>
       <c r="N327" s="4" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="O327" s="4" t="n">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="P327" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="Q327" s="4" t="n">
-        <v>16</v>
+        <v>1.1</v>
       </c>
       <c r="R327" s="4" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="S327" s="4" t="n">
-        <v>7113</v>
+        <v>9358</v>
       </c>
       <c r="T327" s="4" t="n">
-        <v>4469</v>
+        <v>5879</v>
       </c>
       <c r="U327" s="4" t="n">
-        <v>4218</v>
+        <v>5548</v>
       </c>
       <c r="V327" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
         </is>
       </c>
       <c r="W327" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
         </is>
       </c>
       <c r="X327" s="4" t="n">
-        <v>1.376</v>
+        <v>1.186</v>
       </c>
     </row>
     <row r="328">
@@ -16443,80 +16351,80 @@
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>KETO WHEY PROTEIN</t>
+          <t>EVOBASIC WHEY</t>
         </is>
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E328" s="6" t="n">
-        <v>44.03</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F328" s="6" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="G328" s="6" t="n">
-        <v>1.06</v>
+        <v>0.57</v>
       </c>
       <c r="H328" s="6" t="n">
-        <v>30.21</v>
+        <v>19.22</v>
       </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>23/04/2027</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr"/>
       <c r="K328" s="6" t="inlineStr"/>
       <c r="L328" s="6" t="n">
-        <v>46.48</v>
+        <v>27.07</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>1.394</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N328" s="6" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O328" s="6" t="n">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="Q328" s="6" t="n">
         <v>16</v>
       </c>
       <c r="R328" s="6" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="S328" s="6" t="n">
-        <v>7113</v>
+        <v>8224</v>
       </c>
       <c r="T328" s="6" t="n">
-        <v>4469</v>
+        <v>3939</v>
       </c>
       <c r="U328" s="6" t="n">
-        <v>4218</v>
+        <v>4215</v>
       </c>
       <c r="V328" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
         </is>
       </c>
       <c r="W328" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
         </is>
       </c>
       <c r="X328" s="6" t="n">
-        <v>1.274</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="329">
@@ -16527,80 +16435,80 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+          <t>EVOBASIC WHEY</t>
         </is>
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>17.3</v>
+        <v>33.78</v>
       </c>
       <c r="F329" s="4" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="G329" s="4" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H329" s="4" t="n">
-        <v>34.6</v>
+        <v>16.89</v>
       </c>
       <c r="I329" s="4" t="inlineStr">
         <is>
-          <t>14/04/2028</t>
+          <t>10/04/2028</t>
         </is>
       </c>
       <c r="J329" s="4" t="inlineStr"/>
       <c r="K329" s="4" t="inlineStr"/>
       <c r="L329" s="4" t="n">
-        <v>42.72</v>
+        <v>23.79</v>
       </c>
       <c r="M329" s="4" t="n">
-        <v>1.282</v>
+        <v>0.714</v>
       </c>
       <c r="N329" s="4" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O329" s="4" t="n">
-        <v>362</v>
+        <v>430</v>
       </c>
       <c r="P329" s="4" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q329" s="4" t="n">
-        <v>2.8</v>
+        <v>16</v>
       </c>
       <c r="R329" s="4" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="S329" s="4" t="n">
-        <v>9214</v>
+        <v>8224</v>
       </c>
       <c r="T329" s="4" t="n">
-        <v>5654</v>
+        <v>3939</v>
       </c>
       <c r="U329" s="4" t="n">
-        <v>5307</v>
+        <v>4215</v>
       </c>
       <c r="V329" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
         </is>
       </c>
       <c r="W329" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
         </is>
       </c>
       <c r="X329" s="4" t="n">
-        <v>1.127</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="330">
@@ -16611,80 +16519,80 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+          <t>KETO WHEY PROTEIN</t>
         </is>
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E330" s="6" t="n">
-        <v>64.25</v>
+        <v>16.31</v>
       </c>
       <c r="F330" s="6" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="G330" s="6" t="n">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="H330" s="6" t="n">
-        <v>32.13</v>
+        <v>32.62</v>
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>09/04/2028</t>
+          <t>23/09/2027</t>
         </is>
       </c>
       <c r="J330" s="6" t="inlineStr"/>
       <c r="K330" s="6" t="inlineStr"/>
       <c r="L330" s="6" t="n">
-        <v>39.67</v>
+        <v>50.18</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>1.19</v>
+        <v>1.505</v>
       </c>
       <c r="N330" s="6" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="O330" s="6" t="n">
-        <v>362</v>
+        <v>449</v>
       </c>
       <c r="P330" s="6" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q330" s="6" t="n">
-        <v>2.8</v>
+        <v>16</v>
       </c>
       <c r="R330" s="6" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S330" s="6" t="n">
-        <v>9214</v>
+        <v>7113</v>
       </c>
       <c r="T330" s="6" t="n">
-        <v>5654</v>
+        <v>4469</v>
       </c>
       <c r="U330" s="6" t="n">
-        <v>5307</v>
+        <v>4218</v>
       </c>
       <c r="V330" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
         </is>
       </c>
       <c r="W330" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
         </is>
       </c>
       <c r="X330" s="6" t="n">
-        <v>1.046</v>
+        <v>1.376</v>
       </c>
     </row>
     <row r="331">
@@ -16695,80 +16603,80 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>EVOWHEY &amp; OATS</t>
+          <t>KETO WHEY PROTEIN</t>
         </is>
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E331" s="4" t="n">
-        <v>10.02</v>
+        <v>44.03</v>
       </c>
       <c r="F331" s="4" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="G331" s="4" t="n">
-        <v>0.8</v>
+        <v>1.06</v>
       </c>
       <c r="H331" s="4" t="n">
-        <v>15.9</v>
+        <v>30.21</v>
       </c>
       <c r="I331" s="4" t="inlineStr">
         <is>
-          <t>21/04/2028</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="J331" s="4" t="inlineStr"/>
       <c r="K331" s="4" t="inlineStr"/>
       <c r="L331" s="4" t="n">
-        <v>36.98</v>
+        <v>46.48</v>
       </c>
       <c r="M331" s="4" t="n">
-        <v>1.109</v>
+        <v>1.394</v>
       </c>
       <c r="N331" s="4" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="O331" s="4" t="n">
-        <v>388</v>
+        <v>449</v>
       </c>
       <c r="P331" s="4" t="n">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q331" s="4" t="n">
-        <v>6.5</v>
+        <v>16</v>
       </c>
       <c r="R331" s="4" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="S331" s="4" t="n">
-        <v>4577</v>
+        <v>7113</v>
       </c>
       <c r="T331" s="4" t="n">
-        <v>2682</v>
+        <v>4469</v>
       </c>
       <c r="U331" s="4" t="n">
-        <v>2571</v>
+        <v>4218</v>
       </c>
       <c r="V331" s="4" t="inlineStr">
         <is>
-          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
         </is>
       </c>
       <c r="W331" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
         </is>
       </c>
       <c r="X331" s="4" t="n">
-        <v>1.042</v>
+        <v>1.274</v>
       </c>
     </row>
     <row r="332">
@@ -16779,76 +16687,80 @@
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>EVOWHEY &amp; OATS</t>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
         </is>
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E332" s="6" t="n">
-        <v>24.95</v>
+        <v>17.3</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G332" s="6" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H332" s="6" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="I332" s="6" t="n"/>
+        <v>34.6</v>
+      </c>
+      <c r="I332" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
       <c r="J332" s="6" t="inlineStr"/>
       <c r="K332" s="6" t="inlineStr"/>
       <c r="L332" s="6" t="n">
-        <v>36.56</v>
+        <v>42.72</v>
       </c>
       <c r="M332" s="6" t="n">
-        <v>1.097</v>
+        <v>1.282</v>
       </c>
       <c r="N332" s="6" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="O332" s="6" t="n">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="P332" s="6" t="n">
-        <v>38</v>
+        <v>2.8</v>
       </c>
       <c r="Q332" s="6" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="R332" s="6" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="S332" s="6" t="n">
-        <v>4577</v>
+        <v>9214</v>
       </c>
       <c r="T332" s="6" t="n">
-        <v>2682</v>
+        <v>5654</v>
       </c>
       <c r="U332" s="6" t="n">
-        <v>2571</v>
+        <v>5307</v>
       </c>
       <c r="V332" s="6" t="inlineStr">
         <is>
-          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W332" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
         </is>
       </c>
       <c r="X332" s="6" t="n">
-        <v>1.03</v>
+        <v>1.127</v>
       </c>
     </row>
     <row r="333">
@@ -16859,80 +16771,80 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>EVOHYDRO 30HD</t>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
         </is>
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>24.11</v>
+        <v>64.25</v>
       </c>
       <c r="F333" s="4" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="G333" s="4" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H333" s="4" t="n">
-        <v>48.22</v>
+        <v>32.13</v>
       </c>
       <c r="I333" s="4" t="inlineStr">
         <is>
-          <t>13/02/2028</t>
+          <t>09/04/2028</t>
         </is>
       </c>
       <c r="J333" s="4" t="inlineStr"/>
       <c r="K333" s="4" t="inlineStr"/>
       <c r="L333" s="4" t="n">
-        <v>74.18000000000001</v>
+        <v>39.67</v>
       </c>
       <c r="M333" s="4" t="n">
-        <v>2.225</v>
+        <v>1.19</v>
       </c>
       <c r="N333" s="4" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O333" s="4" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P333" s="4" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q333" s="4" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="R333" s="4" t="n">
-        <v>2</v>
+        <v>0.91</v>
       </c>
       <c r="S333" s="4" t="n">
-        <v>7170</v>
+        <v>9214</v>
       </c>
       <c r="T333" s="4" t="n">
-        <v>3857</v>
+        <v>5654</v>
       </c>
       <c r="U333" s="4" t="n">
-        <v>3903</v>
+        <v>5307</v>
       </c>
       <c r="V333" s="4" t="inlineStr">
         <is>
-          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W333" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
         </is>
       </c>
       <c r="X333" s="4" t="n">
-        <v>2.018</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="334">
@@ -16943,12 +16855,12 @@
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
-          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+          <t>EVOWHEY &amp; OATS</t>
         </is>
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
@@ -16957,66 +16869,66 @@
         </is>
       </c>
       <c r="E334" s="6" t="n">
-        <v>42.84</v>
+        <v>10.02</v>
       </c>
       <c r="F334" s="6" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G334" s="6" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="H334" s="6" t="n">
-        <v>85.68000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>20/04/2028</t>
+          <t>21/04/2028</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr"/>
       <c r="K334" s="6" t="inlineStr"/>
       <c r="L334" s="6" t="n">
-        <v>120.68</v>
+        <v>36.98</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>3.62</v>
+        <v>1.109</v>
       </c>
       <c r="N334" s="6" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="O334" s="6" t="n">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="P334" s="6" t="n">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="Q334" s="6" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="R334" s="6" t="n">
-        <v>3.3</v>
+        <v>0.76</v>
       </c>
       <c r="S334" s="6" t="n">
-        <v>6681</v>
+        <v>4577</v>
       </c>
       <c r="T334" s="6" t="n">
-        <v>3385</v>
+        <v>2682</v>
       </c>
       <c r="U334" s="6" t="n">
-        <v>4543</v>
+        <v>2571</v>
       </c>
       <c r="V334" s="6" t="inlineStr">
         <is>
-          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
         </is>
       </c>
       <c r="W334" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
         </is>
       </c>
       <c r="X334" s="6" t="n">
-        <v>3.847</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="335">
@@ -17027,80 +16939,76 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+          <t>EVOWHEY &amp; OATS</t>
         </is>
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>44.2</v>
+        <v>24.95</v>
       </c>
       <c r="F335" s="4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G335" s="4" t="n">
-        <v>1.34</v>
+        <v>0.79</v>
       </c>
       <c r="H335" s="4" t="n">
-        <v>88.42</v>
-      </c>
-      <c r="I335" s="4" t="inlineStr">
-        <is>
-          <t>20/04/2028</t>
-        </is>
-      </c>
+        <v>15.72</v>
+      </c>
+      <c r="I335" s="4" t="n"/>
       <c r="J335" s="4" t="inlineStr"/>
       <c r="K335" s="4" t="inlineStr"/>
       <c r="L335" s="4" t="n">
-        <v>106.53</v>
+        <v>36.56</v>
       </c>
       <c r="M335" s="4" t="n">
-        <v>3.196</v>
+        <v>1.097</v>
       </c>
       <c r="N335" s="4" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="O335" s="4" t="n">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="P335" s="4" t="n">
-        <v>0.5</v>
+        <v>38</v>
       </c>
       <c r="Q335" s="4" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="R335" s="4" t="n">
-        <v>3.8</v>
+        <v>0.76</v>
       </c>
       <c r="S335" s="4" t="n">
-        <v>7812</v>
+        <v>4577</v>
       </c>
       <c r="T335" s="4" t="n">
-        <v>3958</v>
+        <v>2682</v>
       </c>
       <c r="U335" s="4" t="n">
-        <v>5312</v>
+        <v>2571</v>
       </c>
       <c r="V335" s="4" t="inlineStr">
         <is>
-          <t>Caséine hydrolysée (lait).</t>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
         </is>
       </c>
       <c r="W335" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
         </is>
       </c>
       <c r="X335" s="4" t="n">
-        <v>3.396</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="336">
@@ -17111,12 +17019,12 @@
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+          <t>EVOHYDRO 30HD</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
@@ -17125,66 +17033,66 @@
         </is>
       </c>
       <c r="E336" s="6" t="n">
-        <v>20.74</v>
+        <v>24.11</v>
       </c>
       <c r="F336" s="6" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G336" s="6" t="n">
-        <v>1.22</v>
+        <v>0.73</v>
       </c>
       <c r="H336" s="6" t="n">
-        <v>41.48</v>
+        <v>48.22</v>
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>28/11/2027</t>
+          <t>13/02/2028</t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr"/>
       <c r="K336" s="6" t="inlineStr"/>
       <c r="L336" s="6" t="n">
-        <v>45.09</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="M336" s="6" t="n">
-        <v>1.353</v>
+        <v>2.225</v>
       </c>
       <c r="N336" s="6" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="O336" s="6" t="n">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="P336" s="6" t="n">
-        <v>0.2</v>
+        <v>6.6</v>
       </c>
       <c r="Q336" s="6" t="n">
-        <v>1.1</v>
+        <v>7.9</v>
       </c>
       <c r="R336" s="6" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="S336" s="6" t="n">
-        <v>10580</v>
+        <v>7170</v>
       </c>
       <c r="T336" s="6" t="n">
-        <v>6532</v>
+        <v>3857</v>
       </c>
       <c r="U336" s="6" t="n">
-        <v>5796</v>
+        <v>3903</v>
       </c>
       <c r="V336" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
         </is>
       </c>
       <c r="W336" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
         </is>
       </c>
       <c r="X336" s="6" t="n">
-        <v>1.176</v>
+        <v>2.018</v>
       </c>
     </row>
     <row r="337">
@@ -17195,80 +17103,80 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
         </is>
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>42.84</v>
       </c>
       <c r="F337" s="4" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G337" s="4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H337" s="4" t="n">
-        <v>35.55</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="I337" s="4" t="inlineStr">
         <is>
-          <t>31/10/2027</t>
+          <t>20/04/2028</t>
         </is>
       </c>
       <c r="J337" s="4" t="inlineStr"/>
       <c r="K337" s="4" t="inlineStr"/>
       <c r="L337" s="4" t="n">
-        <v>38.64</v>
+        <v>120.68</v>
       </c>
       <c r="M337" s="4" t="n">
-        <v>1.159</v>
+        <v>3.62</v>
       </c>
       <c r="N337" s="4" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="O337" s="4" t="n">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="P337" s="4" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q337" s="4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="R337" s="4" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="S337" s="4" t="n">
-        <v>10580</v>
+        <v>6681</v>
       </c>
       <c r="T337" s="4" t="n">
-        <v>6532</v>
+        <v>3385</v>
       </c>
       <c r="U337" s="4" t="n">
-        <v>5796</v>
+        <v>4543</v>
       </c>
       <c r="V337" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
         </is>
       </c>
       <c r="W337" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
         </is>
       </c>
       <c r="X337" s="4" t="n">
-        <v>1.008</v>
+        <v>3.847</v>
       </c>
     </row>
     <row r="338">
@@ -17279,12 +17187,12 @@
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>GOLDEN PROTEIN</t>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
@@ -17293,66 +17201,66 @@
         </is>
       </c>
       <c r="E338" s="6" t="n">
-        <v>15.5</v>
+        <v>44.2</v>
       </c>
       <c r="F338" s="6" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G338" s="6" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="H338" s="6" t="n">
-        <v>31</v>
+        <v>88.42</v>
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>13/02/2028</t>
+          <t>20/04/2028</t>
         </is>
       </c>
       <c r="J338" s="6" t="inlineStr"/>
       <c r="K338" s="6" t="inlineStr"/>
       <c r="L338" s="6" t="n">
-        <v>58.49</v>
+        <v>106.53</v>
       </c>
       <c r="M338" s="6" t="n">
-        <v>1.755</v>
+        <v>3.196</v>
       </c>
       <c r="N338" s="6" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="O338" s="6" t="n">
-        <v>431</v>
+        <v>349</v>
       </c>
       <c r="P338" s="6" t="n">
-        <v>11</v>
+        <v>0.5</v>
       </c>
       <c r="Q338" s="6" t="n">
-        <v>18</v>
+        <v>1.5</v>
       </c>
       <c r="R338" s="6" t="n">
-        <v>0.79</v>
+        <v>3.8</v>
       </c>
       <c r="S338" s="6" t="n">
-        <v>5893</v>
+        <v>7812</v>
       </c>
       <c r="T338" s="6" t="n">
-        <v>3463</v>
+        <v>3958</v>
       </c>
       <c r="U338" s="6" t="n">
-        <v>3205</v>
+        <v>5312</v>
       </c>
       <c r="V338" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+          <t>Caséine hydrolysée (lait).</t>
         </is>
       </c>
       <c r="W338" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
         </is>
       </c>
       <c r="X338" s="6" t="n">
-        <v>1.578</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="339">
@@ -17363,80 +17271,80 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>GOLDEN PROTEIN</t>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E339" s="4" t="n">
-        <v>53.32</v>
+        <v>20.74</v>
       </c>
       <c r="F339" s="4" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G339" s="4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="H339" s="4" t="n">
-        <v>26.66</v>
+        <v>41.48</v>
       </c>
       <c r="I339" s="4" t="inlineStr">
         <is>
-          <t>13/02/2028</t>
+          <t>28/11/2027</t>
         </is>
       </c>
       <c r="J339" s="4" t="inlineStr"/>
       <c r="K339" s="4" t="inlineStr"/>
       <c r="L339" s="4" t="n">
-        <v>50.3</v>
+        <v>45.09</v>
       </c>
       <c r="M339" s="4" t="n">
-        <v>1.509</v>
+        <v>1.353</v>
       </c>
       <c r="N339" s="4" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="O339" s="4" t="n">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="P339" s="4" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Q339" s="4" t="n">
-        <v>18</v>
+        <v>1.1</v>
       </c>
       <c r="R339" s="4" t="n">
-        <v>0.79</v>
+        <v>1.3</v>
       </c>
       <c r="S339" s="4" t="n">
-        <v>5893</v>
+        <v>10580</v>
       </c>
       <c r="T339" s="4" t="n">
-        <v>3463</v>
+        <v>6532</v>
       </c>
       <c r="U339" s="4" t="n">
-        <v>3205</v>
+        <v>5796</v>
       </c>
       <c r="V339" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
         </is>
       </c>
       <c r="W339" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
         </is>
       </c>
       <c r="X339" s="4" t="n">
-        <v>1.357</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="340">
@@ -17447,80 +17355,80 @@
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E340" s="6" t="n">
-        <v>18.41</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F340" s="6" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G340" s="6" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="H340" s="6" t="n">
-        <v>36.82</v>
+        <v>35.55</v>
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>17/11/2027</t>
+          <t>31/10/2027</t>
         </is>
       </c>
       <c r="J340" s="6" t="inlineStr"/>
       <c r="K340" s="6" t="inlineStr"/>
       <c r="L340" s="6" t="n">
-        <v>54.15</v>
+        <v>38.64</v>
       </c>
       <c r="M340" s="6" t="n">
-        <v>1.624</v>
+        <v>1.159</v>
       </c>
       <c r="N340" s="6" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="O340" s="6" t="n">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="P340" s="6" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Q340" s="6" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="R340" s="6" t="n">
-        <v>0.84</v>
+        <v>1.3</v>
       </c>
       <c r="S340" s="6" t="n">
-        <v>7444</v>
+        <v>10580</v>
       </c>
       <c r="T340" s="6" t="n">
-        <v>4375</v>
+        <v>6532</v>
       </c>
       <c r="U340" s="6" t="n">
-        <v>4048</v>
+        <v>5796</v>
       </c>
       <c r="V340" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
         </is>
       </c>
       <c r="W340" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
         </is>
       </c>
       <c r="X340" s="6" t="n">
-        <v>1.484</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="341">
@@ -17531,65 +17439,81 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+          <t>GOLDEN PROTEIN</t>
         </is>
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>1 boîte (16x35g)</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F341" s="4" t="n"/>
-      <c r="G341" s="4" t="n"/>
-      <c r="H341" s="4" t="n"/>
-      <c r="I341" s="4" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="F341" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G341" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H341" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
       <c r="J341" s="4" t="inlineStr"/>
       <c r="K341" s="4" t="inlineStr"/>
-      <c r="L341" s="4" t="n"/>
-      <c r="M341" s="4" t="n"/>
+      <c r="L341" s="4" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M341" s="4" t="n">
+        <v>1.755</v>
+      </c>
       <c r="N341" s="4" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O341" s="4" t="n">
-        <v>366</v>
+        <v>431</v>
       </c>
       <c r="P341" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q341" s="4" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="R341" s="4" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="S341" s="4" t="n">
-        <v>7444</v>
+        <v>5893</v>
       </c>
       <c r="T341" s="4" t="n">
-        <v>4375</v>
+        <v>3463</v>
       </c>
       <c r="U341" s="4" t="n">
-        <v>4048</v>
+        <v>3205</v>
       </c>
       <c r="V341" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
         </is>
       </c>
       <c r="W341" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
-        </is>
-      </c>
-      <c r="X341" s="4" t="n"/>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X341" s="4" t="n">
+        <v>1.578</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -17599,76 +17523,80 @@
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+          <t>GOLDEN PROTEIN</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E342" s="6" t="n">
-        <v>21.13</v>
+        <v>53.32</v>
       </c>
       <c r="F342" s="6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G342" s="6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H342" s="6" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="I342" s="6" t="n"/>
+        <v>26.66</v>
+      </c>
+      <c r="I342" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
       <c r="J342" s="6" t="inlineStr"/>
       <c r="K342" s="6" t="inlineStr"/>
       <c r="L342" s="6" t="n">
-        <v>48.57</v>
+        <v>50.3</v>
       </c>
       <c r="M342" s="6" t="n">
-        <v>1.457</v>
+        <v>1.509</v>
       </c>
       <c r="N342" s="6" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="O342" s="6" t="n">
-        <v>358</v>
+        <v>431</v>
       </c>
       <c r="P342" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q342" s="6" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="R342" s="6" t="n">
-        <v>0.08</v>
+        <v>0.79</v>
       </c>
       <c r="S342" s="6" t="n">
-        <v>9262</v>
+        <v>5893</v>
       </c>
       <c r="T342" s="6" t="n">
-        <v>5773</v>
+        <v>3463</v>
       </c>
       <c r="U342" s="6" t="n">
-        <v>4940</v>
+        <v>3205</v>
       </c>
       <c r="V342" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
         </is>
       </c>
       <c r="W342" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
         </is>
       </c>
       <c r="X342" s="6" t="n">
-        <v>1.369</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="343">
@@ -17679,80 +17607,72 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
         </is>
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>1Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="F343" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="G343" s="4" t="n">
-        <v>0.93</v>
-      </c>
+        <v>18.41</v>
+      </c>
+      <c r="F343" s="4" t="n"/>
+      <c r="G343" s="4" t="n"/>
       <c r="H343" s="4" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="I343" s="4" t="inlineStr">
-        <is>
-          <t>31/10/2026</t>
-        </is>
-      </c>
+        <v>36.82</v>
+      </c>
+      <c r="I343" s="4" t="inlineStr"/>
       <c r="J343" s="4" t="inlineStr"/>
       <c r="K343" s="4" t="inlineStr"/>
       <c r="L343" s="4" t="n">
-        <v>42.93</v>
+        <v>54.15</v>
       </c>
       <c r="M343" s="4" t="n">
-        <v>1.288</v>
+        <v>1.624</v>
       </c>
       <c r="N343" s="4" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="O343" s="4" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P343" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q343" s="4" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="R343" s="4" t="n">
-        <v>0.08</v>
+        <v>0.84</v>
       </c>
       <c r="S343" s="4" t="n">
-        <v>9262</v>
+        <v>7444</v>
       </c>
       <c r="T343" s="4" t="n">
-        <v>5773</v>
+        <v>4375</v>
       </c>
       <c r="U343" s="4" t="n">
-        <v>4940</v>
+        <v>4048</v>
       </c>
       <c r="V343" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
         </is>
       </c>
       <c r="W343" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
         </is>
       </c>
       <c r="X343" s="4" t="n">
-        <v>1.21</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="344">
@@ -17763,12 +17683,12 @@
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
@@ -17777,66 +17697,62 @@
         </is>
       </c>
       <c r="E344" s="6" t="n">
-        <v>18.41</v>
+        <v>21.13</v>
       </c>
       <c r="F344" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G344" s="6" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="H344" s="6" t="n">
-        <v>36.82</v>
-      </c>
-      <c r="I344" s="6" t="inlineStr">
-        <is>
-          <t>13/11/2027</t>
-        </is>
-      </c>
+        <v>42.26</v>
+      </c>
+      <c r="I344" s="6" t="n"/>
       <c r="J344" s="6" t="inlineStr"/>
       <c r="K344" s="6" t="inlineStr"/>
       <c r="L344" s="6" t="n">
-        <v>61.37</v>
+        <v>48.57</v>
       </c>
       <c r="M344" s="6" t="n">
-        <v>1.841</v>
+        <v>1.457</v>
       </c>
       <c r="N344" s="6" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="O344" s="6" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="P344" s="6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q344" s="6" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="R344" s="6" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="S344" s="6" t="n">
-        <v>6252</v>
+        <v>9262</v>
       </c>
       <c r="T344" s="6" t="n">
-        <v>3565</v>
+        <v>5773</v>
       </c>
       <c r="U344" s="6" t="n">
-        <v>3291</v>
+        <v>4940</v>
       </c>
       <c r="V344" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
         </is>
       </c>
       <c r="W344" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
         </is>
       </c>
       <c r="X344" s="6" t="n">
-        <v>1.767</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="345">
@@ -17847,65 +17763,81 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
         </is>
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>1 boîte (16x35g)</t>
+          <t>1Kg</t>
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="F345" s="4" t="n"/>
-      <c r="G345" s="4" t="n"/>
-      <c r="H345" s="4" t="n"/>
-      <c r="I345" s="4" t="inlineStr"/>
+        <v>37.35</v>
+      </c>
+      <c r="F345" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G345" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H345" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
       <c r="J345" s="4" t="inlineStr"/>
       <c r="K345" s="4" t="inlineStr"/>
-      <c r="L345" s="4" t="n"/>
-      <c r="M345" s="4" t="n"/>
+      <c r="L345" s="4" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M345" s="4" t="n">
+        <v>1.288</v>
+      </c>
       <c r="N345" s="4" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="O345" s="4" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="P345" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q345" s="4" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="R345" s="4" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="S345" s="4" t="n">
-        <v>6252</v>
+        <v>9262</v>
       </c>
       <c r="T345" s="4" t="n">
-        <v>3565</v>
+        <v>5773</v>
       </c>
       <c r="U345" s="4" t="n">
-        <v>3291</v>
+        <v>4940</v>
       </c>
       <c r="V345" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
         </is>
       </c>
       <c r="W345" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
-        </is>
-      </c>
-      <c r="X345" s="4" t="n"/>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X345" s="4" t="n">
+        <v>1.21</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -17915,12 +17847,12 @@
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>100% WHEY PROTEIN CONCENTRATE</t>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
         </is>
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
@@ -17929,66 +17861,66 @@
         </is>
       </c>
       <c r="E346" s="6" t="n">
-        <v>11.28</v>
+        <v>18.41</v>
       </c>
       <c r="F346" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G346" s="6" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
       <c r="H346" s="6" t="n">
-        <v>22.56</v>
+        <v>36.82</v>
       </c>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>30/03/2028</t>
+          <t>13/11/2027</t>
         </is>
       </c>
       <c r="J346" s="6" t="inlineStr"/>
       <c r="K346" s="6" t="inlineStr"/>
       <c r="L346" s="6" t="n">
-        <v>27.51</v>
+        <v>61.37</v>
       </c>
       <c r="M346" s="6" t="n">
-        <v>0.825</v>
+        <v>1.841</v>
       </c>
       <c r="N346" s="6" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="O346" s="6" t="n">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="P346" s="6" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="Q346" s="6" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="R346" s="6" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="S346" s="6" t="n">
-        <v>9312</v>
+        <v>6252</v>
       </c>
       <c r="T346" s="6" t="n">
-        <v>5473</v>
+        <v>3565</v>
       </c>
       <c r="U346" s="6" t="n">
-        <v>5064</v>
+        <v>3291</v>
       </c>
       <c r="V346" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W346" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
         </is>
       </c>
       <c r="X346" s="6" t="n">
-        <v>0.727</v>
+        <v>1.767</v>
       </c>
     </row>
     <row r="347">
@@ -17999,81 +17931,65 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>100% WHEY PROTEIN CONCENTRATE</t>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
         </is>
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>1 boîte (16x35g)</t>
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>40.27</v>
-      </c>
-      <c r="F347" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G347" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H347" s="4" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="I347" s="4" t="inlineStr">
-        <is>
-          <t>14/11/2027</t>
-        </is>
-      </c>
+        <v>2.15</v>
+      </c>
+      <c r="F347" s="4" t="n"/>
+      <c r="G347" s="4" t="n"/>
+      <c r="H347" s="4" t="n"/>
+      <c r="I347" s="4" t="inlineStr"/>
       <c r="J347" s="4" t="inlineStr"/>
       <c r="K347" s="4" t="inlineStr"/>
-      <c r="L347" s="4" t="n">
-        <v>24.56</v>
-      </c>
-      <c r="M347" s="4" t="n">
-        <v>0.737</v>
-      </c>
+      <c r="L347" s="4" t="n"/>
+      <c r="M347" s="4" t="n"/>
       <c r="N347" s="4" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="O347" s="4" t="n">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="P347" s="4" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="Q347" s="4" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="R347" s="4" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="S347" s="4" t="n">
-        <v>9312</v>
+        <v>6252</v>
       </c>
       <c r="T347" s="4" t="n">
-        <v>5473</v>
+        <v>3565</v>
       </c>
       <c r="U347" s="4" t="n">
-        <v>5064</v>
+        <v>3291</v>
       </c>
       <c r="V347" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W347" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
-        </is>
-      </c>
-      <c r="X347" s="4" t="n">
-        <v>0.649</v>
-      </c>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -18083,72 +17999,80 @@
       </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
-          <t>EVONATURAL WHEY</t>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
         </is>
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E348" s="6" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="F348" s="6" t="n"/>
-      <c r="G348" s="6" t="n"/>
+        <v>11.28</v>
+      </c>
+      <c r="F348" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G348" s="6" t="n">
+        <v>0.66</v>
+      </c>
       <c r="H348" s="6" t="n">
-        <v>22.02</v>
-      </c>
-      <c r="I348" s="6" t="inlineStr"/>
+        <v>22.56</v>
+      </c>
+      <c r="I348" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
       <c r="J348" s="6" t="inlineStr"/>
       <c r="K348" s="6" t="inlineStr"/>
       <c r="L348" s="6" t="n">
-        <v>28.97</v>
+        <v>27.51</v>
       </c>
       <c r="M348" s="6" t="n">
-        <v>0.869</v>
+        <v>0.825</v>
       </c>
       <c r="N348" s="6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O348" s="6" t="n">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="P348" s="6" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q348" s="6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="R348" s="6" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="S348" s="6" t="n">
-        <v>8167</v>
+        <v>9312</v>
       </c>
       <c r="T348" s="6" t="n">
-        <v>4656</v>
+        <v>5473</v>
       </c>
       <c r="U348" s="6" t="n">
-        <v>4351</v>
+        <v>5064</v>
       </c>
       <c r="V348" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W348" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
         </is>
       </c>
       <c r="X348" s="6" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="349">
@@ -18159,72 +18083,80 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>EVONATURAL WHEY</t>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
         </is>
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E349" s="4" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="F349" s="4" t="n"/>
-      <c r="G349" s="4" t="n"/>
+        <v>40.27</v>
+      </c>
+      <c r="F349" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G349" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="H349" s="4" t="n">
-        <v>25.08</v>
-      </c>
-      <c r="I349" s="4" t="inlineStr"/>
+        <v>20.14</v>
+      </c>
+      <c r="I349" s="4" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
       <c r="J349" s="4" t="inlineStr"/>
       <c r="K349" s="4" t="inlineStr"/>
       <c r="L349" s="4" t="n">
-        <v>33</v>
+        <v>24.56</v>
       </c>
       <c r="M349" s="4" t="n">
-        <v>0.99</v>
+        <v>0.737</v>
       </c>
       <c r="N349" s="4" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O349" s="4" t="n">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="P349" s="4" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q349" s="4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="R349" s="4" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
       <c r="S349" s="4" t="n">
-        <v>8167</v>
+        <v>9312</v>
       </c>
       <c r="T349" s="4" t="n">
-        <v>4656</v>
+        <v>5473</v>
       </c>
       <c r="U349" s="4" t="n">
-        <v>4351</v>
+        <v>5064</v>
       </c>
       <c r="V349" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W349" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
         </is>
       </c>
       <c r="X349" s="4" t="n">
-        <v>0.921</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="350">
@@ -18235,12 +18167,12 @@
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>EVONATIVE WHEY</t>
+          <t>EVONATURAL WHEY</t>
         </is>
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
@@ -18249,58 +18181,58 @@
         </is>
       </c>
       <c r="E350" s="6" t="n">
-        <v>38.61</v>
+        <v>44.03</v>
       </c>
       <c r="F350" s="6" t="n"/>
       <c r="G350" s="6" t="n"/>
       <c r="H350" s="6" t="n">
-        <v>19.3</v>
+        <v>22.02</v>
       </c>
       <c r="I350" s="6" t="inlineStr"/>
       <c r="J350" s="6" t="inlineStr"/>
       <c r="K350" s="6" t="inlineStr"/>
       <c r="L350" s="6" t="n">
-        <v>24.74</v>
+        <v>28.97</v>
       </c>
       <c r="M350" s="6" t="n">
-        <v>0.742</v>
+        <v>0.869</v>
       </c>
       <c r="N350" s="6" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O350" s="6" t="n">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="P350" s="6" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="Q350" s="6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="R350" s="6" t="n">
-        <v>2.3</v>
+        <v>0.77</v>
       </c>
       <c r="S350" s="6" t="n">
-        <v>10068</v>
+        <v>8167</v>
       </c>
       <c r="T350" s="6" t="n">
-        <v>4449</v>
+        <v>4656</v>
       </c>
       <c r="U350" s="6" t="n">
-        <v>4137</v>
+        <v>4351</v>
       </c>
       <c r="V350" s="6" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
         </is>
       </c>
       <c r="W350" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
         </is>
       </c>
       <c r="X350" s="6" t="n">
-        <v>0.575</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="351">
@@ -18311,12 +18243,12 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>EVONATIVE WHEY</t>
+          <t>EVONATURAL WHEY</t>
         </is>
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -18325,58 +18257,58 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>12.63</v>
+        <v>12.54</v>
       </c>
       <c r="F351" s="4" t="n"/>
       <c r="G351" s="4" t="n"/>
       <c r="H351" s="4" t="n">
-        <v>25.26</v>
+        <v>25.08</v>
       </c>
       <c r="I351" s="4" t="inlineStr"/>
       <c r="J351" s="4" t="inlineStr"/>
       <c r="K351" s="4" t="inlineStr"/>
       <c r="L351" s="4" t="n">
-        <v>32.38</v>
+        <v>33</v>
       </c>
       <c r="M351" s="4" t="n">
-        <v>0.971</v>
+        <v>0.99</v>
       </c>
       <c r="N351" s="4" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O351" s="4" t="n">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="P351" s="4" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="Q351" s="4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="R351" s="4" t="n">
-        <v>2.3</v>
+        <v>0.77</v>
       </c>
       <c r="S351" s="4" t="n">
-        <v>10068</v>
+        <v>8167</v>
       </c>
       <c r="T351" s="4" t="n">
-        <v>4449</v>
+        <v>4656</v>
       </c>
       <c r="U351" s="4" t="n">
-        <v>4137</v>
+        <v>4351</v>
       </c>
       <c r="V351" s="4" t="inlineStr">
         <is>
-          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
         </is>
       </c>
       <c r="W351" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
         </is>
       </c>
       <c r="X351" s="4" t="n">
-        <v>0.753</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="352">
@@ -18387,72 +18319,80 @@
       </c>
       <c r="B352" s="5" t="inlineStr">
         <is>
-          <t>NATIVE WHEY CONCENTRATE</t>
+          <t>EVONATIVE WHEY</t>
         </is>
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E352" s="6" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="F352" s="6" t="n"/>
-      <c r="G352" s="6" t="n"/>
+        <v>12.63</v>
+      </c>
+      <c r="F352" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G352" s="6" t="n">
+        <v>1.02</v>
+      </c>
       <c r="H352" s="6" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="I352" s="6" t="inlineStr"/>
+        <v>34.6</v>
+      </c>
+      <c r="I352" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
       <c r="J352" s="6" t="inlineStr"/>
       <c r="K352" s="6" t="inlineStr"/>
       <c r="L352" s="6" t="n">
-        <v>24.21</v>
+        <v>44.36</v>
       </c>
       <c r="M352" s="6" t="n">
-        <v>0.726</v>
+        <v>1.331</v>
       </c>
       <c r="N352" s="6" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O352" s="6" t="n">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="P352" s="6" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q352" s="6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="R352" s="6" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="S352" s="6" t="n">
-        <v>10449</v>
+        <v>10068</v>
       </c>
       <c r="T352" s="6" t="n">
-        <v>4617</v>
+        <v>4449</v>
       </c>
       <c r="U352" s="6" t="n">
-        <v>4293</v>
+        <v>4137</v>
       </c>
       <c r="V352" s="6" t="inlineStr">
         <is>
-          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
         </is>
       </c>
       <c r="W352" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
         </is>
       </c>
       <c r="X352" s="6" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="353">
@@ -18463,72 +18403,80 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>NATIVE WHEY CONCENTRATE</t>
+          <t>EVONATIVE WHEY</t>
         </is>
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="F353" s="4" t="n"/>
-      <c r="G353" s="4" t="n"/>
+        <v>38.61</v>
+      </c>
+      <c r="F353" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G353" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="H353" s="4" t="n">
-        <v>23.56</v>
-      </c>
-      <c r="I353" s="4" t="inlineStr"/>
+        <v>34.6</v>
+      </c>
+      <c r="I353" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
       <c r="J353" s="4" t="inlineStr"/>
       <c r="K353" s="4" t="inlineStr"/>
       <c r="L353" s="4" t="n">
-        <v>29.09</v>
+        <v>44.36</v>
       </c>
       <c r="M353" s="4" t="n">
-        <v>0.873</v>
+        <v>1.331</v>
       </c>
       <c r="N353" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O353" s="4" t="n">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="P353" s="4" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="Q353" s="4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="R353" s="4" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="S353" s="4" t="n">
-        <v>10449</v>
+        <v>10068</v>
       </c>
       <c r="T353" s="4" t="n">
-        <v>4617</v>
+        <v>4449</v>
       </c>
       <c r="U353" s="4" t="n">
-        <v>4293</v>
+        <v>4137</v>
       </c>
       <c r="V353" s="4" t="inlineStr">
         <is>
-          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
         </is>
       </c>
       <c r="W353" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
         </is>
       </c>
       <c r="X353" s="4" t="n">
-        <v>0.676</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="354">
@@ -18539,12 +18487,12 @@
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+          <t>NATIVE WHEY CONCENTRATE</t>
         </is>
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
@@ -18553,47 +18501,59 @@
         </is>
       </c>
       <c r="E354" s="6" t="n">
-        <v>43.34</v>
+        <v>39.21</v>
       </c>
       <c r="F354" s="6" t="n"/>
       <c r="G354" s="6" t="n"/>
       <c r="H354" s="6" t="n">
-        <v>21.67</v>
+        <v>19.61</v>
       </c>
       <c r="I354" s="6" t="inlineStr"/>
       <c r="J354" s="6" t="inlineStr"/>
       <c r="K354" s="6" t="inlineStr"/>
       <c r="L354" s="6" t="n">
-        <v>47.11</v>
+        <v>24.21</v>
       </c>
       <c r="M354" s="6" t="n">
-        <v>1.413</v>
+        <v>0.726</v>
       </c>
       <c r="N354" s="6" t="n">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="O354" s="6" t="n">
-        <v>304</v>
+        <v>404</v>
       </c>
       <c r="P354" s="6" t="n">
-        <v>28</v>
+        <v>6.5</v>
       </c>
       <c r="Q354" s="6" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="R354" s="6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S354" s="6" t="n"/>
-      <c r="T354" s="6" t="n"/>
-      <c r="U354" s="6" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="S354" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T354" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U354" s="6" t="n">
+        <v>4293</v>
+      </c>
       <c r="V354" s="6" t="inlineStr">
         <is>
-          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
-        </is>
-      </c>
-      <c r="W354" s="6" t="inlineStr"/>
-      <c r="X354" s="6" t="n"/>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W354" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X354" s="6" t="n">
+        <v>0.5629999999999999</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -18603,12 +18563,12 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+          <t>NATIVE WHEY CONCENTRATE</t>
         </is>
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -18617,47 +18577,59 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>11.72</v>
+        <v>11.78</v>
       </c>
       <c r="F355" s="4" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n">
-        <v>23.44</v>
+        <v>23.56</v>
       </c>
       <c r="I355" s="4" t="inlineStr"/>
       <c r="J355" s="4" t="inlineStr"/>
       <c r="K355" s="4" t="inlineStr"/>
       <c r="L355" s="4" t="n">
-        <v>50.96</v>
+        <v>29.09</v>
       </c>
       <c r="M355" s="4" t="n">
-        <v>1.529</v>
+        <v>0.873</v>
       </c>
       <c r="N355" s="4" t="n">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="O355" s="4" t="n">
-        <v>304</v>
+        <v>404</v>
       </c>
       <c r="P355" s="4" t="n">
-        <v>28</v>
+        <v>6.5</v>
       </c>
       <c r="Q355" s="4" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="R355" s="4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S355" s="4" t="n"/>
-      <c r="T355" s="4" t="n"/>
-      <c r="U355" s="4" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="S355" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T355" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U355" s="4" t="n">
+        <v>4293</v>
+      </c>
       <c r="V355" s="4" t="inlineStr">
         <is>
-          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
-        </is>
-      </c>
-      <c r="W355" s="4" t="inlineStr"/>
-      <c r="X355" s="4" t="n"/>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W355" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X355" s="4" t="n">
+        <v>0.676</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -18667,81 +18639,61 @@
       </c>
       <c r="B356" s="5" t="inlineStr">
         <is>
-          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
         </is>
       </c>
       <c r="C356" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>500g</t>
+          <t>2Kg</t>
         </is>
       </c>
       <c r="E356" s="6" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="F356" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G356" s="6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>43.34</v>
+      </c>
+      <c r="F356" s="6" t="n"/>
+      <c r="G356" s="6" t="n"/>
       <c r="H356" s="6" t="n">
-        <v>27.68</v>
-      </c>
-      <c r="I356" s="6" t="inlineStr">
-        <is>
-          <t>17/02/2028</t>
-        </is>
-      </c>
+        <v>21.67</v>
+      </c>
+      <c r="I356" s="6" t="inlineStr"/>
       <c r="J356" s="6" t="inlineStr"/>
       <c r="K356" s="6" t="inlineStr"/>
       <c r="L356" s="6" t="n">
-        <v>33.35</v>
+        <v>47.11</v>
       </c>
       <c r="M356" s="6" t="n">
-        <v>1</v>
+        <v>1.413</v>
       </c>
       <c r="N356" s="6" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="O356" s="6" t="n">
-        <v>373</v>
+        <v>304</v>
       </c>
       <c r="P356" s="6" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="Q356" s="6" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="R356" s="6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S356" s="6" t="n">
-        <v>7926</v>
-      </c>
-      <c r="T356" s="6" t="n">
-        <v>4211</v>
-      </c>
-      <c r="U356" s="6" t="n">
-        <v>5449</v>
-      </c>
+        <v>0.36</v>
+      </c>
+      <c r="S356" s="6" t="n"/>
+      <c r="T356" s="6" t="n"/>
+      <c r="U356" s="6" t="n"/>
       <c r="V356" s="6" t="inlineStr">
         <is>
-          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
-        </is>
-      </c>
-      <c r="W356" s="6" t="inlineStr">
-        <is>
-          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
-        </is>
-      </c>
-      <c r="X356" s="6" t="n">
-        <v>1.048</v>
-      </c>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W356" s="6" t="inlineStr"/>
+      <c r="X356" s="6" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -18751,81 +18703,61 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
         </is>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
+          <t>500g</t>
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="F357" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G357" s="4" t="n">
-        <v>0.72</v>
-      </c>
+        <v>11.72</v>
+      </c>
+      <c r="F357" s="4" t="n"/>
+      <c r="G357" s="4" t="n"/>
       <c r="H357" s="4" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="I357" s="4" t="inlineStr">
-        <is>
-          <t>23/02/2028</t>
-        </is>
-      </c>
+        <v>23.44</v>
+      </c>
+      <c r="I357" s="4" t="inlineStr"/>
       <c r="J357" s="4" t="inlineStr"/>
       <c r="K357" s="4" t="inlineStr"/>
       <c r="L357" s="4" t="n">
-        <v>29.08</v>
+        <v>50.96</v>
       </c>
       <c r="M357" s="4" t="n">
-        <v>0.872</v>
+        <v>1.529</v>
       </c>
       <c r="N357" s="4" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="O357" s="4" t="n">
-        <v>373</v>
+        <v>304</v>
       </c>
       <c r="P357" s="4" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="Q357" s="4" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="R357" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S357" s="4" t="n">
-        <v>7926</v>
-      </c>
-      <c r="T357" s="4" t="n">
-        <v>4211</v>
-      </c>
-      <c r="U357" s="4" t="n">
-        <v>5449</v>
-      </c>
+        <v>0.36</v>
+      </c>
+      <c r="S357" s="4" t="n"/>
+      <c r="T357" s="4" t="n"/>
+      <c r="U357" s="4" t="n"/>
       <c r="V357" s="4" t="inlineStr">
         <is>
-          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
-        </is>
-      </c>
-      <c r="W357" s="4" t="inlineStr">
-        <is>
-          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
-        </is>
-      </c>
-      <c r="X357" s="4" t="n">
-        <v>0.914</v>
-      </c>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W357" s="4" t="inlineStr"/>
+      <c r="X357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -18835,12 +18767,12 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
         </is>
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
@@ -18849,66 +18781,66 @@
         </is>
       </c>
       <c r="E358" s="6" t="n">
-        <v>15.33</v>
+        <v>13.84</v>
       </c>
       <c r="F358" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G358" s="6" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H358" s="6" t="n">
-        <v>30.66</v>
+        <v>27.68</v>
       </c>
       <c r="I358" s="6" t="inlineStr">
         <is>
-          <t>23/01/2028</t>
+          <t>17/02/2028</t>
         </is>
       </c>
       <c r="J358" s="6" t="inlineStr"/>
       <c r="K358" s="6" t="inlineStr"/>
       <c r="L358" s="6" t="n">
-        <v>35.24</v>
+        <v>33.35</v>
       </c>
       <c r="M358" s="6" t="n">
-        <v>1.057</v>
+        <v>1</v>
       </c>
       <c r="N358" s="6" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O358" s="6" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="P358" s="6" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q358" s="6" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="R358" s="6" t="n">
-        <v>0.98</v>
+        <v>0.64</v>
       </c>
       <c r="S358" s="6" t="n">
-        <v>9089</v>
+        <v>7926</v>
       </c>
       <c r="T358" s="6" t="n">
-        <v>5406</v>
+        <v>4211</v>
       </c>
       <c r="U358" s="6" t="n">
-        <v>5683</v>
+        <v>5449</v>
       </c>
       <c r="V358" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W358" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
         </is>
       </c>
       <c r="X358" s="6" t="n">
-        <v>1.012</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="359">
@@ -18919,12 +18851,12 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -18933,66 +18865,66 @@
         </is>
       </c>
       <c r="E359" s="4" t="n">
-        <v>53.13</v>
+        <v>48.28</v>
       </c>
       <c r="F359" s="4" t="n">
         <v>67</v>
       </c>
       <c r="G359" s="4" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H359" s="4" t="n">
-        <v>26.57</v>
+        <v>24.14</v>
       </c>
       <c r="I359" s="4" t="inlineStr">
         <is>
-          <t>08/09/2027</t>
+          <t>23/02/2028</t>
         </is>
       </c>
       <c r="J359" s="4" t="inlineStr"/>
       <c r="K359" s="4" t="inlineStr"/>
       <c r="L359" s="4" t="n">
-        <v>30.54</v>
+        <v>29.08</v>
       </c>
       <c r="M359" s="4" t="n">
-        <v>0.916</v>
+        <v>0.872</v>
       </c>
       <c r="N359" s="4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O359" s="4" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="P359" s="4" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q359" s="4" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="R359" s="4" t="n">
-        <v>0.98</v>
+        <v>0.64</v>
       </c>
       <c r="S359" s="4" t="n">
-        <v>9089</v>
+        <v>7926</v>
       </c>
       <c r="T359" s="4" t="n">
-        <v>5406</v>
+        <v>4211</v>
       </c>
       <c r="U359" s="4" t="n">
-        <v>5683</v>
+        <v>5449</v>
       </c>
       <c r="V359" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
         </is>
       </c>
       <c r="W359" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
         </is>
       </c>
       <c r="X359" s="4" t="n">
-        <v>0.877</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="360">
@@ -19003,12 +18935,12 @@
       </c>
       <c r="B360" s="5" t="inlineStr">
         <is>
-          <t>PUDDING PROTÉINÉ 2.0</t>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
         </is>
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
@@ -19016,65 +18948,67 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E360" s="6" t="n"/>
+      <c r="E360" s="6" t="n">
+        <v>15.33</v>
+      </c>
       <c r="F360" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G360" s="6" t="n">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="H360" s="6" t="n">
-        <v>29.36</v>
+        <v>30.66</v>
       </c>
       <c r="I360" s="6" t="inlineStr">
         <is>
-          <t>05/02/2028</t>
+          <t>23/01/2028</t>
         </is>
       </c>
       <c r="J360" s="6" t="inlineStr"/>
       <c r="K360" s="6" t="inlineStr"/>
       <c r="L360" s="6" t="n">
-        <v>41.35</v>
+        <v>35.24</v>
       </c>
       <c r="M360" s="6" t="n">
-        <v>1.24</v>
+        <v>1.057</v>
       </c>
       <c r="N360" s="6" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="O360" s="6" t="n">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="P360" s="6" t="n">
-        <v>7.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q360" s="6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="R360" s="6" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="S360" s="6" t="n">
-        <v>7009</v>
+        <v>9089</v>
       </c>
       <c r="T360" s="6" t="n">
-        <v>3937</v>
+        <v>5406</v>
       </c>
       <c r="U360" s="6" t="n">
-        <v>4581</v>
+        <v>5683</v>
       </c>
       <c r="V360" s="6" t="inlineStr">
         <is>
-          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W360" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
         </is>
       </c>
       <c r="X360" s="6" t="n">
-        <v>1.257</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="361">
@@ -19085,74 +19019,80 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>PUDDING PROTÉINÉ 2.0</t>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
         </is>
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>1Kg</t>
-        </is>
-      </c>
-      <c r="E361" s="4" t="n"/>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="n">
+        <v>53.13</v>
+      </c>
       <c r="F361" s="4" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="G361" s="4" t="n">
         <v>0.79</v>
       </c>
       <c r="H361" s="4" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="I361" s="4" t="n"/>
+        <v>26.57</v>
+      </c>
+      <c r="I361" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
       <c r="J361" s="4" t="inlineStr"/>
       <c r="K361" s="4" t="inlineStr"/>
       <c r="L361" s="4" t="n">
-        <v>27.9</v>
+        <v>30.54</v>
       </c>
       <c r="M361" s="4" t="n">
-        <v>0.837</v>
+        <v>0.916</v>
       </c>
       <c r="N361" s="4" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="O361" s="4" t="n">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="P361" s="4" t="n">
-        <v>7.9</v>
+        <v>1.3</v>
       </c>
       <c r="Q361" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="R361" s="4" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="S361" s="4" t="n">
-        <v>7009</v>
+        <v>9089</v>
       </c>
       <c r="T361" s="4" t="n">
-        <v>3937</v>
+        <v>5406</v>
       </c>
       <c r="U361" s="4" t="n">
-        <v>4581</v>
+        <v>5683</v>
       </c>
       <c r="V361" s="4" t="inlineStr">
         <is>
-          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
         </is>
       </c>
       <c r="W361" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
         </is>
       </c>
       <c r="X361" s="4" t="n">
-        <v>0.848</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="362">
@@ -19163,12 +19103,12 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>EVODIET VEGAN</t>
+          <t>PUDDING PROTÉINÉ 2.0</t>
         </is>
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
@@ -19176,67 +19116,65 @@
           <t>500g</t>
         </is>
       </c>
-      <c r="E362" s="6" t="n">
-        <v>11.42</v>
-      </c>
+      <c r="E362" s="6" t="n"/>
       <c r="F362" s="6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G362" s="6" t="n">
-        <v>0.29</v>
+        <v>1.13</v>
       </c>
       <c r="H362" s="6" t="n">
-        <v>14.4</v>
+        <v>29.36</v>
       </c>
       <c r="I362" s="6" t="inlineStr">
         <is>
-          <t>19/02/2028</t>
+          <t>05/02/2028</t>
         </is>
       </c>
       <c r="J362" s="6" t="inlineStr"/>
       <c r="K362" s="6" t="inlineStr"/>
       <c r="L362" s="6" t="n">
-        <v>20.28</v>
+        <v>41.35</v>
       </c>
       <c r="M362" s="6" t="n">
-        <v>0.608</v>
+        <v>1.24</v>
       </c>
       <c r="N362" s="6" t="n">
         <v>71</v>
       </c>
       <c r="O362" s="6" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="P362" s="6" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q362" s="6" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="R362" s="6" t="n">
-        <v>2.2</v>
+        <v>0.72</v>
       </c>
       <c r="S362" s="6" t="n">
-        <v>5784</v>
+        <v>7009</v>
       </c>
       <c r="T362" s="6" t="n">
-        <v>2928</v>
+        <v>3937</v>
       </c>
       <c r="U362" s="6" t="n">
-        <v>3642</v>
+        <v>4581</v>
       </c>
       <c r="V362" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
         </is>
       </c>
       <c r="W362" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
         </is>
       </c>
       <c r="X362" s="6" t="n">
-        <v>0.747</v>
+        <v>1.257</v>
       </c>
     </row>
     <row r="363">
@@ -19247,80 +19185,74 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>EVODIET VEGAN</t>
+          <t>PUDDING PROTÉINÉ 2.0</t>
         </is>
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>2Kg</t>
-        </is>
-      </c>
-      <c r="E363" s="4" t="n">
-        <v>36.2</v>
-      </c>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="n"/>
       <c r="F363" s="4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>0.27</v>
+        <v>0.79</v>
       </c>
       <c r="H363" s="4" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="I363" s="4" t="inlineStr">
-        <is>
-          <t>30/10/2027</t>
-        </is>
-      </c>
+        <v>19.81</v>
+      </c>
+      <c r="I363" s="4" t="n"/>
       <c r="J363" s="4" t="inlineStr"/>
       <c r="K363" s="4" t="inlineStr"/>
       <c r="L363" s="4" t="n">
-        <v>19.11</v>
+        <v>27.9</v>
       </c>
       <c r="M363" s="4" t="n">
-        <v>0.573</v>
+        <v>0.837</v>
       </c>
       <c r="N363" s="4" t="n">
         <v>71</v>
       </c>
       <c r="O363" s="4" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="P363" s="4" t="n">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="Q363" s="4" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="R363" s="4" t="n">
-        <v>2.2</v>
+        <v>0.72</v>
       </c>
       <c r="S363" s="4" t="n">
-        <v>5784</v>
+        <v>7009</v>
       </c>
       <c r="T363" s="4" t="n">
-        <v>2928</v>
+        <v>3937</v>
       </c>
       <c r="U363" s="4" t="n">
-        <v>3642</v>
+        <v>4581</v>
       </c>
       <c r="V363" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
         </is>
       </c>
       <c r="W363" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
         </is>
       </c>
       <c r="X363" s="4" t="n">
-        <v>0.704</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="364">
@@ -19331,12 +19263,12 @@
       </c>
       <c r="B364" s="5" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+          <t>EVODIET VEGAN</t>
         </is>
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
@@ -19345,66 +19277,66 @@
         </is>
       </c>
       <c r="E364" s="6" t="n">
-        <v>8</v>
+        <v>11.42</v>
       </c>
       <c r="F364" s="6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G364" s="6" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="H364" s="6" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="I364" s="6" t="inlineStr">
         <is>
-          <t>10/12/2027</t>
+          <t>19/02/2028</t>
         </is>
       </c>
       <c r="J364" s="6" t="inlineStr"/>
       <c r="K364" s="6" t="inlineStr"/>
       <c r="L364" s="6" t="n">
-        <v>17.78</v>
+        <v>20.28</v>
       </c>
       <c r="M364" s="6" t="n">
-        <v>0.533</v>
+        <v>0.608</v>
       </c>
       <c r="N364" s="6" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="O364" s="6" t="n">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="P364" s="6" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q364" s="6" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="R364" s="6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S364" s="6" t="n">
-        <v>7441</v>
+        <v>5784</v>
       </c>
       <c r="T364" s="6" t="n">
-        <v>3835</v>
+        <v>2928</v>
       </c>
       <c r="U364" s="6" t="n">
-        <v>4031</v>
+        <v>3642</v>
       </c>
       <c r="V364" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
         </is>
       </c>
       <c r="W364" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
         </is>
       </c>
       <c r="X364" s="6" t="n">
-        <v>0.645</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="365">
@@ -19415,12 +19347,12 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+          <t>EVODIET VEGAN</t>
         </is>
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -19429,66 +19361,66 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>22.88</v>
+        <v>36.2</v>
       </c>
       <c r="F365" s="4" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G365" s="4" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="H365" s="4" t="n">
-        <v>11.44</v>
+        <v>13.57</v>
       </c>
       <c r="I365" s="4" t="inlineStr">
         <is>
-          <t>10/12/2027</t>
+          <t>30/10/2027</t>
         </is>
       </c>
       <c r="J365" s="4" t="inlineStr"/>
       <c r="K365" s="4" t="inlineStr"/>
       <c r="L365" s="4" t="n">
-        <v>12.71</v>
+        <v>19.11</v>
       </c>
       <c r="M365" s="4" t="n">
-        <v>0.381</v>
+        <v>0.573</v>
       </c>
       <c r="N365" s="4" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="O365" s="4" t="n">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="P365" s="4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q365" s="4" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="R365" s="4" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S365" s="4" t="n">
-        <v>7441</v>
+        <v>5784</v>
       </c>
       <c r="T365" s="4" t="n">
-        <v>3835</v>
+        <v>2928</v>
       </c>
       <c r="U365" s="4" t="n">
-        <v>4031</v>
+        <v>3642</v>
       </c>
       <c r="V365" s="4" t="inlineStr">
         <is>
-          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
         </is>
       </c>
       <c r="W365" s="4" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
         </is>
       </c>
       <c r="X365" s="4" t="n">
-        <v>0.461</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="366">
@@ -19499,12 +19431,12 @@
       </c>
       <c r="B366" s="5" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
         </is>
       </c>
       <c r="C366" s="5" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
@@ -19513,66 +19445,66 @@
         </is>
       </c>
       <c r="E366" s="6" t="n">
-        <v>11.16</v>
+        <v>8</v>
       </c>
       <c r="F366" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G366" s="6" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H366" s="6" t="n">
-        <v>22.32</v>
+        <v>16</v>
       </c>
       <c r="I366" s="6" t="inlineStr">
         <is>
-          <t>16/03/2028</t>
+          <t>10/12/2027</t>
         </is>
       </c>
       <c r="J366" s="6" t="inlineStr"/>
       <c r="K366" s="6" t="inlineStr"/>
       <c r="L366" s="6" t="n">
-        <v>24.8</v>
+        <v>17.78</v>
       </c>
       <c r="M366" s="6" t="n">
-        <v>0.744</v>
+        <v>0.533</v>
       </c>
       <c r="N366" s="6" t="n">
         <v>90</v>
       </c>
       <c r="O366" s="6" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="P366" s="6" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q366" s="6" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="R366" s="6" t="n">
-        <v>0.14</v>
+        <v>3.1</v>
       </c>
       <c r="S366" s="6" t="n">
-        <v>8686</v>
+        <v>7441</v>
       </c>
       <c r="T366" s="6" t="n">
-        <v>4795</v>
+        <v>3835</v>
       </c>
       <c r="U366" s="6" t="n">
-        <v>5790</v>
+        <v>4031</v>
       </c>
       <c r="V366" s="6" t="inlineStr">
         <is>
-          <t>Isolat de protéine de lait.</t>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
         </is>
       </c>
       <c r="W366" s="6" t="inlineStr">
         <is>
-          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
         </is>
       </c>
       <c r="X366" s="6" t="n">
-        <v>0.771</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="367">
@@ -19583,12 +19515,12 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
         </is>
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -19597,65 +19529,233 @@
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>35.47</v>
+        <v>22.88</v>
       </c>
       <c r="F367" s="4" t="n">
         <v>67</v>
       </c>
       <c r="G367" s="4" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="H367" s="4" t="n">
-        <v>17.74</v>
+        <v>11.44</v>
       </c>
       <c r="I367" s="4" t="inlineStr">
         <is>
-          <t>31/10/2027</t>
+          <t>10/12/2027</t>
         </is>
       </c>
       <c r="J367" s="4" t="inlineStr"/>
       <c r="K367" s="4" t="inlineStr"/>
       <c r="L367" s="4" t="n">
-        <v>19.71</v>
+        <v>12.71</v>
       </c>
       <c r="M367" s="4" t="n">
-        <v>0.591</v>
+        <v>0.381</v>
       </c>
       <c r="N367" s="4" t="n">
         <v>90</v>
       </c>
       <c r="O367" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P367" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q367" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R367" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S367" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T367" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U367" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V367" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W367" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X367" s="4" t="n">
+        <v>0.461</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E368" s="6" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F368" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G368" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H368" s="6" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="I368" s="6" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J368" s="6" t="inlineStr"/>
+      <c r="K368" s="6" t="inlineStr"/>
+      <c r="L368" s="6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M368" s="6" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N368" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O368" s="6" t="n">
         <v>381</v>
       </c>
-      <c r="P367" s="4" t="n">
+      <c r="P368" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q367" s="4" t="n">
+      <c r="Q368" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="R367" s="4" t="n">
+      <c r="R368" s="6" t="n">
         <v>0.14</v>
       </c>
-      <c r="S367" s="4" t="n">
+      <c r="S368" s="6" t="n">
         <v>8686</v>
       </c>
-      <c r="T367" s="4" t="n">
+      <c r="T368" s="6" t="n">
         <v>4795</v>
       </c>
-      <c r="U367" s="4" t="n">
+      <c r="U368" s="6" t="n">
         <v>5790</v>
       </c>
-      <c r="V367" s="4" t="inlineStr">
+      <c r="V368" s="6" t="inlineStr">
         <is>
           <t>Isolat de protéine de lait.</t>
         </is>
       </c>
-      <c r="W367" s="4" t="inlineStr">
+      <c r="W368" s="6" t="inlineStr">
         <is>
           <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
         </is>
       </c>
-      <c r="X367" s="4" t="n">
+      <c r="X368" s="6" t="n">
+        <v>0.771</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E369" s="4" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F369" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G369" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H369" s="4" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="I369" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J369" s="4" t="inlineStr"/>
+      <c r="K369" s="4" t="inlineStr"/>
+      <c r="L369" s="4" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M369" s="4" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="N369" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O369" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P369" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q369" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R369" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S369" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T369" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U369" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V369" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W369" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X369" s="4" t="n">
         <v>0.613</v>
       </c>
     </row>

--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y369"/>
+  <dimension ref="A1:Y435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19759,6 +19759,5644 @@
         <v>0.613</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F370" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G370" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H370" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I370" s="4" t="inlineStr">
+        <is>
+          <t>15/04/2028</t>
+        </is>
+      </c>
+      <c r="J370" s="4" t="inlineStr"/>
+      <c r="K370" s="4" t="inlineStr"/>
+      <c r="L370" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="M370" s="4" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="N370" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O370" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P370" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q370" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R370" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S370" s="4" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T370" s="4" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U370" s="4" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V370" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W370" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X370" s="4" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="Y370" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D371" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E371" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F371" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G371" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H371" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I371" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2028</t>
+        </is>
+      </c>
+      <c r="J371" s="6" t="inlineStr"/>
+      <c r="K371" s="6" t="inlineStr"/>
+      <c r="L371" s="6" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="M371" s="6" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="N371" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O371" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="P371" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q371" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R371" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S371" s="6" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T371" s="6" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U371" s="6" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V371" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W371" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X371" s="6" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="Y371" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F372" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G372" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H372" s="4" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I372" s="4" t="inlineStr">
+        <is>
+          <t>19/01/2028</t>
+        </is>
+      </c>
+      <c r="J372" s="4" t="inlineStr"/>
+      <c r="K372" s="4" t="inlineStr"/>
+      <c r="L372" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M372" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N372" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="O372" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="P372" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q372" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R372" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S372" s="4" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T372" s="4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U372" s="4" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V372" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W372" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X372" s="4" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="Y372" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D373" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E373" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F373" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G373" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H373" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I373" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J373" s="6" t="inlineStr"/>
+      <c r="K373" s="6" t="inlineStr"/>
+      <c r="L373" s="6" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="M373" s="6" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="N373" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="O373" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="P373" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q373" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R373" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S373" s="6" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T373" s="6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U373" s="6" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V373" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W373" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X373" s="6" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Y373" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="n"/>
+      <c r="F374" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G374" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H374" s="4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I374" s="4" t="inlineStr">
+        <is>
+          <t>18/09/2027</t>
+        </is>
+      </c>
+      <c r="J374" s="4" t="inlineStr"/>
+      <c r="K374" s="4" t="inlineStr"/>
+      <c r="L374" s="4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="M374" s="4" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="N374" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O374" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="P374" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q374" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R374" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S374" s="4" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T374" s="4" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U374" s="4" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V374" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W374" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X374" s="4" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="Y374" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D375" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E375" s="6" t="n"/>
+      <c r="F375" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G375" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H375" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="I375" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2027</t>
+        </is>
+      </c>
+      <c r="J375" s="6" t="inlineStr"/>
+      <c r="K375" s="6" t="inlineStr"/>
+      <c r="L375" s="6" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="M375" s="6" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="N375" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O375" s="6" t="n">
+        <v>346</v>
+      </c>
+      <c r="P375" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q375" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R375" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S375" s="6" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T375" s="6" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U375" s="6" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V375" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W375" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X375" s="6" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="Y375" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F376" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G376" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H376" s="4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="I376" s="4" t="inlineStr">
+        <is>
+          <t>13/03/2028</t>
+        </is>
+      </c>
+      <c r="J376" s="4" t="inlineStr"/>
+      <c r="K376" s="4" t="inlineStr"/>
+      <c r="L376" s="4" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="M376" s="4" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="N376" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O376" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="P376" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q376" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R376" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S376" s="4" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T376" s="4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U376" s="4" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V376" s="4" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W376" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X376" s="4" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="Y376" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D377" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E377" s="6" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F377" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G377" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H377" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I377" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J377" s="6" t="inlineStr"/>
+      <c r="K377" s="6" t="inlineStr"/>
+      <c r="L377" s="6" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="M377" s="6" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="N377" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O377" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="P377" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q377" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R377" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S377" s="6" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T377" s="6" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U377" s="6" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V377" s="6" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W377" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X377" s="6" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="Y377" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="n"/>
+      <c r="F378" s="4" t="n"/>
+      <c r="G378" s="4" t="n"/>
+      <c r="H378" s="4" t="n"/>
+      <c r="I378" s="4" t="inlineStr"/>
+      <c r="J378" s="4" t="inlineStr"/>
+      <c r="K378" s="4" t="inlineStr"/>
+      <c r="L378" s="4" t="n"/>
+      <c r="M378" s="4" t="n"/>
+      <c r="N378" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O378" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P378" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q378" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R378" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S378" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T378" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U378" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V378" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W378" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X378" s="4" t="n"/>
+      <c r="Y378" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D379" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E379" s="6" t="n"/>
+      <c r="F379" s="6" t="n"/>
+      <c r="G379" s="6" t="n"/>
+      <c r="H379" s="6" t="n"/>
+      <c r="I379" s="6" t="inlineStr"/>
+      <c r="J379" s="6" t="inlineStr"/>
+      <c r="K379" s="6" t="inlineStr"/>
+      <c r="L379" s="6" t="n"/>
+      <c r="M379" s="6" t="n"/>
+      <c r="N379" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O379" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P379" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q379" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R379" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S379" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T379" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U379" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V379" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W379" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X379" s="6" t="n"/>
+      <c r="Y379" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="n"/>
+      <c r="F380" s="4" t="n"/>
+      <c r="G380" s="4" t="n"/>
+      <c r="H380" s="4" t="n"/>
+      <c r="I380" s="4" t="inlineStr"/>
+      <c r="J380" s="4" t="inlineStr"/>
+      <c r="K380" s="4" t="inlineStr"/>
+      <c r="L380" s="4" t="n"/>
+      <c r="M380" s="4" t="n"/>
+      <c r="N380" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O380" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P380" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q380" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R380" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S380" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T380" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U380" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V380" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W380" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X380" s="4" t="n"/>
+      <c r="Y380" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D381" s="6" t="inlineStr">
+        <is>
+          <t>2 Kg</t>
+        </is>
+      </c>
+      <c r="E381" s="6" t="n"/>
+      <c r="F381" s="6" t="n"/>
+      <c r="G381" s="6" t="n"/>
+      <c r="H381" s="6" t="n"/>
+      <c r="I381" s="6" t="inlineStr"/>
+      <c r="J381" s="6" t="inlineStr"/>
+      <c r="K381" s="6" t="inlineStr"/>
+      <c r="L381" s="6" t="n"/>
+      <c r="M381" s="6" t="n"/>
+      <c r="N381" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O381" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P381" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q381" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R381" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S381" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T381" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U381" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V381" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W381" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X381" s="6" t="n"/>
+      <c r="Y381" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="n"/>
+      <c r="F382" s="4" t="n"/>
+      <c r="G382" s="4" t="n"/>
+      <c r="H382" s="4" t="n"/>
+      <c r="I382" s="4" t="inlineStr"/>
+      <c r="J382" s="4" t="inlineStr"/>
+      <c r="K382" s="4" t="inlineStr"/>
+      <c r="L382" s="4" t="n"/>
+      <c r="M382" s="4" t="n"/>
+      <c r="N382" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O382" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P382" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q382" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R382" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S382" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T382" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U382" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V382" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W382" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X382" s="4" t="n"/>
+      <c r="Y382" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D383" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E383" s="6" t="n"/>
+      <c r="F383" s="6" t="n"/>
+      <c r="G383" s="6" t="n"/>
+      <c r="H383" s="6" t="n"/>
+      <c r="I383" s="6" t="inlineStr"/>
+      <c r="J383" s="6" t="inlineStr"/>
+      <c r="K383" s="6" t="inlineStr"/>
+      <c r="L383" s="6" t="n"/>
+      <c r="M383" s="6" t="n"/>
+      <c r="N383" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O383" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P383" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q383" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R383" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S383" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T383" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U383" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V383" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W383" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X383" s="6" t="n"/>
+      <c r="Y383" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F384" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G384" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H384" s="4" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="I384" s="4" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J384" s="4" t="inlineStr"/>
+      <c r="K384" s="4" t="inlineStr"/>
+      <c r="L384" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M384" s="4" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N384" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O384" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="P384" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q384" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R384" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S384" s="4" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T384" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U384" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V384" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W384" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X384" s="4" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="Y384" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D385" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E385" s="6" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="F385" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G385" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H385" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I385" s="6" t="inlineStr">
+        <is>
+          <t>29/08/2027</t>
+        </is>
+      </c>
+      <c r="J385" s="6" t="inlineStr"/>
+      <c r="K385" s="6" t="inlineStr"/>
+      <c r="L385" s="6" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="M385" s="6" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="N385" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O385" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="P385" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q385" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R385" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S385" s="6" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T385" s="6" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U385" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V385" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W385" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X385" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Y385" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F386" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G386" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H386" s="4" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I386" s="4" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
+      <c r="J386" s="4" t="inlineStr"/>
+      <c r="K386" s="4" t="inlineStr"/>
+      <c r="L386" s="4" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="M386" s="4" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="N386" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O386" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P386" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q386" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R386" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S386" s="4" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T386" s="4" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U386" s="4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V386" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W386" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X386" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y386" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D387" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E387" s="6" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="F387" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G387" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H387" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="I387" s="6" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J387" s="6" t="inlineStr"/>
+      <c r="K387" s="6" t="inlineStr"/>
+      <c r="L387" s="6" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M387" s="6" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="N387" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O387" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="P387" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q387" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R387" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S387" s="6" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T387" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U387" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V387" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W387" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X387" s="6" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="Y387" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F388" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G388" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H388" s="4" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I388" s="4" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="J388" s="4" t="inlineStr"/>
+      <c r="K388" s="4" t="inlineStr"/>
+      <c r="L388" s="4" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="M388" s="4" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="N388" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O388" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P388" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q388" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R388" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S388" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T388" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U388" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V388" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W388" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X388" s="4" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="Y388" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D389" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E389" s="6" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F389" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G389" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H389" s="6" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I389" s="6" t="n"/>
+      <c r="J389" s="6" t="inlineStr"/>
+      <c r="K389" s="6" t="inlineStr"/>
+      <c r="L389" s="6" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="M389" s="6" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="N389" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O389" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P389" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q389" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R389" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S389" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T389" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U389" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V389" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W389" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X389" s="6" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="Y389" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="F390" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G390" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H390" s="4" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I390" s="4" t="inlineStr">
+        <is>
+          <t>25/08/2027</t>
+        </is>
+      </c>
+      <c r="J390" s="4" t="inlineStr"/>
+      <c r="K390" s="4" t="inlineStr"/>
+      <c r="L390" s="4" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="M390" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="N390" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O390" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P390" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q390" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R390" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S390" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T390" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U390" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V390" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W390" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X390" s="4" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="Y390" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D391" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E391" s="6" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F391" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G391" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H391" s="6" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="I391" s="6" t="inlineStr">
+        <is>
+          <t>20/03/2028</t>
+        </is>
+      </c>
+      <c r="J391" s="6" t="inlineStr"/>
+      <c r="K391" s="6" t="inlineStr"/>
+      <c r="L391" s="6" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M391" s="6" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N391" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="O391" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="P391" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q391" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R391" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S391" s="6" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T391" s="6" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U391" s="6" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V391" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W391" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X391" s="6" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="Y391" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F392" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G392" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H392" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I392" s="4" t="inlineStr">
+        <is>
+          <t>29/01/2028</t>
+        </is>
+      </c>
+      <c r="J392" s="4" t="inlineStr"/>
+      <c r="K392" s="4" t="inlineStr"/>
+      <c r="L392" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M392" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N392" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O392" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="P392" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q392" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R392" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S392" s="4" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T392" s="4" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U392" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V392" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W392" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X392" s="4" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="Y392" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D393" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E393" s="6" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="F393" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G393" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H393" s="6" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="I393" s="6" t="inlineStr">
+        <is>
+          <t>23/04/2027</t>
+        </is>
+      </c>
+      <c r="J393" s="6" t="inlineStr"/>
+      <c r="K393" s="6" t="inlineStr"/>
+      <c r="L393" s="6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="M393" s="6" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="N393" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O393" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="P393" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q393" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R393" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S393" s="6" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T393" s="6" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U393" s="6" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V393" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W393" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X393" s="6" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="Y393" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="F394" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G394" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H394" s="4" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="I394" s="4" t="inlineStr">
+        <is>
+          <t>10/04/2028</t>
+        </is>
+      </c>
+      <c r="J394" s="4" t="inlineStr"/>
+      <c r="K394" s="4" t="inlineStr"/>
+      <c r="L394" s="4" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="M394" s="4" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N394" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O394" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="P394" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q394" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R394" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S394" s="4" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T394" s="4" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U394" s="4" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V394" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W394" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X394" s="4" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="Y394" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D395" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E395" s="6" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F395" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G395" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H395" s="6" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I395" s="6" t="inlineStr">
+        <is>
+          <t>23/09/2027</t>
+        </is>
+      </c>
+      <c r="J395" s="6" t="inlineStr"/>
+      <c r="K395" s="6" t="inlineStr"/>
+      <c r="L395" s="6" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="M395" s="6" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N395" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O395" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="P395" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q395" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R395" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S395" s="6" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T395" s="6" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U395" s="6" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V395" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W395" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X395" s="6" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="Y395" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F396" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="G396" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H396" s="4" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="I396" s="4" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="J396" s="4" t="inlineStr"/>
+      <c r="K396" s="4" t="inlineStr"/>
+      <c r="L396" s="4" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M396" s="4" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="N396" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O396" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="P396" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q396" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R396" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S396" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T396" s="4" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U396" s="4" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V396" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W396" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X396" s="4" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="Y396" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D397" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E397" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F397" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G397" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H397" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I397" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J397" s="6" t="inlineStr"/>
+      <c r="K397" s="6" t="inlineStr"/>
+      <c r="L397" s="6" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="M397" s="6" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N397" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O397" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P397" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q397" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R397" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S397" s="6" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T397" s="6" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U397" s="6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V397" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W397" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X397" s="6" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="Y397" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F398" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G398" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H398" s="4" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I398" s="4" t="inlineStr">
+        <is>
+          <t>09/04/2028</t>
+        </is>
+      </c>
+      <c r="J398" s="4" t="inlineStr"/>
+      <c r="K398" s="4" t="inlineStr"/>
+      <c r="L398" s="4" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="M398" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N398" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O398" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P398" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q398" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R398" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S398" s="4" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T398" s="4" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U398" s="4" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V398" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W398" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X398" s="4" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="Y398" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D399" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E399" s="6" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F399" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G399" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H399" s="6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I399" s="6" t="inlineStr">
+        <is>
+          <t>21/04/2028</t>
+        </is>
+      </c>
+      <c r="J399" s="6" t="inlineStr"/>
+      <c r="K399" s="6" t="inlineStr"/>
+      <c r="L399" s="6" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="M399" s="6" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="N399" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O399" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="P399" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q399" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R399" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S399" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T399" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U399" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V399" s="6" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W399" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X399" s="6" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="Y399" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C400" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F400" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G400" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H400" s="4" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="I400" s="4" t="n"/>
+      <c r="J400" s="4" t="inlineStr"/>
+      <c r="K400" s="4" t="inlineStr"/>
+      <c r="L400" s="4" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="M400" s="4" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="N400" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O400" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="P400" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q400" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R400" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S400" s="4" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T400" s="4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U400" s="4" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V400" s="4" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W400" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X400" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y400" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 30HD</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+        </is>
+      </c>
+      <c r="D401" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E401" s="6" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F401" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G401" s="6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H401" s="6" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I401" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J401" s="6" t="inlineStr"/>
+      <c r="K401" s="6" t="inlineStr"/>
+      <c r="L401" s="6" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M401" s="6" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="N401" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O401" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="P401" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q401" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R401" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S401" s="6" t="n">
+        <v>7170</v>
+      </c>
+      <c r="T401" s="6" t="n">
+        <v>3857</v>
+      </c>
+      <c r="U401" s="6" t="n">
+        <v>3903</v>
+      </c>
+      <c r="V401" s="6" t="inlineStr">
+        <is>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W401" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+        </is>
+      </c>
+      <c r="X401" s="6" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="Y401" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="F402" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G402" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H402" s="4" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="I402" s="4" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J402" s="4" t="inlineStr"/>
+      <c r="K402" s="4" t="inlineStr"/>
+      <c r="L402" s="4" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="M402" s="4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N402" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O402" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="P402" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q402" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R402" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S402" s="4" t="n">
+        <v>6681</v>
+      </c>
+      <c r="T402" s="4" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U402" s="4" t="n">
+        <v>4543</v>
+      </c>
+      <c r="V402" s="4" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+        </is>
+      </c>
+      <c r="W402" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+        </is>
+      </c>
+      <c r="X402" s="4" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="Y402" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D403" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E403" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F403" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G403" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H403" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I403" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J403" s="6" t="inlineStr"/>
+      <c r="K403" s="6" t="inlineStr"/>
+      <c r="L403" s="6" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M403" s="6" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="N403" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="O403" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="P403" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q403" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="R403" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S403" s="6" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T403" s="6" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U403" s="6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V403" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W403" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X403" s="6" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="Y403" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="F404" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G404" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H404" s="4" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I404" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J404" s="4" t="inlineStr"/>
+      <c r="K404" s="4" t="inlineStr"/>
+      <c r="L404" s="4" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="M404" s="4" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="N404" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="O404" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="P404" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q404" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R404" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S404" s="4" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T404" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U404" s="4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V404" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W404" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X404" s="4" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Y404" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D405" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E405" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F405" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G405" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H405" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I405" s="6" t="inlineStr">
+        <is>
+          <t>17/11/2027</t>
+        </is>
+      </c>
+      <c r="J405" s="6" t="inlineStr"/>
+      <c r="K405" s="6" t="inlineStr"/>
+      <c r="L405" s="6" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="M405" s="6" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="N405" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O405" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="P405" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q405" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R405" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S405" s="6" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T405" s="6" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U405" s="6" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V405" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W405" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X405" s="6" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="Y405" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F406" s="4" t="n"/>
+      <c r="G406" s="4" t="n"/>
+      <c r="H406" s="4" t="n"/>
+      <c r="I406" s="4" t="inlineStr"/>
+      <c r="J406" s="4" t="inlineStr"/>
+      <c r="K406" s="4" t="inlineStr"/>
+      <c r="L406" s="4" t="n"/>
+      <c r="M406" s="4" t="n"/>
+      <c r="N406" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="O406" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="P406" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q406" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R406" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S406" s="4" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T406" s="4" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U406" s="4" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V406" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W406" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X406" s="4" t="n"/>
+      <c r="Y406" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D407" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E407" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F407" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G407" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H407" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I407" s="6" t="inlineStr">
+        <is>
+          <t>13/11/2027</t>
+        </is>
+      </c>
+      <c r="J407" s="6" t="inlineStr"/>
+      <c r="K407" s="6" t="inlineStr"/>
+      <c r="L407" s="6" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="M407" s="6" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="N407" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O407" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="P407" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q407" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R407" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S407" s="6" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T407" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U407" s="6" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V407" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W407" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X407" s="6" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="Y407" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F408" s="4" t="n"/>
+      <c r="G408" s="4" t="n"/>
+      <c r="H408" s="4" t="n"/>
+      <c r="I408" s="4" t="inlineStr"/>
+      <c r="J408" s="4" t="inlineStr"/>
+      <c r="K408" s="4" t="inlineStr"/>
+      <c r="L408" s="4" t="n"/>
+      <c r="M408" s="4" t="n"/>
+      <c r="N408" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O408" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="P408" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q408" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R408" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S408" s="4" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T408" s="4" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U408" s="4" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V408" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W408" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X408" s="4" t="n"/>
+      <c r="Y408" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D409" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E409" s="6" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F409" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G409" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H409" s="6" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I409" s="6" t="n"/>
+      <c r="J409" s="6" t="inlineStr"/>
+      <c r="K409" s="6" t="inlineStr"/>
+      <c r="L409" s="6" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M409" s="6" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="N409" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O409" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="P409" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q409" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R409" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S409" s="6" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T409" s="6" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U409" s="6" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V409" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W409" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X409" s="6" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="Y409" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D410" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F410" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G410" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H410" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I410" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J410" s="4" t="inlineStr"/>
+      <c r="K410" s="4" t="inlineStr"/>
+      <c r="L410" s="4" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M410" s="4" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="N410" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O410" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="P410" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q410" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R410" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S410" s="4" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T410" s="4" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U410" s="4" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V410" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W410" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X410" s="4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y410" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="inlineStr">
+        <is>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+        </is>
+      </c>
+      <c r="D411" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E411" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F411" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G411" s="6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H411" s="6" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I411" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J411" s="6" t="inlineStr"/>
+      <c r="K411" s="6" t="inlineStr"/>
+      <c r="L411" s="6" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="M411" s="6" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="N411" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O411" s="6" t="n">
+        <v>349</v>
+      </c>
+      <c r="P411" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q411" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R411" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S411" s="6" t="n">
+        <v>7812</v>
+      </c>
+      <c r="T411" s="6" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U411" s="6" t="n">
+        <v>5312</v>
+      </c>
+      <c r="V411" s="6" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait).</t>
+        </is>
+      </c>
+      <c r="W411" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+        </is>
+      </c>
+      <c r="X411" s="6" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="Y411" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C412" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D412" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E412" s="4" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F412" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G412" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H412" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I412" s="4" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J412" s="4" t="inlineStr"/>
+      <c r="K412" s="4" t="inlineStr"/>
+      <c r="L412" s="4" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M412" s="4" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N412" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="O412" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="P412" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q412" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R412" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S412" s="4" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T412" s="4" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U412" s="4" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V412" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W412" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X412" s="4" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Y412" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D413" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E413" s="6" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F413" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G413" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H413" s="6" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I413" s="6" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
+      <c r="J413" s="6" t="inlineStr"/>
+      <c r="K413" s="6" t="inlineStr"/>
+      <c r="L413" s="6" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="M413" s="6" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N413" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="O413" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="P413" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q413" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R413" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S413" s="6" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T413" s="6" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U413" s="6" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V413" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W413" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X413" s="6" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="Y413" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C414" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D414" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E414" s="4" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F414" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G414" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H414" s="4" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="I414" s="4" t="inlineStr">
+        <is>
+          <t>28/11/2027</t>
+        </is>
+      </c>
+      <c r="J414" s="4" t="inlineStr"/>
+      <c r="K414" s="4" t="inlineStr"/>
+      <c r="L414" s="4" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="M414" s="4" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="N414" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O414" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="P414" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q414" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R414" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S414" s="4" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T414" s="4" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U414" s="4" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V414" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W414" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X414" s="4" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="Y414" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E415" s="6" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F415" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G415" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H415" s="6" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="I415" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J415" s="6" t="inlineStr"/>
+      <c r="K415" s="6" t="inlineStr"/>
+      <c r="L415" s="6" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="M415" s="6" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="O415" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="P415" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q415" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R415" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S415" s="6" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T415" s="6" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U415" s="6" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V415" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W415" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X415" s="6" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Y415" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F416" s="4" t="n"/>
+      <c r="G416" s="4" t="n"/>
+      <c r="H416" s="4" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="I416" s="4" t="inlineStr"/>
+      <c r="J416" s="4" t="inlineStr"/>
+      <c r="K416" s="4" t="inlineStr"/>
+      <c r="L416" s="4" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="M416" s="4" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="N416" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="O416" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P416" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q416" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R416" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S416" s="4" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T416" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U416" s="4" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V416" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W416" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X416" s="4" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="Y416" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D417" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E417" s="6" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F417" s="6" t="n"/>
+      <c r="G417" s="6" t="n"/>
+      <c r="H417" s="6" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="I417" s="6" t="inlineStr"/>
+      <c r="J417" s="6" t="inlineStr"/>
+      <c r="K417" s="6" t="inlineStr"/>
+      <c r="L417" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="M417" s="6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N417" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="O417" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P417" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q417" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R417" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S417" s="6" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T417" s="6" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U417" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V417" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W417" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X417" s="6" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="Y417" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D418" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E418" s="4" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="F418" s="4" t="n"/>
+      <c r="G418" s="4" t="n"/>
+      <c r="H418" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I418" s="4" t="inlineStr"/>
+      <c r="J418" s="4" t="inlineStr"/>
+      <c r="K418" s="4" t="inlineStr"/>
+      <c r="L418" s="4" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="M418" s="4" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="N418" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="O418" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="P418" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q418" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R418" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S418" s="4" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T418" s="4" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U418" s="4" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V418" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W418" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X418" s="4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="Y418" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D419" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E419" s="6" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F419" s="6" t="n"/>
+      <c r="G419" s="6" t="n"/>
+      <c r="H419" s="6" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="I419" s="6" t="inlineStr"/>
+      <c r="J419" s="6" t="inlineStr"/>
+      <c r="K419" s="6" t="inlineStr"/>
+      <c r="L419" s="6" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="M419" s="6" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="N419" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="O419" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="P419" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q419" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R419" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S419" s="6" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T419" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U419" s="6" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V419" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W419" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X419" s="6" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="Y419" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D420" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F420" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G420" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H420" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I420" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J420" s="4" t="inlineStr"/>
+      <c r="K420" s="4" t="inlineStr"/>
+      <c r="L420" s="4" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M420" s="4" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N420" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O420" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="P420" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q420" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R420" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S420" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T420" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U420" s="4" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V420" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W420" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X420" s="4" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y420" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E421" s="6" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="F421" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G421" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H421" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I421" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J421" s="6" t="inlineStr"/>
+      <c r="K421" s="6" t="inlineStr"/>
+      <c r="L421" s="6" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M421" s="6" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N421" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O421" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="P421" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q421" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R421" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S421" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T421" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U421" s="6" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V421" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W421" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X421" s="6" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y421" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D422" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="F422" s="4" t="n"/>
+      <c r="G422" s="4" t="n"/>
+      <c r="H422" s="4" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I422" s="4" t="inlineStr"/>
+      <c r="J422" s="4" t="inlineStr"/>
+      <c r="K422" s="4" t="inlineStr"/>
+      <c r="L422" s="4" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="M422" s="4" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="N422" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O422" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="P422" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q422" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R422" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S422" s="4" t="n"/>
+      <c r="T422" s="4" t="n"/>
+      <c r="U422" s="4" t="n"/>
+      <c r="V422" s="4" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W422" s="4" t="inlineStr"/>
+      <c r="X422" s="4" t="n"/>
+      <c r="Y422" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D423" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E423" s="6" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F423" s="6" t="n"/>
+      <c r="G423" s="6" t="n"/>
+      <c r="H423" s="6" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I423" s="6" t="inlineStr"/>
+      <c r="J423" s="6" t="inlineStr"/>
+      <c r="K423" s="6" t="inlineStr"/>
+      <c r="L423" s="6" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="M423" s="6" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="N423" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O423" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="P423" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q423" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R423" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S423" s="6" t="n"/>
+      <c r="T423" s="6" t="n"/>
+      <c r="U423" s="6" t="n"/>
+      <c r="V423" s="6" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W423" s="6" t="inlineStr"/>
+      <c r="X423" s="6" t="n"/>
+      <c r="Y423" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D424" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E424" s="4" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F424" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G424" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H424" s="4" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="I424" s="4" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J424" s="4" t="inlineStr"/>
+      <c r="K424" s="4" t="inlineStr"/>
+      <c r="L424" s="4" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="M424" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N424" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O424" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="P424" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q424" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R424" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S424" s="4" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T424" s="4" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U424" s="4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V424" s="4" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W424" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X424" s="4" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="Y424" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D425" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E425" s="6" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="F425" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G425" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H425" s="6" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="I425" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2028</t>
+        </is>
+      </c>
+      <c r="J425" s="6" t="inlineStr"/>
+      <c r="K425" s="6" t="inlineStr"/>
+      <c r="L425" s="6" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="M425" s="6" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="N425" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O425" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="P425" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q425" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R425" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S425" s="6" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T425" s="6" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U425" s="6" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V425" s="6" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W425" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X425" s="6" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="Y425" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D426" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F426" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G426" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H426" s="4" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I426" s="4" t="inlineStr">
+        <is>
+          <t>23/01/2028</t>
+        </is>
+      </c>
+      <c r="J426" s="4" t="inlineStr"/>
+      <c r="K426" s="4" t="inlineStr"/>
+      <c r="L426" s="4" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="M426" s="4" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="N426" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O426" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P426" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q426" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R426" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S426" s="4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T426" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U426" s="4" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V426" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W426" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X426" s="4" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="Y426" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D427" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E427" s="6" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="F427" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G427" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H427" s="6" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I427" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
+      <c r="J427" s="6" t="inlineStr"/>
+      <c r="K427" s="6" t="inlineStr"/>
+      <c r="L427" s="6" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="M427" s="6" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="N427" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O427" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P427" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q427" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R427" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S427" s="6" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T427" s="6" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U427" s="6" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V427" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W427" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X427" s="6" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="Y427" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D428" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="n"/>
+      <c r="F428" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G428" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H428" s="4" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="I428" s="4" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J428" s="4" t="inlineStr"/>
+      <c r="K428" s="4" t="inlineStr"/>
+      <c r="L428" s="4" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="M428" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N428" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O428" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="P428" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q428" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R428" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S428" s="4" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T428" s="4" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U428" s="4" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V428" s="4" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W428" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X428" s="4" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="Y428" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D429" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E429" s="6" t="n"/>
+      <c r="F429" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G429" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H429" s="6" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I429" s="6" t="n"/>
+      <c r="J429" s="6" t="inlineStr"/>
+      <c r="K429" s="6" t="inlineStr"/>
+      <c r="L429" s="6" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M429" s="6" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N429" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O429" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="P429" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q429" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R429" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S429" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T429" s="6" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U429" s="6" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V429" s="6" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W429" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X429" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y429" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D430" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F430" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G430" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H430" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I430" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J430" s="4" t="inlineStr"/>
+      <c r="K430" s="4" t="inlineStr"/>
+      <c r="L430" s="4" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="M430" s="4" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N430" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O430" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="P430" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q430" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R430" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S430" s="4" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T430" s="4" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U430" s="4" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V430" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W430" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X430" s="4" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="Y430" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D431" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E431" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F431" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G431" s="6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H431" s="6" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I431" s="6" t="inlineStr">
+        <is>
+          <t>30/10/2027</t>
+        </is>
+      </c>
+      <c r="J431" s="6" t="inlineStr"/>
+      <c r="K431" s="6" t="inlineStr"/>
+      <c r="L431" s="6" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="M431" s="6" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="N431" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O431" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="P431" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q431" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R431" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S431" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T431" s="6" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U431" s="6" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V431" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W431" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X431" s="6" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="Y431" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F432" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G432" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H432" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I432" s="4" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J432" s="4" t="inlineStr"/>
+      <c r="K432" s="4" t="inlineStr"/>
+      <c r="L432" s="4" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="M432" s="4" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N432" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O432" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P432" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q432" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R432" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S432" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T432" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U432" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V432" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W432" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X432" s="4" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="Y432" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D433" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E433" s="6" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="F433" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G433" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H433" s="6" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I433" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J433" s="6" t="inlineStr"/>
+      <c r="K433" s="6" t="inlineStr"/>
+      <c r="L433" s="6" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="M433" s="6" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="N433" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O433" s="6" t="n">
+        <v>384</v>
+      </c>
+      <c r="P433" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q433" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R433" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S433" s="6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T433" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U433" s="6" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V433" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W433" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X433" s="6" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="Y433" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D434" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F434" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G434" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H434" s="4" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="I434" s="4" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J434" s="4" t="inlineStr"/>
+      <c r="K434" s="4" t="inlineStr"/>
+      <c r="L434" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M434" s="4" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N434" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O434" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P434" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q434" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R434" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S434" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T434" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U434" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V434" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W434" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X434" s="4" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="Y434" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D435" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E435" s="6" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F435" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G435" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H435" s="6" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="I435" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J435" s="6" t="inlineStr"/>
+      <c r="K435" s="6" t="inlineStr"/>
+      <c r="L435" s="6" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M435" s="6" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="N435" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O435" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="P435" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q435" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R435" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S435" s="6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T435" s="6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U435" s="6" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V435" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W435" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X435" s="6" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="Y435" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y435"/>
+  <dimension ref="A1:Y498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25397,6 +25397,5491 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D436" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F436" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G436" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H436" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I436" s="4" t="inlineStr">
+        <is>
+          <t>15/04/2028</t>
+        </is>
+      </c>
+      <c r="J436" s="4" t="inlineStr"/>
+      <c r="K436" s="4" t="inlineStr"/>
+      <c r="L436" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="M436" s="4" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="N436" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O436" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P436" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q436" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R436" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S436" s="4" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T436" s="4" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U436" s="4" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V436" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W436" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X436" s="4" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="Y436" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E437" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F437" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G437" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H437" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I437" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2028</t>
+        </is>
+      </c>
+      <c r="J437" s="6" t="inlineStr"/>
+      <c r="K437" s="6" t="inlineStr"/>
+      <c r="L437" s="6" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="M437" s="6" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="N437" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O437" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="P437" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q437" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R437" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S437" s="6" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T437" s="6" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U437" s="6" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V437" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W437" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X437" s="6" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="Y437" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D438" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="n"/>
+      <c r="F438" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G438" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H438" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I438" s="4" t="inlineStr">
+        <is>
+          <t>19/01/2028</t>
+        </is>
+      </c>
+      <c r="J438" s="4" t="inlineStr"/>
+      <c r="K438" s="4" t="inlineStr"/>
+      <c r="L438" s="4" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="M438" s="4" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="N438" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="O438" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="P438" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q438" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R438" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S438" s="4" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T438" s="4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U438" s="4" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V438" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W438" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X438" s="4" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="Y438" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D439" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E439" s="6" t="n"/>
+      <c r="F439" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G439" s="6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H439" s="6" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I439" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J439" s="6" t="inlineStr"/>
+      <c r="K439" s="6" t="inlineStr"/>
+      <c r="L439" s="6" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="M439" s="6" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="N439" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="O439" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="P439" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q439" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R439" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S439" s="6" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T439" s="6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U439" s="6" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V439" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W439" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X439" s="6" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="Y439" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D440" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E440" s="4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="F440" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G440" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H440" s="4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I440" s="4" t="inlineStr">
+        <is>
+          <t>18/09/2027</t>
+        </is>
+      </c>
+      <c r="J440" s="4" t="inlineStr"/>
+      <c r="K440" s="4" t="inlineStr"/>
+      <c r="L440" s="4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="M440" s="4" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="N440" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O440" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="P440" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q440" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R440" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S440" s="4" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T440" s="4" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U440" s="4" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V440" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W440" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X440" s="4" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="Y440" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E441" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F441" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G441" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H441" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="I441" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2027</t>
+        </is>
+      </c>
+      <c r="J441" s="6" t="inlineStr"/>
+      <c r="K441" s="6" t="inlineStr"/>
+      <c r="L441" s="6" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="M441" s="6" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="N441" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O441" s="6" t="n">
+        <v>346</v>
+      </c>
+      <c r="P441" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q441" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R441" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S441" s="6" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T441" s="6" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U441" s="6" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V441" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W441" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X441" s="6" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="Y441" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D442" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F442" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G442" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H442" s="4" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="I442" s="4" t="inlineStr">
+        <is>
+          <t>13/03/2028</t>
+        </is>
+      </c>
+      <c r="J442" s="4" t="inlineStr"/>
+      <c r="K442" s="4" t="inlineStr"/>
+      <c r="L442" s="4" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="M442" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="N442" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O442" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="P442" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q442" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R442" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S442" s="4" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T442" s="4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U442" s="4" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V442" s="4" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W442" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X442" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="Y442" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E443" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F443" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G443" s="6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H443" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I443" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J443" s="6" t="inlineStr"/>
+      <c r="K443" s="6" t="inlineStr"/>
+      <c r="L443" s="6" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="M443" s="6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N443" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O443" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="P443" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q443" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R443" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S443" s="6" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T443" s="6" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U443" s="6" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V443" s="6" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W443" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X443" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y443" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="n"/>
+      <c r="F444" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G444" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H444" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I444" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J444" s="4" t="inlineStr"/>
+      <c r="K444" s="4" t="inlineStr"/>
+      <c r="L444" s="4" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="M444" s="4" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="N444" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O444" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P444" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q444" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R444" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S444" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T444" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U444" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V444" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W444" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X444" s="4" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="Y444" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E445" s="6" t="n"/>
+      <c r="F445" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G445" s="6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H445" s="6" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="I445" s="6" t="n"/>
+      <c r="J445" s="6" t="inlineStr"/>
+      <c r="K445" s="6" t="inlineStr"/>
+      <c r="L445" s="6" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="M445" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="N445" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O445" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P445" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q445" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R445" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S445" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T445" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U445" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V445" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W445" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X445" s="6" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="Y445" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D446" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="n"/>
+      <c r="F446" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G446" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H446" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I446" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2027</t>
+        </is>
+      </c>
+      <c r="J446" s="4" t="inlineStr"/>
+      <c r="K446" s="4" t="inlineStr"/>
+      <c r="L446" s="4" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="M446" s="4" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="N446" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O446" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P446" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q446" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R446" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S446" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T446" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U446" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V446" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W446" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X446" s="4" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Y446" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E447" s="6" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F447" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G447" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H447" s="6" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="I447" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J447" s="6" t="inlineStr"/>
+      <c r="K447" s="6" t="inlineStr"/>
+      <c r="L447" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M447" s="6" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N447" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O447" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="P447" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q447" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R447" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S447" s="6" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T447" s="6" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U447" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V447" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W447" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X447" s="6" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="Y447" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D448" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E448" s="4" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="F448" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G448" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H448" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I448" s="4" t="inlineStr">
+        <is>
+          <t>29/08/2027</t>
+        </is>
+      </c>
+      <c r="J448" s="4" t="inlineStr"/>
+      <c r="K448" s="4" t="inlineStr"/>
+      <c r="L448" s="4" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="M448" s="4" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="N448" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O448" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="P448" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q448" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R448" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S448" s="4" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T448" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U448" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V448" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W448" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X448" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Y448" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D449" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E449" s="6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F449" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G449" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H449" s="6" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I449" s="6" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
+      <c r="J449" s="6" t="inlineStr"/>
+      <c r="K449" s="6" t="inlineStr"/>
+      <c r="L449" s="6" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="M449" s="6" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="N449" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O449" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="P449" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q449" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R449" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S449" s="6" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T449" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U449" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V449" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W449" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X449" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y449" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="F450" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G450" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H450" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I450" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J450" s="4" t="inlineStr"/>
+      <c r="K450" s="4" t="inlineStr"/>
+      <c r="L450" s="4" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M450" s="4" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="N450" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O450" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P450" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q450" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R450" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S450" s="4" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T450" s="4" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U450" s="4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V450" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W450" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X450" s="4" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="Y450" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D451" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E451" s="6" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F451" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G451" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H451" s="6" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I451" s="6" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="J451" s="6" t="inlineStr"/>
+      <c r="K451" s="6" t="inlineStr"/>
+      <c r="L451" s="6" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="M451" s="6" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="N451" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O451" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P451" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q451" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R451" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S451" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T451" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U451" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V451" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W451" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X451" s="6" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="Y451" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D452" s="4" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F452" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G452" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H452" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I452" s="4" t="n"/>
+      <c r="J452" s="4" t="inlineStr"/>
+      <c r="K452" s="4" t="inlineStr"/>
+      <c r="L452" s="4" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="M452" s="4" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="N452" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O452" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P452" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q452" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R452" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S452" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T452" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U452" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V452" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W452" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X452" s="4" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="Y452" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E453" s="6" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="F453" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G453" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H453" s="6" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I453" s="6" t="inlineStr">
+        <is>
+          <t>25/08/2027</t>
+        </is>
+      </c>
+      <c r="J453" s="6" t="inlineStr"/>
+      <c r="K453" s="6" t="inlineStr"/>
+      <c r="L453" s="6" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="M453" s="6" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="N453" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O453" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P453" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q453" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R453" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S453" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T453" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U453" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V453" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W453" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X453" s="6" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="Y453" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D454" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F454" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G454" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H454" s="4" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="I454" s="4" t="inlineStr">
+        <is>
+          <t>20/03/2028</t>
+        </is>
+      </c>
+      <c r="J454" s="4" t="inlineStr"/>
+      <c r="K454" s="4" t="inlineStr"/>
+      <c r="L454" s="4" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M454" s="4" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N454" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O454" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="P454" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q454" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R454" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S454" s="4" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T454" s="4" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U454" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V454" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W454" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X454" s="4" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="Y454" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D455" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E455" s="6" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F455" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G455" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H455" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I455" s="6" t="inlineStr">
+        <is>
+          <t>29/01/2028</t>
+        </is>
+      </c>
+      <c r="J455" s="6" t="inlineStr"/>
+      <c r="K455" s="6" t="inlineStr"/>
+      <c r="L455" s="6" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M455" s="6" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N455" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="O455" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="P455" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q455" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R455" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S455" s="6" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T455" s="6" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U455" s="6" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V455" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W455" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X455" s="6" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="Y455" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D456" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F456" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G456" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H456" s="4" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="I456" s="4" t="inlineStr">
+        <is>
+          <t>23/04/2027</t>
+        </is>
+      </c>
+      <c r="J456" s="4" t="inlineStr"/>
+      <c r="K456" s="4" t="inlineStr"/>
+      <c r="L456" s="4" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="M456" s="4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="N456" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O456" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="P456" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q456" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R456" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S456" s="4" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T456" s="4" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U456" s="4" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V456" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W456" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X456" s="4" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="Y456" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D457" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E457" s="6" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="F457" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G457" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H457" s="6" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I457" s="6" t="inlineStr">
+        <is>
+          <t>10/04/2028</t>
+        </is>
+      </c>
+      <c r="J457" s="6" t="inlineStr"/>
+      <c r="K457" s="6" t="inlineStr"/>
+      <c r="L457" s="6" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="M457" s="6" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N457" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O457" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="P457" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q457" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R457" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S457" s="6" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T457" s="6" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U457" s="6" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V457" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W457" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X457" s="6" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Y457" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D458" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E458" s="4" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F458" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G458" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H458" s="4" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I458" s="4" t="inlineStr">
+        <is>
+          <t>23/09/2027</t>
+        </is>
+      </c>
+      <c r="J458" s="4" t="inlineStr"/>
+      <c r="K458" s="4" t="inlineStr"/>
+      <c r="L458" s="4" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="M458" s="4" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N458" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O458" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="P458" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q458" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R458" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S458" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T458" s="4" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U458" s="4" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V458" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W458" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X458" s="4" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="Y458" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D459" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E459" s="6" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F459" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G459" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H459" s="6" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="I459" s="6" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="J459" s="6" t="inlineStr"/>
+      <c r="K459" s="6" t="inlineStr"/>
+      <c r="L459" s="6" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M459" s="6" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="N459" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O459" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="P459" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q459" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R459" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S459" s="6" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T459" s="6" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U459" s="6" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V459" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W459" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X459" s="6" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="Y459" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D460" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E460" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F460" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G460" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H460" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I460" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J460" s="4" t="inlineStr"/>
+      <c r="K460" s="4" t="inlineStr"/>
+      <c r="L460" s="4" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="M460" s="4" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N460" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O460" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P460" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q460" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R460" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S460" s="4" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T460" s="4" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U460" s="4" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V460" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W460" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X460" s="4" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="Y460" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E461" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F461" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G461" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H461" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I461" s="6" t="inlineStr">
+        <is>
+          <t>09/04/2028</t>
+        </is>
+      </c>
+      <c r="J461" s="6" t="inlineStr"/>
+      <c r="K461" s="6" t="inlineStr"/>
+      <c r="L461" s="6" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="M461" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N461" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O461" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P461" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q461" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R461" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S461" s="6" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T461" s="6" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U461" s="6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V461" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W461" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X461" s="6" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="Y461" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D462" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="F462" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G462" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H462" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I462" s="4" t="inlineStr">
+        <is>
+          <t>21/04/2028</t>
+        </is>
+      </c>
+      <c r="J462" s="4" t="inlineStr"/>
+      <c r="K462" s="4" t="inlineStr"/>
+      <c r="L462" s="4" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="M462" s="4" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="N462" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O462" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="P462" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q462" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R462" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S462" s="4" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T462" s="4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U462" s="4" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V462" s="4" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W462" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X462" s="4" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="Y462" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E463" s="6" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F463" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G463" s="6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H463" s="6" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="I463" s="6" t="n"/>
+      <c r="J463" s="6" t="inlineStr"/>
+      <c r="K463" s="6" t="inlineStr"/>
+      <c r="L463" s="6" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="M463" s="6" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="N463" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O463" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="P463" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q463" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R463" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S463" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T463" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U463" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V463" s="6" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W463" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 1789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 1904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X463" s="6" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="Y463" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 30HD</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+        </is>
+      </c>
+      <c r="D464" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E464" s="4" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F464" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G464" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H464" s="4" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I464" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J464" s="4" t="inlineStr"/>
+      <c r="K464" s="4" t="inlineStr"/>
+      <c r="L464" s="4" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M464" s="4" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="N464" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O464" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="P464" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q464" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R464" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S464" s="4" t="n">
+        <v>7170</v>
+      </c>
+      <c r="T464" s="4" t="n">
+        <v>3857</v>
+      </c>
+      <c r="U464" s="4" t="n">
+        <v>3903</v>
+      </c>
+      <c r="V464" s="4" t="inlineStr">
+        <is>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W464" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+        </is>
+      </c>
+      <c r="X464" s="4" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="Y464" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E465" s="6" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="F465" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G465" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H465" s="6" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="I465" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J465" s="6" t="inlineStr"/>
+      <c r="K465" s="6" t="inlineStr"/>
+      <c r="L465" s="6" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="M465" s="6" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N465" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O465" s="6" t="n">
+        <v>318</v>
+      </c>
+      <c r="P465" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q465" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R465" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S465" s="6" t="n">
+        <v>6681</v>
+      </c>
+      <c r="T465" s="6" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U465" s="6" t="n">
+        <v>4543</v>
+      </c>
+      <c r="V465" s="6" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+        </is>
+      </c>
+      <c r="W465" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+        </is>
+      </c>
+      <c r="X465" s="6" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="Y465" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D466" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E466" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F466" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G466" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H466" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I466" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J466" s="4" t="inlineStr"/>
+      <c r="K466" s="4" t="inlineStr"/>
+      <c r="L466" s="4" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M466" s="4" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="N466" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="O466" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="P466" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q466" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R466" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S466" s="4" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T466" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U466" s="4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V466" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W466" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X466" s="4" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="Y466" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D467" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E467" s="6" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="F467" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G467" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H467" s="6" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I467" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J467" s="6" t="inlineStr"/>
+      <c r="K467" s="6" t="inlineStr"/>
+      <c r="L467" s="6" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="M467" s="6" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="N467" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="O467" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="P467" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q467" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="R467" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S467" s="6" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T467" s="6" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U467" s="6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V467" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W467" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X467" s="6" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Y467" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E468" s="4" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F468" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G468" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H468" s="4" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I468" s="4" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J468" s="4" t="inlineStr"/>
+      <c r="K468" s="4" t="inlineStr"/>
+      <c r="L468" s="4" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="M468" s="4" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="N468" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O468" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="P468" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q468" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R468" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S468" s="4" t="n">
+        <v>7812</v>
+      </c>
+      <c r="T468" s="4" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U468" s="4" t="n">
+        <v>5312</v>
+      </c>
+      <c r="V468" s="4" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait).</t>
+        </is>
+      </c>
+      <c r="W468" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+        </is>
+      </c>
+      <c r="X468" s="4" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="Y468" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E469" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F469" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G469" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H469" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I469" s="6" t="inlineStr">
+        <is>
+          <t>13/11/2027</t>
+        </is>
+      </c>
+      <c r="J469" s="6" t="inlineStr"/>
+      <c r="K469" s="6" t="inlineStr"/>
+      <c r="L469" s="6" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="M469" s="6" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="N469" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O469" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="P469" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q469" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R469" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S469" s="6" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T469" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U469" s="6" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V469" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W469" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X469" s="6" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="Y469" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F470" s="4" t="n"/>
+      <c r="G470" s="4" t="n"/>
+      <c r="H470" s="4" t="n"/>
+      <c r="I470" s="4" t="inlineStr"/>
+      <c r="J470" s="4" t="inlineStr"/>
+      <c r="K470" s="4" t="inlineStr"/>
+      <c r="L470" s="4" t="n"/>
+      <c r="M470" s="4" t="n"/>
+      <c r="N470" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O470" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="P470" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q470" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R470" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S470" s="4" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T470" s="4" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U470" s="4" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V470" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W470" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X470" s="4" t="n"/>
+      <c r="Y470" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D471" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E471" s="6" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F471" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G471" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H471" s="6" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I471" s="6" t="n"/>
+      <c r="J471" s="6" t="inlineStr"/>
+      <c r="K471" s="6" t="inlineStr"/>
+      <c r="L471" s="6" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M471" s="6" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="N471" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O471" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="P471" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q471" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R471" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S471" s="6" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T471" s="6" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U471" s="6" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V471" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W471" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X471" s="6" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="Y471" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F472" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G472" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H472" s="4" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I472" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J472" s="4" t="inlineStr"/>
+      <c r="K472" s="4" t="inlineStr"/>
+      <c r="L472" s="4" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M472" s="4" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="N472" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O472" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="P472" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q472" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R472" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S472" s="4" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T472" s="4" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U472" s="4" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V472" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W472" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X472" s="4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y472" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D473" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E473" s="6" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F473" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G473" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H473" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I473" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J473" s="6" t="inlineStr"/>
+      <c r="K473" s="6" t="inlineStr"/>
+      <c r="L473" s="6" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M473" s="6" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N473" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="O473" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="P473" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q473" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R473" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S473" s="6" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T473" s="6" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U473" s="6" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V473" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W473" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X473" s="6" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Y473" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F474" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G474" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H474" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I474" s="4" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
+      <c r="J474" s="4" t="inlineStr"/>
+      <c r="K474" s="4" t="inlineStr"/>
+      <c r="L474" s="4" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="M474" s="4" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N474" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="O474" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="P474" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q474" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R474" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S474" s="4" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T474" s="4" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U474" s="4" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V474" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W474" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X474" s="4" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="Y474" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D475" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E475" s="6" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F475" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G475" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H475" s="6" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="I475" s="6" t="inlineStr">
+        <is>
+          <t>28/11/2027</t>
+        </is>
+      </c>
+      <c r="J475" s="6" t="inlineStr"/>
+      <c r="K475" s="6" t="inlineStr"/>
+      <c r="L475" s="6" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="M475" s="6" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="N475" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="O475" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="P475" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q475" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R475" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S475" s="6" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T475" s="6" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U475" s="6" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V475" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W475" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X475" s="6" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="Y475" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D476" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E476" s="4" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F476" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G476" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H476" s="4" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="I476" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J476" s="4" t="inlineStr"/>
+      <c r="K476" s="4" t="inlineStr"/>
+      <c r="L476" s="4" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="M476" s="4" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N476" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O476" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="P476" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q476" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R476" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S476" s="4" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T476" s="4" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U476" s="4" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V476" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W476" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X476" s="4" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Y476" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D477" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E477" s="6" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F477" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G477" s="6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H477" s="6" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I477" s="6" t="inlineStr">
+        <is>
+          <t>17/11/2027</t>
+        </is>
+      </c>
+      <c r="J477" s="6" t="inlineStr"/>
+      <c r="K477" s="6" t="inlineStr"/>
+      <c r="L477" s="6" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="M477" s="6" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="N477" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O477" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="P477" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q477" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R477" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S477" s="6" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T477" s="6" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U477" s="6" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V477" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W477" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X477" s="6" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="Y477" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D478" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E478" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F478" s="4" t="n"/>
+      <c r="G478" s="4" t="n"/>
+      <c r="H478" s="4" t="n"/>
+      <c r="I478" s="4" t="inlineStr"/>
+      <c r="J478" s="4" t="inlineStr"/>
+      <c r="K478" s="4" t="inlineStr"/>
+      <c r="L478" s="4" t="n"/>
+      <c r="M478" s="4" t="n"/>
+      <c r="N478" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="O478" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="P478" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q478" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R478" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S478" s="4" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T478" s="4" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U478" s="4" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V478" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W478" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X478" s="4" t="n"/>
+      <c r="Y478" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D479" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E479" s="6" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F479" s="6" t="n"/>
+      <c r="G479" s="6" t="n"/>
+      <c r="H479" s="6" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="I479" s="6" t="inlineStr"/>
+      <c r="J479" s="6" t="inlineStr"/>
+      <c r="K479" s="6" t="inlineStr"/>
+      <c r="L479" s="6" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="M479" s="6" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="N479" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="O479" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P479" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q479" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R479" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S479" s="6" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T479" s="6" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U479" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V479" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W479" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X479" s="6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="Y479" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D480" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E480" s="4" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F480" s="4" t="n"/>
+      <c r="G480" s="4" t="n"/>
+      <c r="H480" s="4" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="I480" s="4" t="inlineStr"/>
+      <c r="J480" s="4" t="inlineStr"/>
+      <c r="K480" s="4" t="inlineStr"/>
+      <c r="L480" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M480" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N480" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="O480" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P480" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q480" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R480" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S480" s="4" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T480" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U480" s="4" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V480" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W480" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X480" s="4" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="Y480" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D481" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E481" s="6" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F481" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G481" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H481" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I481" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J481" s="6" t="inlineStr"/>
+      <c r="K481" s="6" t="inlineStr"/>
+      <c r="L481" s="6" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="M481" s="6" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="N481" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="O481" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="P481" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q481" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R481" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S481" s="6" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T481" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U481" s="6" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V481" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W481" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X481" s="6" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="Y481" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E482" s="4" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="F482" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G482" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H482" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I482" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J482" s="4" t="inlineStr"/>
+      <c r="K482" s="4" t="inlineStr"/>
+      <c r="L482" s="4" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="M482" s="4" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="N482" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="O482" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="P482" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q482" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R482" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S482" s="4" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T482" s="4" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U482" s="4" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V482" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W482" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X482" s="4" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="Y482" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D483" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E483" s="6" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="F483" s="6" t="n"/>
+      <c r="G483" s="6" t="n"/>
+      <c r="H483" s="6" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I483" s="6" t="inlineStr"/>
+      <c r="J483" s="6" t="inlineStr"/>
+      <c r="K483" s="6" t="inlineStr"/>
+      <c r="L483" s="6" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="M483" s="6" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="N483" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O483" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="P483" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q483" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R483" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S483" s="6" t="n"/>
+      <c r="T483" s="6" t="n"/>
+      <c r="U483" s="6" t="n"/>
+      <c r="V483" s="6" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W483" s="6" t="inlineStr"/>
+      <c r="X483" s="6" t="n"/>
+      <c r="Y483" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D484" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E484" s="4" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F484" s="4" t="n"/>
+      <c r="G484" s="4" t="n"/>
+      <c r="H484" s="4" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I484" s="4" t="inlineStr"/>
+      <c r="J484" s="4" t="inlineStr"/>
+      <c r="K484" s="4" t="inlineStr"/>
+      <c r="L484" s="4" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="M484" s="4" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="N484" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O484" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="P484" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q484" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R484" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S484" s="4" t="n"/>
+      <c r="T484" s="4" t="n"/>
+      <c r="U484" s="4" t="n"/>
+      <c r="V484" s="4" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W484" s="4" t="inlineStr"/>
+      <c r="X484" s="4" t="n"/>
+      <c r="Y484" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D485" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E485" s="6" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F485" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G485" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H485" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I485" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J485" s="6" t="inlineStr"/>
+      <c r="K485" s="6" t="inlineStr"/>
+      <c r="L485" s="6" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M485" s="6" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N485" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O485" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="P485" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q485" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R485" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S485" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T485" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U485" s="6" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V485" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W485" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X485" s="6" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y485" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D486" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E486" s="4" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="F486" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G486" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H486" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I486" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J486" s="4" t="inlineStr"/>
+      <c r="K486" s="4" t="inlineStr"/>
+      <c r="L486" s="4" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M486" s="4" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N486" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O486" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="P486" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q486" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R486" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S486" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T486" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U486" s="4" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V486" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W486" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X486" s="4" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y486" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D487" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E487" s="6" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F487" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G487" s="6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H487" s="6" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="I487" s="6" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J487" s="6" t="inlineStr"/>
+      <c r="K487" s="6" t="inlineStr"/>
+      <c r="L487" s="6" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="M487" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N487" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O487" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="P487" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q487" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R487" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S487" s="6" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T487" s="6" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U487" s="6" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V487" s="6" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W487" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X487" s="6" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="Y487" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D488" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="F488" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G488" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H488" s="4" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="I488" s="4" t="inlineStr">
+        <is>
+          <t>23/02/2028</t>
+        </is>
+      </c>
+      <c r="J488" s="4" t="inlineStr"/>
+      <c r="K488" s="4" t="inlineStr"/>
+      <c r="L488" s="4" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="M488" s="4" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="N488" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O488" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="P488" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q488" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R488" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S488" s="4" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T488" s="4" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U488" s="4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V488" s="4" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W488" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X488" s="4" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="Y488" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D489" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E489" s="6" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F489" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G489" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H489" s="6" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I489" s="6" t="inlineStr">
+        <is>
+          <t>23/01/2028</t>
+        </is>
+      </c>
+      <c r="J489" s="6" t="inlineStr"/>
+      <c r="K489" s="6" t="inlineStr"/>
+      <c r="L489" s="6" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="M489" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="N489" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O489" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P489" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q489" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R489" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S489" s="6" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T489" s="6" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U489" s="6" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V489" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W489" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X489" s="6" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="Y489" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D490" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E490" s="4" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="F490" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G490" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H490" s="4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I490" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
+      <c r="J490" s="4" t="inlineStr"/>
+      <c r="K490" s="4" t="inlineStr"/>
+      <c r="L490" s="4" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="M490" s="4" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="N490" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O490" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P490" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q490" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R490" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S490" s="4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T490" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U490" s="4" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V490" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W490" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X490" s="4" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="Y490" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D491" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E491" s="6" t="n"/>
+      <c r="F491" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G491" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H491" s="6" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="I491" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J491" s="6" t="inlineStr"/>
+      <c r="K491" s="6" t="inlineStr"/>
+      <c r="L491" s="6" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="M491" s="6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N491" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O491" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="P491" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q491" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R491" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S491" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T491" s="6" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U491" s="6" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V491" s="6" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W491" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X491" s="6" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="Y491" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D492" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="n"/>
+      <c r="F492" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G492" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H492" s="4" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I492" s="4" t="n"/>
+      <c r="J492" s="4" t="inlineStr"/>
+      <c r="K492" s="4" t="inlineStr"/>
+      <c r="L492" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M492" s="4" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N492" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O492" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="P492" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q492" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R492" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S492" s="4" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T492" s="4" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U492" s="4" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V492" s="4" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W492" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X492" s="4" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y492" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D493" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E493" s="6" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F493" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G493" s="6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H493" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I493" s="6" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J493" s="6" t="inlineStr"/>
+      <c r="K493" s="6" t="inlineStr"/>
+      <c r="L493" s="6" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="M493" s="6" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N493" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O493" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="P493" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q493" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R493" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S493" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T493" s="6" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U493" s="6" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V493" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W493" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X493" s="6" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="Y493" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F494" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G494" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H494" s="4" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I494" s="4" t="inlineStr">
+        <is>
+          <t>30/10/2027</t>
+        </is>
+      </c>
+      <c r="J494" s="4" t="inlineStr"/>
+      <c r="K494" s="4" t="inlineStr"/>
+      <c r="L494" s="4" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="M494" s="4" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="N494" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O494" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="P494" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q494" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R494" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S494" s="4" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T494" s="4" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U494" s="4" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V494" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W494" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X494" s="4" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="Y494" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D495" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E495" s="6" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="F495" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G495" s="6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H495" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I495" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J495" s="6" t="inlineStr"/>
+      <c r="K495" s="6" t="inlineStr"/>
+      <c r="L495" s="6" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="M495" s="6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N495" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O495" s="6" t="n">
+        <v>384</v>
+      </c>
+      <c r="P495" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q495" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R495" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S495" s="6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T495" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U495" s="6" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V495" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W495" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X495" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y495" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D496" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E496" s="4" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F496" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G496" s="4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H496" s="4" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="I496" s="4" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J496" s="4" t="inlineStr"/>
+      <c r="K496" s="4" t="inlineStr"/>
+      <c r="L496" s="4" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="M496" s="4" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N496" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O496" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P496" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q496" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R496" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S496" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T496" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U496" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V496" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W496" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X496" s="4" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="Y496" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D497" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E497" s="6" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F497" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G497" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H497" s="6" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="I497" s="6" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J497" s="6" t="inlineStr"/>
+      <c r="K497" s="6" t="inlineStr"/>
+      <c r="L497" s="6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M497" s="6" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N497" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O497" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="P497" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q497" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R497" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S497" s="6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T497" s="6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U497" s="6" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V497" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W497" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X497" s="6" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="Y497" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D498" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E498" s="4" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F498" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G498" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H498" s="4" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="I498" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J498" s="4" t="inlineStr"/>
+      <c r="K498" s="4" t="inlineStr"/>
+      <c r="L498" s="4" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M498" s="4" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="N498" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O498" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P498" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q498" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R498" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S498" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T498" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U498" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V498" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W498" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X498" s="4" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="Y498" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE606"/>
+  <dimension ref="A1:AE692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40924,6 +40924,7814 @@
         <v>32.4</v>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B607" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C607" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D607" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E607" s="4" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F607" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G607" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H607" s="4" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="I607" s="4" t="inlineStr">
+        <is>
+          <t>15/04/2028</t>
+        </is>
+      </c>
+      <c r="J607" s="4" t="inlineStr"/>
+      <c r="K607" s="4" t="inlineStr"/>
+      <c r="L607" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="M607" s="4" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="N607" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O607" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P607" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q607" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R607" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S607" s="4" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T607" s="4" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U607" s="4" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V607" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W607" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X607" s="4" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="Y607" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z607" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA607" s="4" t="n"/>
+      <c r="AB607" s="4" t="n"/>
+      <c r="AC607" s="4" t="n"/>
+      <c r="AD607" s="4" t="n"/>
+      <c r="AE607" s="4" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B608" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C608" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D608" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E608" s="6" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="F608" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G608" s="6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H608" s="6" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="I608" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2028</t>
+        </is>
+      </c>
+      <c r="J608" s="6" t="inlineStr"/>
+      <c r="K608" s="6" t="inlineStr"/>
+      <c r="L608" s="6" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="M608" s="6" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="N608" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O608" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="P608" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q608" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R608" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S608" s="6" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T608" s="6" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U608" s="6" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V608" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W608" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X608" s="6" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="Y608" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z608" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA608" s="6" t="n"/>
+      <c r="AB608" s="6" t="n"/>
+      <c r="AC608" s="6" t="n"/>
+      <c r="AD608" s="6" t="n"/>
+      <c r="AE608" s="6" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B609" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C609" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D609" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E609" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F609" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G609" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H609" s="4" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I609" s="4" t="inlineStr">
+        <is>
+          <t>19/01/2028</t>
+        </is>
+      </c>
+      <c r="J609" s="4" t="inlineStr"/>
+      <c r="K609" s="4" t="inlineStr"/>
+      <c r="L609" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M609" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N609" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="O609" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="P609" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q609" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R609" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S609" s="4" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T609" s="4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U609" s="4" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V609" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W609" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X609" s="4" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="Y609" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z609" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA609" s="4" t="n"/>
+      <c r="AB609" s="4" t="n"/>
+      <c r="AC609" s="4" t="n"/>
+      <c r="AD609" s="4" t="n"/>
+      <c r="AE609" s="4" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B610" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C610" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D610" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E610" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F610" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G610" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H610" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I610" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J610" s="6" t="inlineStr"/>
+      <c r="K610" s="6" t="inlineStr"/>
+      <c r="L610" s="6" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="M610" s="6" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="N610" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="O610" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="P610" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q610" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R610" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S610" s="6" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T610" s="6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U610" s="6" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V610" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W610" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X610" s="6" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Y610" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z610" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA610" s="6" t="n"/>
+      <c r="AB610" s="6" t="n"/>
+      <c r="AC610" s="6" t="n"/>
+      <c r="AD610" s="6" t="n"/>
+      <c r="AE610" s="6" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B611" s="3" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C611" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D611" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E611" s="4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="F611" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G611" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H611" s="4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I611" s="4" t="inlineStr">
+        <is>
+          <t>10/11/2027</t>
+        </is>
+      </c>
+      <c r="J611" s="4" t="inlineStr"/>
+      <c r="K611" s="4" t="inlineStr"/>
+      <c r="L611" s="4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="M611" s="4" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="N611" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O611" s="4" t="n">
+        <v>347</v>
+      </c>
+      <c r="P611" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q611" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R611" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S611" s="4" t="n">
+        <v>8834</v>
+      </c>
+      <c r="T611" s="4" t="n">
+        <v>5507</v>
+      </c>
+      <c r="U611" s="4" t="n">
+        <v>4712</v>
+      </c>
+      <c r="V611" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées de lait, arôme naturel, acidifiant (acide citrique), correcteur d'acidité (citrate de tripotassium), régulateur d'acidité (citrate trisodique), édulcorant (sucralose), correcteur d'acidité (acide tartrique), colorant (complexes de chlorophylline de cuivre).</t>
+        </is>
+      </c>
+      <c r="W611" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4228.0, "L-Arginine": 1499.0, "Acide L-spartique": 9367.0, "L-Cystéine": 1902.0, "Acide L-Glutamique": 14367.0, "Glycine": 1295.0, "L-Histidine": 1328.0, "L-Isoleucine": 5507.0, "L-Leucine": 8834.0, "L-Lysine": 8104.0, "L-Méthionine": 1770.0, "L-Phénylalanine": 2410.0, "L-Proline": 4729.0, "L-Sérine": 3590.0, "L-Thréonine": 5810.0, "L-Tryptophane": 1581.0, "L-Tyrosine": 2327.0, "L-Valine": 4712.0}</t>
+        </is>
+      </c>
+      <c r="X611" s="4" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="Y611" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z611" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA611" s="4" t="n"/>
+      <c r="AB611" s="4" t="n"/>
+      <c r="AC611" s="4" t="n"/>
+      <c r="AD611" s="4" t="n"/>
+      <c r="AE611" s="4" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B612" s="5" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C612" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D612" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E612" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F612" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G612" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H612" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="I612" s="6" t="inlineStr">
+        <is>
+          <t>10/11/2027</t>
+        </is>
+      </c>
+      <c r="J612" s="6" t="inlineStr"/>
+      <c r="K612" s="6" t="inlineStr"/>
+      <c r="L612" s="6" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="M612" s="6" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="N612" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O612" s="6" t="n">
+        <v>347</v>
+      </c>
+      <c r="P612" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q612" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R612" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S612" s="6" t="n">
+        <v>8834</v>
+      </c>
+      <c r="T612" s="6" t="n">
+        <v>5507</v>
+      </c>
+      <c r="U612" s="6" t="n">
+        <v>4712</v>
+      </c>
+      <c r="V612" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées de lait, arôme naturel, acidifiant (acide citrique), correcteur d'acidité (citrate de tripotassium), régulateur d'acidité (citrate trisodique), édulcorant (sucralose), correcteur d'acidité (acide tartrique), colorant (complexes de chlorophylline de cuivre).</t>
+        </is>
+      </c>
+      <c r="W612" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4228.0, "L-Arginine": 1499.0, "Acide L-spartique": 9367.0, "L-Cystéine": 1902.0, "Acide L-Glutamique": 14367.0, "Glycine": 1295.0, "L-Histidine": 1328.0, "L-Isoleucine": 5507.0, "L-Leucine": 8834.0, "L-Lysine": 8104.0, "L-Méthionine": 1770.0, "L-Phénylalanine": 2410.0, "L-Proline": 4729.0, "L-Sérine": 3590.0, "L-Thréonine": 5810.0, "L-Tryptophane": 1581.0, "L-Tyrosine": 2327.0, "L-Valine": 4712.0}</t>
+        </is>
+      </c>
+      <c r="X612" s="6" t="n">
+        <v>1.229</v>
+      </c>
+      <c r="Y612" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z612" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA612" s="6" t="n"/>
+      <c r="AB612" s="6" t="n"/>
+      <c r="AC612" s="6" t="n"/>
+      <c r="AD612" s="6" t="n"/>
+      <c r="AE612" s="6" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B613" s="3" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C613" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D613" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E613" s="4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F613" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G613" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H613" s="4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="I613" s="4" t="inlineStr">
+        <is>
+          <t>13/03/2028</t>
+        </is>
+      </c>
+      <c r="J613" s="4" t="inlineStr"/>
+      <c r="K613" s="4" t="inlineStr"/>
+      <c r="L613" s="4" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="M613" s="4" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="N613" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O613" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="P613" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q613" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R613" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S613" s="4" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T613" s="4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U613" s="4" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V613" s="4" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W613" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X613" s="4" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="Y613" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z613" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA613" s="4" t="n"/>
+      <c r="AB613" s="4" t="n"/>
+      <c r="AC613" s="4" t="n"/>
+      <c r="AD613" s="4" t="n"/>
+      <c r="AE613" s="4" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B614" s="5" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C614" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D614" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E614" s="6" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="F614" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G614" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H614" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I614" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J614" s="6" t="inlineStr"/>
+      <c r="K614" s="6" t="inlineStr"/>
+      <c r="L614" s="6" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="M614" s="6" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="N614" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O614" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="P614" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q614" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R614" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S614" s="6" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T614" s="6" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U614" s="6" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V614" s="6" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W614" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X614" s="6" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="Y614" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z614" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA614" s="6" t="n"/>
+      <c r="AB614" s="6" t="n"/>
+      <c r="AC614" s="6" t="n"/>
+      <c r="AD614" s="6" t="n"/>
+      <c r="AE614" s="6" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B615" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C615" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D615" s="4" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="E615" s="4" t="n"/>
+      <c r="F615" s="4" t="n"/>
+      <c r="G615" s="4" t="n"/>
+      <c r="H615" s="4" t="n"/>
+      <c r="I615" s="4" t="inlineStr"/>
+      <c r="J615" s="4" t="inlineStr"/>
+      <c r="K615" s="4" t="inlineStr"/>
+      <c r="L615" s="4" t="n"/>
+      <c r="M615" s="4" t="n"/>
+      <c r="N615" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O615" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P615" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q615" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R615" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S615" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T615" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U615" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V615" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W615" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X615" s="4" t="n"/>
+      <c r="Y615" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z615" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA615" s="4" t="n"/>
+      <c r="AB615" s="4" t="n"/>
+      <c r="AC615" s="4" t="n"/>
+      <c r="AD615" s="4" t="n"/>
+      <c r="AE615" s="4" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B616" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D616" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E616" s="6" t="n"/>
+      <c r="F616" s="6" t="n"/>
+      <c r="G616" s="6" t="n"/>
+      <c r="H616" s="6" t="n"/>
+      <c r="I616" s="6" t="inlineStr"/>
+      <c r="J616" s="6" t="inlineStr"/>
+      <c r="K616" s="6" t="inlineStr"/>
+      <c r="L616" s="6" t="n"/>
+      <c r="M616" s="6" t="n"/>
+      <c r="N616" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O616" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P616" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q616" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R616" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S616" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T616" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U616" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V616" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W616" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X616" s="6" t="n"/>
+      <c r="Y616" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z616" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA616" s="6" t="n"/>
+      <c r="AB616" s="6" t="n"/>
+      <c r="AC616" s="6" t="n"/>
+      <c r="AD616" s="6" t="n"/>
+      <c r="AE616" s="6" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B617" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C617" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D617" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E617" s="4" t="n"/>
+      <c r="F617" s="4" t="n"/>
+      <c r="G617" s="4" t="n"/>
+      <c r="H617" s="4" t="n"/>
+      <c r="I617" s="4" t="inlineStr"/>
+      <c r="J617" s="4" t="inlineStr"/>
+      <c r="K617" s="4" t="inlineStr"/>
+      <c r="L617" s="4" t="n"/>
+      <c r="M617" s="4" t="n"/>
+      <c r="N617" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O617" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P617" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q617" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R617" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S617" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T617" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U617" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V617" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W617" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X617" s="4" t="n"/>
+      <c r="Y617" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z617" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA617" s="4" t="n"/>
+      <c r="AB617" s="4" t="n"/>
+      <c r="AC617" s="4" t="n"/>
+      <c r="AD617" s="4" t="n"/>
+      <c r="AE617" s="4" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B618" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C618" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D618" s="6" t="inlineStr">
+        <is>
+          <t>2 Kg</t>
+        </is>
+      </c>
+      <c r="E618" s="6" t="n"/>
+      <c r="F618" s="6" t="n"/>
+      <c r="G618" s="6" t="n"/>
+      <c r="H618" s="6" t="n"/>
+      <c r="I618" s="6" t="inlineStr"/>
+      <c r="J618" s="6" t="inlineStr"/>
+      <c r="K618" s="6" t="inlineStr"/>
+      <c r="L618" s="6" t="n"/>
+      <c r="M618" s="6" t="n"/>
+      <c r="N618" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O618" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P618" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q618" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R618" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S618" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T618" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U618" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V618" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W618" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X618" s="6" t="n"/>
+      <c r="Y618" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z618" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA618" s="6" t="n"/>
+      <c r="AB618" s="6" t="n"/>
+      <c r="AC618" s="6" t="n"/>
+      <c r="AD618" s="6" t="n"/>
+      <c r="AE618" s="6" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B619" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C619" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D619" s="4" t="inlineStr">
+        <is>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="E619" s="4" t="n"/>
+      <c r="F619" s="4" t="n"/>
+      <c r="G619" s="4" t="n"/>
+      <c r="H619" s="4" t="n"/>
+      <c r="I619" s="4" t="inlineStr"/>
+      <c r="J619" s="4" t="inlineStr"/>
+      <c r="K619" s="4" t="inlineStr"/>
+      <c r="L619" s="4" t="n"/>
+      <c r="M619" s="4" t="n"/>
+      <c r="N619" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O619" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P619" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q619" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R619" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S619" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T619" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U619" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V619" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W619" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X619" s="4" t="n"/>
+      <c r="Y619" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z619" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA619" s="4" t="n"/>
+      <c r="AB619" s="4" t="n"/>
+      <c r="AC619" s="4" t="n"/>
+      <c r="AD619" s="4" t="n"/>
+      <c r="AE619" s="4" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B620" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C620" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D620" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E620" s="6" t="n"/>
+      <c r="F620" s="6" t="n"/>
+      <c r="G620" s="6" t="n"/>
+      <c r="H620" s="6" t="n"/>
+      <c r="I620" s="6" t="inlineStr"/>
+      <c r="J620" s="6" t="inlineStr"/>
+      <c r="K620" s="6" t="inlineStr"/>
+      <c r="L620" s="6" t="n"/>
+      <c r="M620" s="6" t="n"/>
+      <c r="N620" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O620" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P620" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q620" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R620" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S620" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T620" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U620" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V620" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W620" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X620" s="6" t="n"/>
+      <c r="Y620" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z620" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA620" s="6" t="n"/>
+      <c r="AB620" s="6" t="n"/>
+      <c r="AC620" s="6" t="n"/>
+      <c r="AD620" s="6" t="n"/>
+      <c r="AE620" s="6" t="n"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B621" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C621" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D621" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E621" s="4" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="F621" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G621" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H621" s="4" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="I621" s="4" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J621" s="4" t="inlineStr"/>
+      <c r="K621" s="4" t="inlineStr"/>
+      <c r="L621" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M621" s="4" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N621" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O621" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="P621" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q621" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R621" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S621" s="4" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T621" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U621" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V621" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W621" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X621" s="4" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="Y621" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z621" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA621" s="4" t="n"/>
+      <c r="AB621" s="4" t="n"/>
+      <c r="AC621" s="4" t="n"/>
+      <c r="AD621" s="4" t="n"/>
+      <c r="AE621" s="4" t="n"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B622" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C622" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D622" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E622" s="6" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="F622" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G622" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H622" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I622" s="6" t="inlineStr">
+        <is>
+          <t>29/08/2027</t>
+        </is>
+      </c>
+      <c r="J622" s="6" t="inlineStr"/>
+      <c r="K622" s="6" t="inlineStr"/>
+      <c r="L622" s="6" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="M622" s="6" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="N622" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O622" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="P622" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q622" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R622" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S622" s="6" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T622" s="6" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U622" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V622" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W622" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X622" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Y622" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z622" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA622" s="6" t="n"/>
+      <c r="AB622" s="6" t="n"/>
+      <c r="AC622" s="6" t="n"/>
+      <c r="AD622" s="6" t="n"/>
+      <c r="AE622" s="6" t="n"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C623" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D623" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E623" s="4" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F623" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G623" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H623" s="4" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I623" s="4" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
+      <c r="J623" s="4" t="inlineStr"/>
+      <c r="K623" s="4" t="inlineStr"/>
+      <c r="L623" s="4" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="M623" s="4" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="N623" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O623" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P623" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q623" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R623" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S623" s="4" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T623" s="4" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U623" s="4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V623" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W623" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X623" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y623" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z623" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA623" s="4" t="n"/>
+      <c r="AB623" s="4" t="n"/>
+      <c r="AC623" s="4" t="n"/>
+      <c r="AD623" s="4" t="n"/>
+      <c r="AE623" s="4" t="n"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B624" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D624" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E624" s="6" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="F624" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G624" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H624" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="I624" s="6" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J624" s="6" t="inlineStr"/>
+      <c r="K624" s="6" t="inlineStr"/>
+      <c r="L624" s="6" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M624" s="6" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="N624" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O624" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="P624" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q624" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R624" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S624" s="6" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T624" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U624" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V624" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W624" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X624" s="6" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="Y624" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z624" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA624" s="6" t="n"/>
+      <c r="AB624" s="6" t="n"/>
+      <c r="AC624" s="6" t="n"/>
+      <c r="AD624" s="6" t="n"/>
+      <c r="AE624" s="6" t="n"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C625" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D625" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E625" s="4" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F625" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G625" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H625" s="4" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I625" s="4" t="inlineStr">
+        <is>
+          <t>06/10/2027</t>
+        </is>
+      </c>
+      <c r="J625" s="4" t="inlineStr"/>
+      <c r="K625" s="4" t="inlineStr"/>
+      <c r="L625" s="4" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="M625" s="4" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="N625" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O625" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P625" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q625" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R625" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S625" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T625" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U625" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V625" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W625" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X625" s="4" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="Y625" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z625" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA625" s="4" t="n"/>
+      <c r="AB625" s="4" t="n"/>
+      <c r="AC625" s="4" t="n"/>
+      <c r="AD625" s="4" t="n"/>
+      <c r="AE625" s="4" t="n"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B626" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C626" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D626" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E626" s="6" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F626" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G626" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H626" s="6" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I626" s="6" t="n"/>
+      <c r="J626" s="6" t="inlineStr"/>
+      <c r="K626" s="6" t="inlineStr"/>
+      <c r="L626" s="6" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="M626" s="6" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="N626" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O626" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P626" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q626" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R626" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S626" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T626" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U626" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V626" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W626" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X626" s="6" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="Y626" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z626" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA626" s="6" t="n"/>
+      <c r="AB626" s="6" t="n"/>
+      <c r="AC626" s="6" t="n"/>
+      <c r="AD626" s="6" t="n"/>
+      <c r="AE626" s="6" t="n"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B627" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C627" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D627" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E627" s="4" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="F627" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G627" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H627" s="4" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I627" s="4" t="inlineStr">
+        <is>
+          <t>25/08/2027</t>
+        </is>
+      </c>
+      <c r="J627" s="4" t="inlineStr"/>
+      <c r="K627" s="4" t="inlineStr"/>
+      <c r="L627" s="4" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="M627" s="4" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="N627" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O627" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P627" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q627" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R627" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S627" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T627" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U627" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V627" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W627" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X627" s="4" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="Y627" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z627" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA627" s="4" t="n"/>
+      <c r="AB627" s="4" t="n"/>
+      <c r="AC627" s="4" t="n"/>
+      <c r="AD627" s="4" t="n"/>
+      <c r="AE627" s="4" t="n"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B628" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D628" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E628" s="6" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F628" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G628" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H628" s="6" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="I628" s="6" t="inlineStr">
+        <is>
+          <t>20/03/2028</t>
+        </is>
+      </c>
+      <c r="J628" s="6" t="inlineStr"/>
+      <c r="K628" s="6" t="inlineStr"/>
+      <c r="L628" s="6" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M628" s="6" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N628" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="O628" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="P628" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q628" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R628" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S628" s="6" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T628" s="6" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U628" s="6" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V628" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W628" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X628" s="6" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="Y628" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z628" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA628" s="6" t="n"/>
+      <c r="AB628" s="6" t="n"/>
+      <c r="AC628" s="6" t="n"/>
+      <c r="AD628" s="6" t="n"/>
+      <c r="AE628" s="6" t="n"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B629" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C629" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D629" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E629" s="4" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F629" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G629" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H629" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="I629" s="4" t="inlineStr">
+        <is>
+          <t>29/01/2028</t>
+        </is>
+      </c>
+      <c r="J629" s="4" t="inlineStr"/>
+      <c r="K629" s="4" t="inlineStr"/>
+      <c r="L629" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M629" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N629" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O629" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="P629" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q629" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R629" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S629" s="4" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T629" s="4" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U629" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V629" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W629" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X629" s="4" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="Y629" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z629" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA629" s="4" t="n"/>
+      <c r="AB629" s="4" t="n"/>
+      <c r="AC629" s="4" t="n"/>
+      <c r="AD629" s="4" t="n"/>
+      <c r="AE629" s="4" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B630" s="5" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C630" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D630" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E630" s="6" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F630" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G630" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H630" s="6" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="I630" s="6" t="inlineStr">
+        <is>
+          <t>23/04/2027</t>
+        </is>
+      </c>
+      <c r="J630" s="6" t="inlineStr"/>
+      <c r="K630" s="6" t="inlineStr"/>
+      <c r="L630" s="6" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="M630" s="6" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="N630" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O630" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="P630" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q630" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R630" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S630" s="6" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T630" s="6" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U630" s="6" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V630" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W630" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X630" s="6" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="Y630" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z630" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA630" s="6" t="n"/>
+      <c r="AB630" s="6" t="n"/>
+      <c r="AC630" s="6" t="n"/>
+      <c r="AD630" s="6" t="n"/>
+      <c r="AE630" s="6" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B631" s="3" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D631" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E631" s="4" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="F631" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G631" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H631" s="4" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I631" s="4" t="inlineStr">
+        <is>
+          <t>10/04/2028</t>
+        </is>
+      </c>
+      <c r="J631" s="4" t="inlineStr"/>
+      <c r="K631" s="4" t="inlineStr"/>
+      <c r="L631" s="4" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="M631" s="4" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N631" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O631" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="P631" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q631" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R631" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S631" s="4" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T631" s="4" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U631" s="4" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V631" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W631" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X631" s="4" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Y631" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z631" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA631" s="4" t="n"/>
+      <c r="AB631" s="4" t="n"/>
+      <c r="AC631" s="4" t="n"/>
+      <c r="AD631" s="4" t="n"/>
+      <c r="AE631" s="4" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B632" s="5" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D632" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E632" s="6" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F632" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G632" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H632" s="6" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I632" s="6" t="inlineStr">
+        <is>
+          <t>23/09/2027</t>
+        </is>
+      </c>
+      <c r="J632" s="6" t="inlineStr"/>
+      <c r="K632" s="6" t="inlineStr"/>
+      <c r="L632" s="6" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="M632" s="6" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N632" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O632" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="P632" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q632" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R632" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S632" s="6" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T632" s="6" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U632" s="6" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V632" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W632" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X632" s="6" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="Y632" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z632" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA632" s="6" t="n"/>
+      <c r="AB632" s="6" t="n"/>
+      <c r="AC632" s="6" t="n"/>
+      <c r="AD632" s="6" t="n"/>
+      <c r="AE632" s="6" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D633" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E633" s="4" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F633" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="G633" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H633" s="4" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="I633" s="4" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="J633" s="4" t="inlineStr"/>
+      <c r="K633" s="4" t="inlineStr"/>
+      <c r="L633" s="4" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M633" s="4" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="N633" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O633" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="P633" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q633" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R633" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S633" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T633" s="4" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U633" s="4" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V633" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W633" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X633" s="4" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="Y633" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z633" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA633" s="4" t="n"/>
+      <c r="AB633" s="4" t="n"/>
+      <c r="AC633" s="4" t="n"/>
+      <c r="AD633" s="4" t="n"/>
+      <c r="AE633" s="4" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B634" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C634" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D634" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E634" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F634" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G634" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H634" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I634" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J634" s="6" t="inlineStr"/>
+      <c r="K634" s="6" t="inlineStr"/>
+      <c r="L634" s="6" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="M634" s="6" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N634" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O634" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P634" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q634" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R634" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S634" s="6" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T634" s="6" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U634" s="6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V634" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W634" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X634" s="6" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="Y634" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z634" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA634" s="6" t="n"/>
+      <c r="AB634" s="6" t="n"/>
+      <c r="AC634" s="6" t="n"/>
+      <c r="AD634" s="6" t="n"/>
+      <c r="AE634" s="6" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D635" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E635" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F635" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G635" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H635" s="4" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I635" s="4" t="inlineStr">
+        <is>
+          <t>09/04/2028</t>
+        </is>
+      </c>
+      <c r="J635" s="4" t="inlineStr"/>
+      <c r="K635" s="4" t="inlineStr"/>
+      <c r="L635" s="4" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="M635" s="4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N635" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O635" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P635" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q635" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R635" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S635" s="4" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T635" s="4" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U635" s="4" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V635" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W635" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X635" s="4" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="Y635" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z635" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA635" s="4" t="n"/>
+      <c r="AB635" s="4" t="n"/>
+      <c r="AC635" s="4" t="n"/>
+      <c r="AD635" s="4" t="n"/>
+      <c r="AE635" s="4" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B636" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C636" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D636" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E636" s="6" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F636" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G636" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H636" s="6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I636" s="6" t="inlineStr">
+        <is>
+          <t>21/04/2028</t>
+        </is>
+      </c>
+      <c r="J636" s="6" t="inlineStr"/>
+      <c r="K636" s="6" t="inlineStr"/>
+      <c r="L636" s="6" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="M636" s="6" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="N636" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O636" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="P636" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q636" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R636" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S636" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T636" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U636" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V636" s="6" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W636" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 4789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 3904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X636" s="6" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="Y636" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z636" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA636" s="6" t="n"/>
+      <c r="AB636" s="6" t="n"/>
+      <c r="AC636" s="6" t="n"/>
+      <c r="AD636" s="6" t="n"/>
+      <c r="AE636" s="6" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B637" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C637" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D637" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E637" s="4" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F637" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G637" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H637" s="4" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="I637" s="4" t="n"/>
+      <c r="J637" s="4" t="inlineStr"/>
+      <c r="K637" s="4" t="inlineStr"/>
+      <c r="L637" s="4" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="M637" s="4" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="N637" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O637" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="P637" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q637" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R637" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S637" s="4" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T637" s="4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U637" s="4" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V637" s="4" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W637" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 4789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 3904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X637" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y637" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z637" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA637" s="4" t="n"/>
+      <c r="AB637" s="4" t="n"/>
+      <c r="AC637" s="4" t="n"/>
+      <c r="AD637" s="4" t="n"/>
+      <c r="AE637" s="4" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B638" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 30HD</t>
+        </is>
+      </c>
+      <c r="C638" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+        </is>
+      </c>
+      <c r="D638" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E638" s="6" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F638" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G638" s="6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H638" s="6" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I638" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J638" s="6" t="inlineStr"/>
+      <c r="K638" s="6" t="inlineStr"/>
+      <c r="L638" s="6" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M638" s="6" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="N638" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O638" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="P638" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q638" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R638" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S638" s="6" t="n">
+        <v>7170</v>
+      </c>
+      <c r="T638" s="6" t="n">
+        <v>3857</v>
+      </c>
+      <c r="U638" s="6" t="n">
+        <v>3903</v>
+      </c>
+      <c r="V638" s="6" t="inlineStr">
+        <is>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W638" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+        </is>
+      </c>
+      <c r="X638" s="6" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="Y638" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z638" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA638" s="6" t="n"/>
+      <c r="AB638" s="6" t="n"/>
+      <c r="AC638" s="6" t="n"/>
+      <c r="AD638" s="6" t="n"/>
+      <c r="AE638" s="6" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B639" s="3" t="inlineStr">
+        <is>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+        </is>
+      </c>
+      <c r="D639" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E639" s="4" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="F639" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G639" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H639" s="4" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="I639" s="4" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J639" s="4" t="inlineStr"/>
+      <c r="K639" s="4" t="inlineStr"/>
+      <c r="L639" s="4" t="n">
+        <v>120.68</v>
+      </c>
+      <c r="M639" s="4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N639" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O639" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="P639" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q639" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R639" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S639" s="4" t="n">
+        <v>6681</v>
+      </c>
+      <c r="T639" s="4" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U639" s="4" t="n">
+        <v>4543</v>
+      </c>
+      <c r="V639" s="4" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+        </is>
+      </c>
+      <c r="W639" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+        </is>
+      </c>
+      <c r="X639" s="4" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="Y639" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z639" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA639" s="4" t="n"/>
+      <c r="AB639" s="4" t="n"/>
+      <c r="AC639" s="4" t="n"/>
+      <c r="AD639" s="4" t="n"/>
+      <c r="AE639" s="4" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B640" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C640" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D640" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E640" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F640" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G640" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H640" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I640" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J640" s="6" t="inlineStr"/>
+      <c r="K640" s="6" t="inlineStr"/>
+      <c r="L640" s="6" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="M640" s="6" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="N640" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="O640" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="P640" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q640" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="R640" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S640" s="6" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T640" s="6" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U640" s="6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V640" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W640" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X640" s="6" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="Y640" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z640" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA640" s="6" t="n"/>
+      <c r="AB640" s="6" t="n"/>
+      <c r="AC640" s="6" t="n"/>
+      <c r="AD640" s="6" t="n"/>
+      <c r="AE640" s="6" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D641" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E641" s="4" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="F641" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G641" s="4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H641" s="4" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="I641" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J641" s="4" t="inlineStr"/>
+      <c r="K641" s="4" t="inlineStr"/>
+      <c r="L641" s="4" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="M641" s="4" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="N641" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="O641" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="P641" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q641" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R641" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S641" s="4" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T641" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U641" s="4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V641" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W641" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X641" s="4" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Y641" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z641" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA641" s="4" t="n"/>
+      <c r="AB641" s="4" t="n"/>
+      <c r="AC641" s="4" t="n"/>
+      <c r="AD641" s="4" t="n"/>
+      <c r="AE641" s="4" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B642" s="5" t="inlineStr">
+        <is>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C642" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+        </is>
+      </c>
+      <c r="D642" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E642" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F642" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G642" s="6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H642" s="6" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I642" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J642" s="6" t="inlineStr"/>
+      <c r="K642" s="6" t="inlineStr"/>
+      <c r="L642" s="6" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="M642" s="6" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="N642" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O642" s="6" t="n">
+        <v>349</v>
+      </c>
+      <c r="P642" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q642" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R642" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S642" s="6" t="n">
+        <v>7812</v>
+      </c>
+      <c r="T642" s="6" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U642" s="6" t="n">
+        <v>5312</v>
+      </c>
+      <c r="V642" s="6" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait).</t>
+        </is>
+      </c>
+      <c r="W642" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+        </is>
+      </c>
+      <c r="X642" s="6" t="n">
+        <v>3.396</v>
+      </c>
+      <c r="Y642" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z642" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA642" s="6" t="n"/>
+      <c r="AB642" s="6" t="n"/>
+      <c r="AC642" s="6" t="n"/>
+      <c r="AD642" s="6" t="n"/>
+      <c r="AE642" s="6" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D643" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E643" s="4" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F643" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G643" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H643" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I643" s="4" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J643" s="4" t="inlineStr"/>
+      <c r="K643" s="4" t="inlineStr"/>
+      <c r="L643" s="4" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M643" s="4" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N643" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="O643" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="P643" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q643" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R643" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S643" s="4" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T643" s="4" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U643" s="4" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V643" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W643" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X643" s="4" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Y643" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z643" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA643" s="4" t="n"/>
+      <c r="AB643" s="4" t="n"/>
+      <c r="AC643" s="4" t="n"/>
+      <c r="AD643" s="4" t="n"/>
+      <c r="AE643" s="4" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B644" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C644" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D644" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E644" s="6" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F644" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G644" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H644" s="6" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I644" s="6" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
+      <c r="J644" s="6" t="inlineStr"/>
+      <c r="K644" s="6" t="inlineStr"/>
+      <c r="L644" s="6" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="M644" s="6" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N644" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="O644" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="P644" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q644" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R644" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S644" s="6" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T644" s="6" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U644" s="6" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V644" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W644" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X644" s="6" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="Y644" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z644" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA644" s="6" t="n"/>
+      <c r="AB644" s="6" t="n"/>
+      <c r="AC644" s="6" t="n"/>
+      <c r="AD644" s="6" t="n"/>
+      <c r="AE644" s="6" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D645" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E645" s="4" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F645" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G645" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H645" s="4" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I645" s="4" t="inlineStr">
+        <is>
+          <t>17/11/2027</t>
+        </is>
+      </c>
+      <c r="J645" s="4" t="inlineStr"/>
+      <c r="K645" s="4" t="inlineStr"/>
+      <c r="L645" s="4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="M645" s="4" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="N645" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="O645" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="P645" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q645" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R645" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S645" s="4" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T645" s="4" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U645" s="4" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V645" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W645" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X645" s="4" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="Y645" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z645" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA645" s="4" t="n"/>
+      <c r="AB645" s="4" t="n"/>
+      <c r="AC645" s="4" t="n"/>
+      <c r="AD645" s="4" t="n"/>
+      <c r="AE645" s="4" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B646" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C646" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D646" s="6" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E646" s="6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F646" s="6" t="n"/>
+      <c r="G646" s="6" t="n"/>
+      <c r="H646" s="6" t="n"/>
+      <c r="I646" s="6" t="inlineStr"/>
+      <c r="J646" s="6" t="inlineStr"/>
+      <c r="K646" s="6" t="inlineStr"/>
+      <c r="L646" s="6" t="n"/>
+      <c r="M646" s="6" t="n"/>
+      <c r="N646" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O646" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="P646" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q646" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R646" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S646" s="6" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T646" s="6" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U646" s="6" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V646" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W646" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X646" s="6" t="n"/>
+      <c r="Y646" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z646" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA646" s="6" t="n"/>
+      <c r="AB646" s="6" t="n"/>
+      <c r="AC646" s="6" t="n"/>
+      <c r="AD646" s="6" t="n"/>
+      <c r="AE646" s="6" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D647" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E647" s="4" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="F647" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G647" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H647" s="4" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I647" s="4" t="inlineStr">
+        <is>
+          <t>13/11/2027</t>
+        </is>
+      </c>
+      <c r="J647" s="4" t="inlineStr"/>
+      <c r="K647" s="4" t="inlineStr"/>
+      <c r="L647" s="4" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="M647" s="4" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="N647" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O647" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="P647" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q647" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R647" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S647" s="4" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T647" s="4" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U647" s="4" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V647" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W647" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X647" s="4" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="Y647" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z647" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA647" s="4" t="n"/>
+      <c r="AB647" s="4" t="n"/>
+      <c r="AC647" s="4" t="n"/>
+      <c r="AD647" s="4" t="n"/>
+      <c r="AE647" s="4" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B648" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C648" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D648" s="6" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E648" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F648" s="6" t="n"/>
+      <c r="G648" s="6" t="n"/>
+      <c r="H648" s="6" t="n"/>
+      <c r="I648" s="6" t="inlineStr"/>
+      <c r="J648" s="6" t="inlineStr"/>
+      <c r="K648" s="6" t="inlineStr"/>
+      <c r="L648" s="6" t="n"/>
+      <c r="M648" s="6" t="n"/>
+      <c r="N648" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O648" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="P648" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q648" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R648" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S648" s="6" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T648" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U648" s="6" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V648" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W648" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X648" s="6" t="n"/>
+      <c r="Y648" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z648" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA648" s="6" t="n"/>
+      <c r="AB648" s="6" t="n"/>
+      <c r="AC648" s="6" t="n"/>
+      <c r="AD648" s="6" t="n"/>
+      <c r="AE648" s="6" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D649" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E649" s="4" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F649" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G649" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H649" s="4" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="I649" s="4" t="inlineStr">
+        <is>
+          <t>28/11/2027</t>
+        </is>
+      </c>
+      <c r="J649" s="4" t="inlineStr"/>
+      <c r="K649" s="4" t="inlineStr"/>
+      <c r="L649" s="4" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="M649" s="4" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="N649" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O649" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="P649" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q649" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R649" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S649" s="4" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T649" s="4" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U649" s="4" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V649" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W649" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X649" s="4" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="Y649" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z649" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA649" s="4" t="n"/>
+      <c r="AB649" s="4" t="n"/>
+      <c r="AC649" s="4" t="n"/>
+      <c r="AD649" s="4" t="n"/>
+      <c r="AE649" s="4" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B650" s="5" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C650" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D650" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E650" s="6" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F650" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G650" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H650" s="6" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="I650" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J650" s="6" t="inlineStr"/>
+      <c r="K650" s="6" t="inlineStr"/>
+      <c r="L650" s="6" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="M650" s="6" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N650" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="O650" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="P650" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q650" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R650" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S650" s="6" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T650" s="6" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U650" s="6" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V650" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W650" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X650" s="6" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Y650" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z650" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA650" s="6" t="n"/>
+      <c r="AB650" s="6" t="n"/>
+      <c r="AC650" s="6" t="n"/>
+      <c r="AD650" s="6" t="n"/>
+      <c r="AE650" s="6" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B651" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C651" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D651" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E651" s="4" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F651" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G651" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H651" s="4" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I651" s="4" t="n"/>
+      <c r="J651" s="4" t="inlineStr"/>
+      <c r="K651" s="4" t="inlineStr"/>
+      <c r="L651" s="4" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M651" s="4" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="N651" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O651" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="P651" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q651" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R651" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S651" s="4" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T651" s="4" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U651" s="4" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V651" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W651" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X651" s="4" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="Y651" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z651" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA651" s="4" t="n"/>
+      <c r="AB651" s="4" t="n"/>
+      <c r="AC651" s="4" t="n"/>
+      <c r="AD651" s="4" t="n"/>
+      <c r="AE651" s="4" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B652" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C652" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D652" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E652" s="6" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F652" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G652" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H652" s="6" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I652" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J652" s="6" t="inlineStr"/>
+      <c r="K652" s="6" t="inlineStr"/>
+      <c r="L652" s="6" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M652" s="6" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="N652" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O652" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="P652" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q652" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R652" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S652" s="6" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T652" s="6" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U652" s="6" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V652" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W652" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X652" s="6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y652" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z652" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA652" s="6" t="n"/>
+      <c r="AB652" s="6" t="n"/>
+      <c r="AC652" s="6" t="n"/>
+      <c r="AD652" s="6" t="n"/>
+      <c r="AE652" s="6" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B653" s="3" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D653" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E653" s="4" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="F653" s="4" t="n"/>
+      <c r="G653" s="4" t="n"/>
+      <c r="H653" s="4" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="I653" s="4" t="inlineStr"/>
+      <c r="J653" s="4" t="inlineStr"/>
+      <c r="K653" s="4" t="inlineStr"/>
+      <c r="L653" s="4" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="M653" s="4" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="N653" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="O653" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P653" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q653" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R653" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S653" s="4" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T653" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U653" s="4" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V653" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W653" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X653" s="4" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="Y653" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z653" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA653" s="4" t="n"/>
+      <c r="AB653" s="4" t="n"/>
+      <c r="AC653" s="4" t="n"/>
+      <c r="AD653" s="4" t="n"/>
+      <c r="AE653" s="4" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B654" s="5" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C654" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D654" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E654" s="6" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F654" s="6" t="n"/>
+      <c r="G654" s="6" t="n"/>
+      <c r="H654" s="6" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="I654" s="6" t="inlineStr"/>
+      <c r="J654" s="6" t="inlineStr"/>
+      <c r="K654" s="6" t="inlineStr"/>
+      <c r="L654" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="M654" s="6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N654" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="O654" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P654" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q654" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R654" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S654" s="6" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T654" s="6" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U654" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V654" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W654" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X654" s="6" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="Y654" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z654" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA654" s="6" t="n"/>
+      <c r="AB654" s="6" t="n"/>
+      <c r="AC654" s="6" t="n"/>
+      <c r="AD654" s="6" t="n"/>
+      <c r="AE654" s="6" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B655" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C655" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D655" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E655" s="4" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="F655" s="4" t="n"/>
+      <c r="G655" s="4" t="n"/>
+      <c r="H655" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I655" s="4" t="inlineStr"/>
+      <c r="J655" s="4" t="inlineStr"/>
+      <c r="K655" s="4" t="inlineStr"/>
+      <c r="L655" s="4" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="M655" s="4" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="N655" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="O655" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="P655" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q655" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R655" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S655" s="4" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T655" s="4" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U655" s="4" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V655" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W655" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X655" s="4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="Y655" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z655" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA655" s="4" t="n"/>
+      <c r="AB655" s="4" t="n"/>
+      <c r="AC655" s="4" t="n"/>
+      <c r="AD655" s="4" t="n"/>
+      <c r="AE655" s="4" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B656" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C656" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D656" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E656" s="6" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="F656" s="6" t="n"/>
+      <c r="G656" s="6" t="n"/>
+      <c r="H656" s="6" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="I656" s="6" t="inlineStr"/>
+      <c r="J656" s="6" t="inlineStr"/>
+      <c r="K656" s="6" t="inlineStr"/>
+      <c r="L656" s="6" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="M656" s="6" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="N656" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="O656" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="P656" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q656" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R656" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S656" s="6" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T656" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U656" s="6" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V656" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W656" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X656" s="6" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="Y656" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z656" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA656" s="6" t="n"/>
+      <c r="AB656" s="6" t="n"/>
+      <c r="AC656" s="6" t="n"/>
+      <c r="AD656" s="6" t="n"/>
+      <c r="AE656" s="6" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B657" s="3" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C657" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D657" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E657" s="4" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="F657" s="4" t="n"/>
+      <c r="G657" s="4" t="n"/>
+      <c r="H657" s="4" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="I657" s="4" t="inlineStr"/>
+      <c r="J657" s="4" t="inlineStr"/>
+      <c r="K657" s="4" t="inlineStr"/>
+      <c r="L657" s="4" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="M657" s="4" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="N657" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O657" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="P657" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q657" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R657" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S657" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T657" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U657" s="4" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V657" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W657" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X657" s="4" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Y657" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z657" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA657" s="4" t="n"/>
+      <c r="AB657" s="4" t="n"/>
+      <c r="AC657" s="4" t="n"/>
+      <c r="AD657" s="4" t="n"/>
+      <c r="AE657" s="4" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B658" s="5" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C658" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D658" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E658" s="6" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F658" s="6" t="n"/>
+      <c r="G658" s="6" t="n"/>
+      <c r="H658" s="6" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="I658" s="6" t="inlineStr"/>
+      <c r="J658" s="6" t="inlineStr"/>
+      <c r="K658" s="6" t="inlineStr"/>
+      <c r="L658" s="6" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="M658" s="6" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="N658" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O658" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="P658" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q658" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R658" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S658" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T658" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U658" s="6" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V658" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W658" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X658" s="6" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="Y658" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z658" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA658" s="6" t="n"/>
+      <c r="AB658" s="6" t="n"/>
+      <c r="AC658" s="6" t="n"/>
+      <c r="AD658" s="6" t="n"/>
+      <c r="AE658" s="6" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B659" s="3" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C659" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D659" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E659" s="4" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="F659" s="4" t="n"/>
+      <c r="G659" s="4" t="n"/>
+      <c r="H659" s="4" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="I659" s="4" t="inlineStr"/>
+      <c r="J659" s="4" t="inlineStr"/>
+      <c r="K659" s="4" t="inlineStr"/>
+      <c r="L659" s="4" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="M659" s="4" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="N659" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O659" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="P659" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q659" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R659" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S659" s="4" t="n"/>
+      <c r="T659" s="4" t="n"/>
+      <c r="U659" s="4" t="n"/>
+      <c r="V659" s="4" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W659" s="4" t="inlineStr"/>
+      <c r="X659" s="4" t="n"/>
+      <c r="Y659" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z659" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA659" s="4" t="n"/>
+      <c r="AB659" s="4" t="n"/>
+      <c r="AC659" s="4" t="n"/>
+      <c r="AD659" s="4" t="n"/>
+      <c r="AE659" s="4" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B660" s="5" t="inlineStr">
+        <is>
+          <t>SMOOTHIE PROTÉINÉ AU COLLAGÈNE</t>
+        </is>
+      </c>
+      <c r="C660" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/smoothie-proteine-au-collagene</t>
+        </is>
+      </c>
+      <c r="D660" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E660" s="6" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F660" s="6" t="n"/>
+      <c r="G660" s="6" t="n"/>
+      <c r="H660" s="6" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="I660" s="6" t="inlineStr"/>
+      <c r="J660" s="6" t="inlineStr"/>
+      <c r="K660" s="6" t="inlineStr"/>
+      <c r="L660" s="6" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="M660" s="6" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="N660" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O660" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="P660" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q660" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R660" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S660" s="6" t="n"/>
+      <c r="T660" s="6" t="n"/>
+      <c r="U660" s="6" t="n"/>
+      <c r="V660" s="6" t="inlineStr">
+        <is>
+          <t>Collagène bovin hydrolysé, concentré de protéines de lactosérum de lait, édulcorant (érythritol), isolat de protéines de lait, jus de pomme concentré en poudre, farine de riz, eau de coco en poudre (de Cocos nucifera), arôme naturel, épaississant (gomme xanthane), extrait d'acérola (15:1, de baie de Malpighia glabra, 25% de vitamine C), jus de cassis concentré en poudre, jus de fraise concentré en poudre, framboise en poudre, colorant (rouge de betterave), édulcorant (glycosides de stéviol provenant de la stévia), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W660" s="6" t="inlineStr"/>
+      <c r="X660" s="6" t="n"/>
+      <c r="Y660" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z660" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA660" s="6" t="n"/>
+      <c r="AB660" s="6" t="n"/>
+      <c r="AC660" s="6" t="n"/>
+      <c r="AD660" s="6" t="n"/>
+      <c r="AE660" s="6" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C661" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D661" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E661" s="4" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F661" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G661" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H661" s="4" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="I661" s="4" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J661" s="4" t="inlineStr"/>
+      <c r="K661" s="4" t="inlineStr"/>
+      <c r="L661" s="4" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="M661" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N661" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O661" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="P661" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q661" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R661" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S661" s="4" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T661" s="4" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U661" s="4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V661" s="4" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W661" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X661" s="4" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="Y661" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z661" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA661" s="4" t="n"/>
+      <c r="AB661" s="4" t="n"/>
+      <c r="AC661" s="4" t="n"/>
+      <c r="AD661" s="4" t="n"/>
+      <c r="AE661" s="4" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B662" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C662" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D662" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E662" s="6" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="F662" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G662" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H662" s="6" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="I662" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2028</t>
+        </is>
+      </c>
+      <c r="J662" s="6" t="inlineStr"/>
+      <c r="K662" s="6" t="inlineStr"/>
+      <c r="L662" s="6" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="M662" s="6" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="N662" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O662" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="P662" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q662" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R662" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S662" s="6" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T662" s="6" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U662" s="6" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V662" s="6" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W662" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X662" s="6" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="Y662" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z662" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA662" s="6" t="n"/>
+      <c r="AB662" s="6" t="n"/>
+      <c r="AC662" s="6" t="n"/>
+      <c r="AD662" s="6" t="n"/>
+      <c r="AE662" s="6" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C663" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D663" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E663" s="4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F663" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G663" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H663" s="4" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I663" s="4" t="inlineStr">
+        <is>
+          <t>23/01/2028</t>
+        </is>
+      </c>
+      <c r="J663" s="4" t="inlineStr"/>
+      <c r="K663" s="4" t="inlineStr"/>
+      <c r="L663" s="4" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="M663" s="4" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="N663" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O663" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P663" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q663" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R663" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S663" s="4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T663" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U663" s="4" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V663" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W663" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X663" s="4" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="Y663" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z663" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA663" s="4" t="n"/>
+      <c r="AB663" s="4" t="n"/>
+      <c r="AC663" s="4" t="n"/>
+      <c r="AD663" s="4" t="n"/>
+      <c r="AE663" s="4" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B664" s="5" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C664" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D664" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E664" s="6" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="F664" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G664" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H664" s="6" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I664" s="6" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
+      <c r="J664" s="6" t="inlineStr"/>
+      <c r="K664" s="6" t="inlineStr"/>
+      <c r="L664" s="6" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="M664" s="6" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="N664" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O664" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P664" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q664" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R664" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S664" s="6" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T664" s="6" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U664" s="6" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V664" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W664" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X664" s="6" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="Y664" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z664" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA664" s="6" t="n"/>
+      <c r="AB664" s="6" t="n"/>
+      <c r="AC664" s="6" t="n"/>
+      <c r="AD664" s="6" t="n"/>
+      <c r="AE664" s="6" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D665" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E665" s="4" t="n"/>
+      <c r="F665" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G665" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H665" s="4" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="I665" s="4" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J665" s="4" t="inlineStr"/>
+      <c r="K665" s="4" t="inlineStr"/>
+      <c r="L665" s="4" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="M665" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N665" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O665" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="P665" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q665" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R665" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S665" s="4" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T665" s="4" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U665" s="4" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V665" s="4" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W665" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X665" s="4" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="Y665" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z665" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA665" s="4" t="n"/>
+      <c r="AB665" s="4" t="n"/>
+      <c r="AC665" s="4" t="n"/>
+      <c r="AD665" s="4" t="n"/>
+      <c r="AE665" s="4" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B666" s="5" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C666" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D666" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E666" s="6" t="n"/>
+      <c r="F666" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G666" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H666" s="6" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I666" s="6" t="n"/>
+      <c r="J666" s="6" t="inlineStr"/>
+      <c r="K666" s="6" t="inlineStr"/>
+      <c r="L666" s="6" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M666" s="6" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N666" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O666" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="P666" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q666" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R666" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S666" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T666" s="6" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U666" s="6" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V666" s="6" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W666" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X666" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y666" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z666" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA666" s="6" t="n"/>
+      <c r="AB666" s="6" t="n"/>
+      <c r="AC666" s="6" t="n"/>
+      <c r="AD666" s="6" t="n"/>
+      <c r="AE666" s="6" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D667" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E667" s="4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F667" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G667" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H667" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I667" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J667" s="4" t="inlineStr"/>
+      <c r="K667" s="4" t="inlineStr"/>
+      <c r="L667" s="4" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="M667" s="4" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N667" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O667" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="P667" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q667" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R667" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S667" s="4" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T667" s="4" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U667" s="4" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V667" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W667" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X667" s="4" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="Y667" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z667" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA667" s="4" t="n"/>
+      <c r="AB667" s="4" t="n"/>
+      <c r="AC667" s="4" t="n"/>
+      <c r="AD667" s="4" t="n"/>
+      <c r="AE667" s="4" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B668" s="5" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C668" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D668" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E668" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F668" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G668" s="6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H668" s="6" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="I668" s="6" t="inlineStr">
+        <is>
+          <t>30/10/2027</t>
+        </is>
+      </c>
+      <c r="J668" s="6" t="inlineStr"/>
+      <c r="K668" s="6" t="inlineStr"/>
+      <c r="L668" s="6" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="M668" s="6" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="N668" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O668" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="P668" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q668" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R668" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S668" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T668" s="6" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U668" s="6" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V668" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W668" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X668" s="6" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="Y668" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z668" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA668" s="6" t="n"/>
+      <c r="AB668" s="6" t="n"/>
+      <c r="AC668" s="6" t="n"/>
+      <c r="AD668" s="6" t="n"/>
+      <c r="AE668" s="6" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D669" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E669" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F669" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G669" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H669" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I669" s="4" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J669" s="4" t="inlineStr"/>
+      <c r="K669" s="4" t="inlineStr"/>
+      <c r="L669" s="4" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="M669" s="4" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N669" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O669" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P669" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q669" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R669" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S669" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T669" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U669" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V669" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W669" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X669" s="4" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="Y669" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z669" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA669" s="4" t="n"/>
+      <c r="AB669" s="4" t="n"/>
+      <c r="AC669" s="4" t="n"/>
+      <c r="AD669" s="4" t="n"/>
+      <c r="AE669" s="4" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B670" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C670" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D670" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E670" s="6" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="F670" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G670" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H670" s="6" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="I670" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J670" s="6" t="inlineStr"/>
+      <c r="K670" s="6" t="inlineStr"/>
+      <c r="L670" s="6" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="M670" s="6" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="N670" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O670" s="6" t="n">
+        <v>384</v>
+      </c>
+      <c r="P670" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q670" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R670" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S670" s="6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T670" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U670" s="6" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V670" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W670" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X670" s="6" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="Y670" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z670" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA670" s="6" t="n"/>
+      <c r="AB670" s="6" t="n"/>
+      <c r="AC670" s="6" t="n"/>
+      <c r="AD670" s="6" t="n"/>
+      <c r="AE670" s="6" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D671" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E671" s="4" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="F671" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G671" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H671" s="4" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="I671" s="4" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J671" s="4" t="inlineStr"/>
+      <c r="K671" s="4" t="inlineStr"/>
+      <c r="L671" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="M671" s="4" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="N671" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O671" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P671" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q671" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R671" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S671" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T671" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U671" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V671" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W671" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X671" s="4" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="Y671" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z671" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA671" s="4" t="n"/>
+      <c r="AB671" s="4" t="n"/>
+      <c r="AC671" s="4" t="n"/>
+      <c r="AD671" s="4" t="n"/>
+      <c r="AE671" s="4" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B672" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C672" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D672" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E672" s="6" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F672" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G672" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H672" s="6" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="I672" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J672" s="6" t="inlineStr"/>
+      <c r="K672" s="6" t="inlineStr"/>
+      <c r="L672" s="6" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="M672" s="6" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="N672" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O672" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="P672" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q672" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R672" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S672" s="6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T672" s="6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U672" s="6" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V672" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W672" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X672" s="6" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="Y672" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z672" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA672" s="6" t="n"/>
+      <c r="AB672" s="6" t="n"/>
+      <c r="AC672" s="6" t="n"/>
+      <c r="AD672" s="6" t="n"/>
+      <c r="AE672" s="6" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>PREMIUM OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/premium-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D673" s="4" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E673" s="4" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F673" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G673" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H673" s="4" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="I673" s="4" t="inlineStr">
+        <is>
+          <t>12/01/2029</t>
+        </is>
+      </c>
+      <c r="J673" s="4" t="inlineStr"/>
+      <c r="K673" s="4" t="inlineStr"/>
+      <c r="L673" s="4" t="n"/>
+      <c r="M673" s="4" t="n"/>
+      <c r="N673" s="4" t="n"/>
+      <c r="O673" s="4" t="n"/>
+      <c r="P673" s="4" t="n"/>
+      <c r="Q673" s="4" t="n"/>
+      <c r="R673" s="4" t="n"/>
+      <c r="S673" s="4" t="n"/>
+      <c r="T673" s="4" t="n"/>
+      <c r="U673" s="4" t="n"/>
+      <c r="V673" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 50 % acide eicosapentaénoïque (EPA), 25 % acide docosahexaénoïque (DHA)], gélatine, humectant (glycérine).</t>
+        </is>
+      </c>
+      <c r="W673" s="4" t="inlineStr"/>
+      <c r="X673" s="4" t="n"/>
+      <c r="Y673" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z673" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA673" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB673" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC673" s="4" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AD673" s="4" t="n"/>
+      <c r="AE673" s="4" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B674" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C674" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/premium-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D674" s="6" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E674" s="6" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="F674" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="G674" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H674" s="6" t="n">
+        <v>193.58</v>
+      </c>
+      <c r="I674" s="6" t="n"/>
+      <c r="J674" s="6" t="inlineStr"/>
+      <c r="K674" s="6" t="inlineStr"/>
+      <c r="L674" s="6" t="n"/>
+      <c r="M674" s="6" t="n"/>
+      <c r="N674" s="6" t="n"/>
+      <c r="O674" s="6" t="n"/>
+      <c r="P674" s="6" t="n"/>
+      <c r="Q674" s="6" t="n"/>
+      <c r="R674" s="6" t="n"/>
+      <c r="S674" s="6" t="n"/>
+      <c r="T674" s="6" t="n"/>
+      <c r="U674" s="6" t="n"/>
+      <c r="V674" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 50 % acide eicosapentaénoïque (EPA), 25 % acide docosahexaénoïque (DHA)], gélatine, humectant (glycérine).</t>
+        </is>
+      </c>
+      <c r="W674" s="6" t="inlineStr"/>
+      <c r="X674" s="6" t="n"/>
+      <c r="Y674" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z674" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA674" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB674" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC674" s="6" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AD674" s="6" t="n"/>
+      <c r="AE674" s="6" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D675" s="4" t="inlineStr">
+        <is>
+          <t>30 softgels</t>
+        </is>
+      </c>
+      <c r="E675" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F675" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G675" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H675" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I675" s="4" t="inlineStr">
+        <is>
+          <t>20/10/2028</t>
+        </is>
+      </c>
+      <c r="J675" s="4" t="inlineStr"/>
+      <c r="K675" s="4" t="inlineStr"/>
+      <c r="L675" s="4" t="n"/>
+      <c r="M675" s="4" t="n"/>
+      <c r="N675" s="4" t="n"/>
+      <c r="O675" s="4" t="n"/>
+      <c r="P675" s="4" t="n"/>
+      <c r="Q675" s="4" t="n"/>
+      <c r="R675" s="4" t="n"/>
+      <c r="S675" s="4" t="n"/>
+      <c r="T675" s="4" t="n"/>
+      <c r="U675" s="4" t="n"/>
+      <c r="V675" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W675" s="4" t="inlineStr"/>
+      <c r="X675" s="4" t="n"/>
+      <c r="Y675" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z675" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA675" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB675" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC675" s="4" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AD675" s="4" t="n"/>
+      <c r="AE675" s="4" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B676" s="5" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C676" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D676" s="6" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E676" s="6" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="F676" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G676" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H676" s="6" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="I676" s="6" t="inlineStr">
+        <is>
+          <t>05/09/2028</t>
+        </is>
+      </c>
+      <c r="J676" s="6" t="inlineStr"/>
+      <c r="K676" s="6" t="inlineStr"/>
+      <c r="L676" s="6" t="n"/>
+      <c r="M676" s="6" t="n"/>
+      <c r="N676" s="6" t="n"/>
+      <c r="O676" s="6" t="n"/>
+      <c r="P676" s="6" t="n"/>
+      <c r="Q676" s="6" t="n"/>
+      <c r="R676" s="6" t="n"/>
+      <c r="S676" s="6" t="n"/>
+      <c r="T676" s="6" t="n"/>
+      <c r="U676" s="6" t="n"/>
+      <c r="V676" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W676" s="6" t="inlineStr"/>
+      <c r="X676" s="6" t="n"/>
+      <c r="Y676" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z676" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA676" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB676" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC676" s="6" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AD676" s="6" t="n"/>
+      <c r="AE676" s="6" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D677" s="4" t="inlineStr">
+        <is>
+          <t>180 softgels</t>
+        </is>
+      </c>
+      <c r="E677" s="4" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="F677" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="G677" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H677" s="4" t="n">
+        <v>69.39</v>
+      </c>
+      <c r="I677" s="4" t="n"/>
+      <c r="J677" s="4" t="inlineStr"/>
+      <c r="K677" s="4" t="inlineStr"/>
+      <c r="L677" s="4" t="n"/>
+      <c r="M677" s="4" t="n"/>
+      <c r="N677" s="4" t="n"/>
+      <c r="O677" s="4" t="n"/>
+      <c r="P677" s="4" t="n"/>
+      <c r="Q677" s="4" t="n"/>
+      <c r="R677" s="4" t="n"/>
+      <c r="S677" s="4" t="n"/>
+      <c r="T677" s="4" t="n"/>
+      <c r="U677" s="4" t="n"/>
+      <c r="V677" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W677" s="4" t="inlineStr"/>
+      <c r="X677" s="4" t="n"/>
+      <c r="Y677" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z677" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA677" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB677" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC677" s="4" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="AD677" s="4" t="n"/>
+      <c r="AE677" s="4" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B678" s="5" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C678" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D678" s="6" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E678" s="6" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="F678" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="G678" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H678" s="6" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="I678" s="6" t="n"/>
+      <c r="J678" s="6" t="inlineStr"/>
+      <c r="K678" s="6" t="inlineStr"/>
+      <c r="L678" s="6" t="n"/>
+      <c r="M678" s="6" t="n"/>
+      <c r="N678" s="6" t="n"/>
+      <c r="O678" s="6" t="n"/>
+      <c r="P678" s="6" t="n"/>
+      <c r="Q678" s="6" t="n"/>
+      <c r="R678" s="6" t="n"/>
+      <c r="S678" s="6" t="n"/>
+      <c r="T678" s="6" t="n"/>
+      <c r="U678" s="6" t="n"/>
+      <c r="V678" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W678" s="6" t="inlineStr"/>
+      <c r="X678" s="6" t="n"/>
+      <c r="Y678" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z678" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA678" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB678" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC678" s="6" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD678" s="6" t="n"/>
+      <c r="AE678" s="6" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D679" s="4" t="inlineStr">
+        <is>
+          <t>30 softgels</t>
+        </is>
+      </c>
+      <c r="E679" s="4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="F679" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G679" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H679" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="I679" s="4" t="inlineStr">
+        <is>
+          <t>02/12/2028</t>
+        </is>
+      </c>
+      <c r="J679" s="4" t="inlineStr"/>
+      <c r="K679" s="4" t="inlineStr"/>
+      <c r="L679" s="4" t="n"/>
+      <c r="M679" s="4" t="n"/>
+      <c r="N679" s="4" t="n"/>
+      <c r="O679" s="4" t="n"/>
+      <c r="P679" s="4" t="n"/>
+      <c r="Q679" s="4" t="n"/>
+      <c r="R679" s="4" t="n"/>
+      <c r="S679" s="4" t="n"/>
+      <c r="T679" s="4" t="n"/>
+      <c r="U679" s="4" t="n"/>
+      <c r="V679" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W679" s="4" t="inlineStr"/>
+      <c r="X679" s="4" t="n"/>
+      <c r="Y679" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z679" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA679" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB679" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC679" s="4" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AD679" s="4" t="n"/>
+      <c r="AE679" s="4" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B680" s="5" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C680" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D680" s="6" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E680" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F680" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G680" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H680" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="I680" s="6" t="inlineStr">
+        <is>
+          <t>01/10/2028</t>
+        </is>
+      </c>
+      <c r="J680" s="6" t="inlineStr"/>
+      <c r="K680" s="6" t="inlineStr"/>
+      <c r="L680" s="6" t="n"/>
+      <c r="M680" s="6" t="n"/>
+      <c r="N680" s="6" t="n"/>
+      <c r="O680" s="6" t="n"/>
+      <c r="P680" s="6" t="n"/>
+      <c r="Q680" s="6" t="n"/>
+      <c r="R680" s="6" t="n"/>
+      <c r="S680" s="6" t="n"/>
+      <c r="T680" s="6" t="n"/>
+      <c r="U680" s="6" t="n"/>
+      <c r="V680" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W680" s="6" t="inlineStr"/>
+      <c r="X680" s="6" t="n"/>
+      <c r="Y680" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z680" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA680" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB680" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC680" s="6" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AD680" s="6" t="n"/>
+      <c r="AE680" s="6" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D681" s="4" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E681" s="4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="F681" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="G681" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H681" s="4" t="n">
+        <v>119.12</v>
+      </c>
+      <c r="I681" s="4" t="inlineStr">
+        <is>
+          <t>03/12/2028</t>
+        </is>
+      </c>
+      <c r="J681" s="4" t="inlineStr"/>
+      <c r="K681" s="4" t="inlineStr"/>
+      <c r="L681" s="4" t="n"/>
+      <c r="M681" s="4" t="n"/>
+      <c r="N681" s="4" t="n"/>
+      <c r="O681" s="4" t="n"/>
+      <c r="P681" s="4" t="n"/>
+      <c r="Q681" s="4" t="n"/>
+      <c r="R681" s="4" t="n"/>
+      <c r="S681" s="4" t="n"/>
+      <c r="T681" s="4" t="n"/>
+      <c r="U681" s="4" t="n"/>
+      <c r="V681" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W681" s="4" t="inlineStr"/>
+      <c r="X681" s="4" t="n"/>
+      <c r="Y681" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z681" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA681" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB681" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC681" s="4" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AD681" s="4" t="n"/>
+      <c r="AE681" s="4" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B682" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C682" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D682" s="6" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
+      <c r="E682" s="6" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="F682" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G682" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H682" s="6" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="I682" s="6" t="n"/>
+      <c r="J682" s="6" t="inlineStr"/>
+      <c r="K682" s="6" t="inlineStr"/>
+      <c r="L682" s="6" t="n"/>
+      <c r="M682" s="6" t="n"/>
+      <c r="N682" s="6" t="n"/>
+      <c r="O682" s="6" t="n"/>
+      <c r="P682" s="6" t="n"/>
+      <c r="Q682" s="6" t="n"/>
+      <c r="R682" s="6" t="n"/>
+      <c r="S682" s="6" t="n"/>
+      <c r="T682" s="6" t="n"/>
+      <c r="U682" s="6" t="n"/>
+      <c r="V682" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W682" s="6" t="inlineStr"/>
+      <c r="X682" s="6" t="n"/>
+      <c r="Y682" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z682" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA682" s="6" t="n"/>
+      <c r="AB682" s="6" t="n"/>
+      <c r="AC682" s="6" t="n"/>
+      <c r="AD682" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE682" s="6" t="n">
+        <v>57.73</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D683" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="E683" s="4" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="F683" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="G683" s="4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H683" s="4" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="I683" s="4" t="n"/>
+      <c r="J683" s="4" t="inlineStr"/>
+      <c r="K683" s="4" t="inlineStr"/>
+      <c r="L683" s="4" t="n"/>
+      <c r="M683" s="4" t="n"/>
+      <c r="N683" s="4" t="n"/>
+      <c r="O683" s="4" t="n"/>
+      <c r="P683" s="4" t="n"/>
+      <c r="Q683" s="4" t="n"/>
+      <c r="R683" s="4" t="n"/>
+      <c r="S683" s="4" t="n"/>
+      <c r="T683" s="4" t="n"/>
+      <c r="U683" s="4" t="n"/>
+      <c r="V683" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W683" s="4" t="inlineStr"/>
+      <c r="X683" s="4" t="n"/>
+      <c r="Y683" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z683" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA683" s="4" t="n"/>
+      <c r="AB683" s="4" t="n"/>
+      <c r="AC683" s="4" t="n"/>
+      <c r="AD683" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE683" s="4" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B684" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C684" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D684" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E684" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F684" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="G684" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H684" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="I684" s="6" t="inlineStr">
+        <is>
+          <t>17/03/2028</t>
+        </is>
+      </c>
+      <c r="J684" s="6" t="inlineStr"/>
+      <c r="K684" s="6" t="inlineStr"/>
+      <c r="L684" s="6" t="n"/>
+      <c r="M684" s="6" t="n"/>
+      <c r="N684" s="6" t="n"/>
+      <c r="O684" s="6" t="n"/>
+      <c r="P684" s="6" t="n"/>
+      <c r="Q684" s="6" t="n"/>
+      <c r="R684" s="6" t="n"/>
+      <c r="S684" s="6" t="n"/>
+      <c r="T684" s="6" t="n"/>
+      <c r="U684" s="6" t="n"/>
+      <c r="V684" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W684" s="6" t="inlineStr"/>
+      <c r="X684" s="6" t="n"/>
+      <c r="Y684" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z684" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA684" s="6" t="n"/>
+      <c r="AB684" s="6" t="n"/>
+      <c r="AC684" s="6" t="n"/>
+      <c r="AD684" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE684" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D685" s="4" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="E685" s="4" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="F685" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="G685" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H685" s="4" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="I685" s="4" t="n"/>
+      <c r="J685" s="4" t="inlineStr"/>
+      <c r="K685" s="4" t="inlineStr"/>
+      <c r="L685" s="4" t="n"/>
+      <c r="M685" s="4" t="n"/>
+      <c r="N685" s="4" t="n"/>
+      <c r="O685" s="4" t="n"/>
+      <c r="P685" s="4" t="n"/>
+      <c r="Q685" s="4" t="n"/>
+      <c r="R685" s="4" t="n"/>
+      <c r="S685" s="4" t="n"/>
+      <c r="T685" s="4" t="n"/>
+      <c r="U685" s="4" t="n"/>
+      <c r="V685" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W685" s="4" t="inlineStr"/>
+      <c r="X685" s="4" t="n"/>
+      <c r="Y685" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z685" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA685" s="4" t="n"/>
+      <c r="AB685" s="4" t="n"/>
+      <c r="AC685" s="4" t="n"/>
+      <c r="AD685" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE685" s="4" t="n">
+        <v>50.82</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B686" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C686" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D686" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E686" s="6" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="F686" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="G686" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H686" s="6" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="I686" s="6" t="n"/>
+      <c r="J686" s="6" t="inlineStr"/>
+      <c r="K686" s="6" t="inlineStr"/>
+      <c r="L686" s="6" t="n"/>
+      <c r="M686" s="6" t="n"/>
+      <c r="N686" s="6" t="n"/>
+      <c r="O686" s="6" t="n"/>
+      <c r="P686" s="6" t="n"/>
+      <c r="Q686" s="6" t="n"/>
+      <c r="R686" s="6" t="n"/>
+      <c r="S686" s="6" t="n"/>
+      <c r="T686" s="6" t="n"/>
+      <c r="U686" s="6" t="n"/>
+      <c r="V686" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W686" s="6" t="inlineStr"/>
+      <c r="X686" s="6" t="n"/>
+      <c r="Y686" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z686" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA686" s="6" t="n"/>
+      <c r="AB686" s="6" t="n"/>
+      <c r="AC686" s="6" t="n"/>
+      <c r="AD686" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE686" s="6" t="n">
+        <v>48.56</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C687" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D687" s="4" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
+      <c r="E687" s="4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F687" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G687" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H687" s="4" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I687" s="4" t="inlineStr">
+        <is>
+          <t>12/02/2028</t>
+        </is>
+      </c>
+      <c r="J687" s="4" t="inlineStr"/>
+      <c r="K687" s="4" t="inlineStr"/>
+      <c r="L687" s="4" t="n"/>
+      <c r="M687" s="4" t="n"/>
+      <c r="N687" s="4" t="n"/>
+      <c r="O687" s="4" t="n"/>
+      <c r="P687" s="4" t="n"/>
+      <c r="Q687" s="4" t="n"/>
+      <c r="R687" s="4" t="n"/>
+      <c r="S687" s="4" t="n"/>
+      <c r="T687" s="4" t="n"/>
+      <c r="U687" s="4" t="n"/>
+      <c r="V687" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W687" s="4" t="inlineStr"/>
+      <c r="X687" s="4" t="n"/>
+      <c r="Y687" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z687" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA687" s="4" t="n"/>
+      <c r="AB687" s="4" t="n"/>
+      <c r="AC687" s="4" t="n"/>
+      <c r="AD687" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE687" s="4" t="n">
+        <v>15.13</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B688" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C688" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D688" s="6" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="E688" s="6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F688" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="G688" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H688" s="6" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="I688" s="6" t="n"/>
+      <c r="J688" s="6" t="inlineStr"/>
+      <c r="K688" s="6" t="inlineStr"/>
+      <c r="L688" s="6" t="n"/>
+      <c r="M688" s="6" t="n"/>
+      <c r="N688" s="6" t="n"/>
+      <c r="O688" s="6" t="n"/>
+      <c r="P688" s="6" t="n"/>
+      <c r="Q688" s="6" t="n"/>
+      <c r="R688" s="6" t="n"/>
+      <c r="S688" s="6" t="n"/>
+      <c r="T688" s="6" t="n"/>
+      <c r="U688" s="6" t="n"/>
+      <c r="V688" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W688" s="6" t="inlineStr"/>
+      <c r="X688" s="6" t="n"/>
+      <c r="Y688" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z688" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA688" s="6" t="n"/>
+      <c r="AB688" s="6" t="n"/>
+      <c r="AC688" s="6" t="n"/>
+      <c r="AD688" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE688" s="6" t="n">
+        <v>15.23</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D689" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E689" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F689" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="G689" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H689" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I689" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2028</t>
+        </is>
+      </c>
+      <c r="J689" s="4" t="inlineStr"/>
+      <c r="K689" s="4" t="inlineStr"/>
+      <c r="L689" s="4" t="n"/>
+      <c r="M689" s="4" t="n"/>
+      <c r="N689" s="4" t="n"/>
+      <c r="O689" s="4" t="n"/>
+      <c r="P689" s="4" t="n"/>
+      <c r="Q689" s="4" t="n"/>
+      <c r="R689" s="4" t="n"/>
+      <c r="S689" s="4" t="n"/>
+      <c r="T689" s="4" t="n"/>
+      <c r="U689" s="4" t="n"/>
+      <c r="V689" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W689" s="4" t="inlineStr"/>
+      <c r="X689" s="4" t="n"/>
+      <c r="Y689" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z689" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA689" s="4" t="n"/>
+      <c r="AB689" s="4" t="n"/>
+      <c r="AC689" s="4" t="n"/>
+      <c r="AD689" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE689" s="4" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B690" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C690" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D690" s="6" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="E690" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F690" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="G690" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H690" s="6" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I690" s="6" t="n"/>
+      <c r="J690" s="6" t="inlineStr"/>
+      <c r="K690" s="6" t="inlineStr"/>
+      <c r="L690" s="6" t="n"/>
+      <c r="M690" s="6" t="n"/>
+      <c r="N690" s="6" t="n"/>
+      <c r="O690" s="6" t="n"/>
+      <c r="P690" s="6" t="n"/>
+      <c r="Q690" s="6" t="n"/>
+      <c r="R690" s="6" t="n"/>
+      <c r="S690" s="6" t="n"/>
+      <c r="T690" s="6" t="n"/>
+      <c r="U690" s="6" t="n"/>
+      <c r="V690" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W690" s="6" t="inlineStr"/>
+      <c r="X690" s="6" t="n"/>
+      <c r="Y690" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z690" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA690" s="6" t="n"/>
+      <c r="AB690" s="6" t="n"/>
+      <c r="AC690" s="6" t="n"/>
+      <c r="AD690" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE690" s="6" t="n">
+        <v>14.17</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D691" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E691" s="4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F691" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="G691" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H691" s="4" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="I691" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2027</t>
+        </is>
+      </c>
+      <c r="J691" s="4" t="inlineStr"/>
+      <c r="K691" s="4" t="inlineStr"/>
+      <c r="L691" s="4" t="n"/>
+      <c r="M691" s="4" t="n"/>
+      <c r="N691" s="4" t="n"/>
+      <c r="O691" s="4" t="n"/>
+      <c r="P691" s="4" t="n"/>
+      <c r="Q691" s="4" t="n"/>
+      <c r="R691" s="4" t="n"/>
+      <c r="S691" s="4" t="n"/>
+      <c r="T691" s="4" t="n"/>
+      <c r="U691" s="4" t="n"/>
+      <c r="V691" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W691" s="4" t="inlineStr"/>
+      <c r="X691" s="4" t="n"/>
+      <c r="Y691" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z691" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA691" s="4" t="n"/>
+      <c r="AB691" s="4" t="n"/>
+      <c r="AC691" s="4" t="n"/>
+      <c r="AD691" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE691" s="4" t="n">
+        <v>13.43</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B692" s="5" t="inlineStr">
+        <is>
+          <t>MONOHYDRATE DE CRÉATINE ULTRA-FIN EN POUDRE (500 MESH)</t>
+        </is>
+      </c>
+      <c r="C692" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/monohydrate-de-creatine-ultra-fin-en-poudre-500-mesh</t>
+        </is>
+      </c>
+      <c r="D692" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E692" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F692" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="G692" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H692" s="6" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="I692" s="6" t="inlineStr">
+        <is>
+          <t>24/02/2028</t>
+        </is>
+      </c>
+      <c r="J692" s="6" t="inlineStr"/>
+      <c r="K692" s="6" t="inlineStr"/>
+      <c r="L692" s="6" t="n"/>
+      <c r="M692" s="6" t="n"/>
+      <c r="N692" s="6" t="n"/>
+      <c r="O692" s="6" t="n"/>
+      <c r="P692" s="6" t="n"/>
+      <c r="Q692" s="6" t="n"/>
+      <c r="R692" s="6" t="n"/>
+      <c r="S692" s="6" t="n"/>
+      <c r="T692" s="6" t="n"/>
+      <c r="U692" s="6" t="n"/>
+      <c r="V692" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W692" s="6" t="inlineStr"/>
+      <c r="X692" s="6" t="n"/>
+      <c r="Y692" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z692" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA692" s="6" t="n"/>
+      <c r="AB692" s="6" t="n"/>
+      <c r="AC692" s="6" t="n"/>
+      <c r="AD692" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE692" s="6" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/whey_prices.xlsx
+++ b/whey_prices.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF863"/>
+  <dimension ref="A1:AF944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64744,6 +64744,7732 @@
         <v>1</v>
       </c>
     </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C864" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D864" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E864" s="4" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="F864" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G864" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H864" s="4" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="I864" s="4" t="inlineStr">
+        <is>
+          <t>15/04/2028</t>
+        </is>
+      </c>
+      <c r="J864" s="4" t="inlineStr"/>
+      <c r="K864" s="4" t="inlineStr"/>
+      <c r="L864" s="4" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="M864" s="4" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="N864" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O864" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="P864" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q864" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R864" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S864" s="4" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T864" s="4" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U864" s="4" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V864" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W864" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X864" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y864" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z864" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA864" s="4" t="n"/>
+      <c r="AB864" s="4" t="n"/>
+      <c r="AC864" s="4" t="n"/>
+      <c r="AD864" s="4" t="n"/>
+      <c r="AE864" s="4" t="n"/>
+      <c r="AF864" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B865" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL SANS ÉDULCORANTS (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C865" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-sans-edulcorants-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D865" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E865" s="6" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="F865" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G865" s="6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H865" s="6" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I865" s="6" t="inlineStr">
+        <is>
+          <t>16/04/2028</t>
+        </is>
+      </c>
+      <c r="J865" s="6" t="inlineStr"/>
+      <c r="K865" s="6" t="inlineStr"/>
+      <c r="L865" s="6" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="M865" s="6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N865" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O865" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="P865" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q865" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R865" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S865" s="6" t="n">
+        <v>8768</v>
+      </c>
+      <c r="T865" s="6" t="n">
+        <v>5370</v>
+      </c>
+      <c r="U865" s="6" t="n">
+        <v>5038</v>
+      </c>
+      <c r="V865" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, cacao dégraissé en poudre non alcalinisé (10-12 % de beurre de cacao, de graines de Theobroma cacao), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, complexe d’enzymes [alpha-amylase, protéase, beta-D-galactosidase (lactase), lipase et cellulase], colostrum bovin (protéines de lait).</t>
+        </is>
+      </c>
+      <c r="W865" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4157.0, "L-Arginine": 2063.0, "Acide L-spartique": 9219.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14687.0, "Glycine": 1472.0, "L-Histidine": 1262.0, "L-Isoleucine": 5370.0, "L-Leucine": 8768.0, "L-Lysine": 7666.0, "L-Méthionine": 1779.0, "L-Phénylalanine": 2585.0, "L-Proline": 5384.0, "L-Sérine": 3896.0, "L-Thréonine": 5926.0, "L-Tryptophane": 1361.0, "L-Tyrosine": 2297.0, "L-Valine": 5038.0}</t>
+        </is>
+      </c>
+      <c r="X865" s="6" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="Y865" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z865" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA865" s="6" t="n"/>
+      <c r="AB865" s="6" t="n"/>
+      <c r="AC865" s="6" t="n"/>
+      <c r="AD865" s="6" t="n"/>
+      <c r="AE865" s="6" t="n"/>
+      <c r="AF865" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C866" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D866" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E866" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F866" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G866" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H866" s="4" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I866" s="4" t="inlineStr">
+        <is>
+          <t>19/01/2028</t>
+        </is>
+      </c>
+      <c r="J866" s="4" t="inlineStr"/>
+      <c r="K866" s="4" t="inlineStr"/>
+      <c r="L866" s="4" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M866" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N866" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="O866" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="P866" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q866" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R866" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S866" s="4" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T866" s="4" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U866" s="4" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V866" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W866" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X866" s="4" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="Y866" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z866" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA866" s="4" t="n"/>
+      <c r="AB866" s="4" t="n"/>
+      <c r="AC866" s="4" t="n"/>
+      <c r="AD866" s="4" t="n"/>
+      <c r="AE866" s="4" t="n"/>
+      <c r="AF866" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B867" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C867" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D867" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E867" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F867" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G867" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H867" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I867" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J867" s="6" t="inlineStr"/>
+      <c r="K867" s="6" t="inlineStr"/>
+      <c r="L867" s="6" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="M867" s="6" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="N867" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="O867" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="P867" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q867" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R867" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S867" s="6" t="n">
+        <v>9981</v>
+      </c>
+      <c r="T867" s="6" t="n">
+        <v>6271</v>
+      </c>
+      <c r="U867" s="6" t="n">
+        <v>5918</v>
+      </c>
+      <c r="V867" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, arôme, émulsifiant (lécithine de tournesol), épaississant (gomme xanthane), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colorant (caramel d'ammonium), arôme naturel, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W867" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4681.0, "L-Arginine": 2385.0, "Acide L-spartique": 10599.0, "L-Cystéine": 2296.0, "Acide L-Glutamique": 16870.0, "Glycine": 1678.0, "L-Histidine": 1237.0, "L-Isoleucine": 6271.0, "L-Leucine": 9981.0, "L-Lysine": 8656.0, "L-Méthionine": 2032.0, "L-Phénylalanine": 2915.0, "L-Proline": 6448.0, "L-Sérine": 4240.0, "L-Thréonine": 6801.0, "L-Tryptophane": 1590.0, "L-Tyrosine": 2650.0, "L-Valine": 5918.0}</t>
+        </is>
+      </c>
+      <c r="X867" s="6" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="Y867" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z867" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA867" s="6" t="n"/>
+      <c r="AB867" s="6" t="n"/>
+      <c r="AC867" s="6" t="n"/>
+      <c r="AD867" s="6" t="n"/>
+      <c r="AE867" s="6" t="n"/>
+      <c r="AF867" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C868" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D868" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E868" s="4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="F868" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G868" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H868" s="4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="I868" s="4" t="inlineStr">
+        <is>
+          <t>18/09/2027</t>
+        </is>
+      </c>
+      <c r="J868" s="4" t="inlineStr"/>
+      <c r="K868" s="4" t="inlineStr"/>
+      <c r="L868" s="4" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="M868" s="4" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="N868" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O868" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="P868" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q868" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R868" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S868" s="4" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T868" s="4" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U868" s="4" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V868" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W868" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X868" s="4" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="Y868" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z868" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA868" s="4" t="n"/>
+      <c r="AB868" s="4" t="n"/>
+      <c r="AC868" s="4" t="n"/>
+      <c r="AD868" s="4" t="n"/>
+      <c r="AE868" s="4" t="n"/>
+      <c r="AF868" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B869" s="5" t="inlineStr">
+        <is>
+          <t>EVOCLEAR HYDRO</t>
+        </is>
+      </c>
+      <c r="C869" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoclear-hydro</t>
+        </is>
+      </c>
+      <c r="D869" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E869" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F869" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G869" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H869" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="I869" s="6" t="inlineStr">
+        <is>
+          <t>23/02/2027</t>
+        </is>
+      </c>
+      <c r="J869" s="6" t="inlineStr"/>
+      <c r="K869" s="6" t="inlineStr"/>
+      <c r="L869" s="6" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="M869" s="6" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="N869" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O869" s="6" t="n">
+        <v>346</v>
+      </c>
+      <c r="P869" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q869" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R869" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S869" s="6" t="n">
+        <v>8788</v>
+      </c>
+      <c r="T869" s="6" t="n">
+        <v>5477</v>
+      </c>
+      <c r="U869" s="6" t="n">
+        <v>4687</v>
+      </c>
+      <c r="V869" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant de lait, arôme naturel, acidulant (acide citrique), correcteur d'acidité (citrate tripotassique), correcteur d'acidité (citrate trisodique), édulcorant (sucralose), poudre de spiruline (Arthrospira platensis), correcteur d'acidité (acide tartrique).</t>
+        </is>
+      </c>
+      <c r="W869" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4206.0, "L-Arginine": 1491.0, "Acide L-spartique": 9317.0, "L-Cystéine": 1892.0, "Acide L-Glutamique": 14290.0, "Glycine": 1288.0, "L-Histidine": 1321.0, "L-Isoleucine": 5477.0, "L-Leucine": 8788.0, "L-Lysine": 8061.0, "L-Méthionine": 1761.0, "L-Phénylalanine": 2397.0, "L-Proline": 4704.0, "L-Sérine": 3571.0, "L-Thréonine": 5779.0, "L-Tryptophane": 1573.0, "L-Tyrosine": 2315.0, "L-Valine": 4687.0}</t>
+        </is>
+      </c>
+      <c r="X869" s="6" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="Y869" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z869" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA869" s="6" t="n"/>
+      <c r="AB869" s="6" t="n"/>
+      <c r="AC869" s="6" t="n"/>
+      <c r="AD869" s="6" t="n"/>
+      <c r="AE869" s="6" t="n"/>
+      <c r="AF869" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D870" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E870" s="4" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="F870" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G870" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H870" s="4" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="I870" s="4" t="inlineStr">
+        <is>
+          <t>13/03/2028</t>
+        </is>
+      </c>
+      <c r="J870" s="4" t="inlineStr"/>
+      <c r="K870" s="4" t="inlineStr"/>
+      <c r="L870" s="4" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="M870" s="4" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="N870" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="O870" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="P870" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q870" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R870" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S870" s="4" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T870" s="4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U870" s="4" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V870" s="4" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W870" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X870" s="4" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="Y870" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z870" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA870" s="4" t="n"/>
+      <c r="AB870" s="4" t="n"/>
+      <c r="AC870" s="4" t="n"/>
+      <c r="AD870" s="4" t="n"/>
+      <c r="AE870" s="4" t="n"/>
+      <c r="AF870" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B871" s="5" t="inlineStr">
+        <is>
+          <t>CRÈME DE RIZ PROTÉINÉE</t>
+        </is>
+      </c>
+      <c r="C871" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/creme-de-riz-proteinee</t>
+        </is>
+      </c>
+      <c r="D871" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E871" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F871" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G871" s="6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H871" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I871" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J871" s="6" t="inlineStr"/>
+      <c r="K871" s="6" t="inlineStr"/>
+      <c r="L871" s="6" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="M871" s="6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="N871" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="O871" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="P871" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q871" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R871" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S871" s="6" t="n">
+        <v>4422</v>
+      </c>
+      <c r="T871" s="6" t="n">
+        <v>2482</v>
+      </c>
+      <c r="U871" s="6" t="n">
+        <v>2632</v>
+      </c>
+      <c r="V871" s="6" t="inlineStr">
+        <is>
+          <t>Farine de riz, caséine micellaire (lait), concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W871" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 1815.0, "L-Arginine": 1352.0, "Acide L-spartique": 4057.0, "L-Cystéine": 711.0, "Acide L-Glutamique": 8508.0, "Glycine": 805.0, "L-Histidine": 963.0, "L-Isoleucine": 2482.0, "L-Leucine": 4422.0, "L-Lysine": 3827.0, "L-Méthionine": 1016.0, "L-Phénylalanine": 1763.0, "L-Proline": 3451.0, "L-Sérine": 2328.0, "L-Thréonine": 2516.0, "L-Tryptophane": 695.0, "L-Tyrosine": 1891.0, "L-Valine": 2632.0}</t>
+        </is>
+      </c>
+      <c r="X871" s="6" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y871" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z871" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA871" s="6" t="n"/>
+      <c r="AB871" s="6" t="n"/>
+      <c r="AC871" s="6" t="n"/>
+      <c r="AD871" s="6" t="n"/>
+      <c r="AE871" s="6" t="n"/>
+      <c r="AF871" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D872" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E872" s="4" t="n"/>
+      <c r="F872" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G872" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H872" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I872" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J872" s="4" t="inlineStr"/>
+      <c r="K872" s="4" t="inlineStr"/>
+      <c r="L872" s="4" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="M872" s="4" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="N872" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O872" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P872" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q872" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R872" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S872" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T872" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U872" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V872" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W872" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X872" s="4" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="Y872" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z872" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA872" s="4" t="n"/>
+      <c r="AB872" s="4" t="n"/>
+      <c r="AC872" s="4" t="n"/>
+      <c r="AD872" s="4" t="n"/>
+      <c r="AE872" s="4" t="n"/>
+      <c r="AF872" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B873" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C873" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D873" s="6" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E873" s="6" t="n"/>
+      <c r="F873" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G873" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H873" s="6" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="I873" s="6" t="n"/>
+      <c r="J873" s="6" t="inlineStr"/>
+      <c r="K873" s="6" t="inlineStr"/>
+      <c r="L873" s="6" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="M873" s="6" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="N873" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O873" s="6" t="n">
+        <v>361</v>
+      </c>
+      <c r="P873" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q873" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R873" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S873" s="6" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T873" s="6" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U873" s="6" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V873" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W873" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X873" s="6" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="Y873" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z873" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA873" s="6" t="n"/>
+      <c r="AB873" s="6" t="n"/>
+      <c r="AC873" s="6" t="n"/>
+      <c r="AD873" s="6" t="n"/>
+      <c r="AE873" s="6" t="n"/>
+      <c r="AF873" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C874" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein</t>
+        </is>
+      </c>
+      <c r="D874" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E874" s="4" t="n"/>
+      <c r="F874" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G874" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H874" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I874" s="4" t="inlineStr">
+        <is>
+          <t>12/12/2027</t>
+        </is>
+      </c>
+      <c r="J874" s="4" t="inlineStr"/>
+      <c r="K874" s="4" t="inlineStr"/>
+      <c r="L874" s="4" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="M874" s="4" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="N874" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O874" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="P874" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q874" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R874" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S874" s="4" t="n">
+        <v>8247</v>
+      </c>
+      <c r="T874" s="4" t="n">
+        <v>4702</v>
+      </c>
+      <c r="U874" s="4" t="n">
+        <v>4341</v>
+      </c>
+      <c r="V874" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait [émulsifiant (lécithine de tournesol)], café instantané, arôme, chlorure de sodium, édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W874" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3915.0, "L-Arginine": 1886.0, "Acide L-spartique": 8399.0, "L-Cystéine": 1611.0, "Acide L-Glutamique": 13272.0, "Glycine": 1374.0, "L-Histidine": 1289.0, "L-Isoleucine": 4702.0, "L-Leucine": 8247.0, "L-Lysine": 7062.0, "L-Méthionine": 1403.0, "L-Phénylalanine": 2398.0, "L-Proline": 4522.0, "L-Sérine": 3887.0, "L-Thréonine": 5489.0, "L-Tryptophane": 1384.0, "L-Tyrosine": 2171.0, "L-Valine": 4341.0}</t>
+        </is>
+      </c>
+      <c r="X874" s="4" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Y874" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z874" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA874" s="4" t="n"/>
+      <c r="AB874" s="4" t="n"/>
+      <c r="AC874" s="4" t="n"/>
+      <c r="AD874" s="4" t="n"/>
+      <c r="AE874" s="4" t="n"/>
+      <c r="AF874" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B875" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C875" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D875" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E875" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F875" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G875" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H875" s="6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I875" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J875" s="6" t="inlineStr"/>
+      <c r="K875" s="6" t="inlineStr"/>
+      <c r="L875" s="6" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="M875" s="6" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="N875" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="O875" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="P875" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q875" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R875" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S875" s="6" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T875" s="6" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U875" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V875" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W875" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X875" s="6" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="Y875" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z875" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA875" s="6" t="n"/>
+      <c r="AB875" s="6" t="n"/>
+      <c r="AC875" s="6" t="n"/>
+      <c r="AD875" s="6" t="n"/>
+      <c r="AE875" s="6" t="n"/>
+      <c r="AF875" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY PROTEIN SANS ÉDULCORANTS</t>
+        </is>
+      </c>
+      <c r="C876" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-protein-sans-edulcorants</t>
+        </is>
+      </c>
+      <c r="D876" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E876" s="4" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="F876" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G876" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H876" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I876" s="4" t="inlineStr">
+        <is>
+          <t>29/08/2027</t>
+        </is>
+      </c>
+      <c r="J876" s="4" t="inlineStr"/>
+      <c r="K876" s="4" t="inlineStr"/>
+      <c r="L876" s="4" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="M876" s="4" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="N876" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="O876" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="P876" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q876" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R876" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S876" s="4" t="n">
+        <v>8356</v>
+      </c>
+      <c r="T876" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="U876" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="V876" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lait de petit-lait, poudre de framboise (de Rubus idaeus), arômes naturels, émulsifiant (lécithine de tournesol), chlorure de sodium, lactase (100000 ALU/g, de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W876" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4032.0, "L-Arginine": 1906.0, "Acide L-spartique": 8650.0, "L-Cystéine": 1613.0, "Acide L-Glutamique": 13781.0, "Glycine": 1393.0, "L-Histidine": 1466.0, "L-Isoleucine": 4911.0, "L-Leucine": 8356.0, "L-Lysine": 7403.0, "L-Méthionine": 1686.0, "L-Phénylalanine": 2492.0, "L-Proline": 4691.0, "L-Sérine": 3958.0, "L-Thréonine": 5571.0, "L-Tryptophane": 1246.0, "L-Tyrosine": 2126.0, "L-Valine": 4544.0}</t>
+        </is>
+      </c>
+      <c r="X876" s="4" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="Y876" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z876" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA876" s="4" t="n"/>
+      <c r="AB876" s="4" t="n"/>
+      <c r="AC876" s="4" t="n"/>
+      <c r="AD876" s="4" t="n"/>
+      <c r="AE876" s="4" t="n"/>
+      <c r="AF876" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B877" s="5" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C877" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D877" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E877" s="6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F877" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G877" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H877" s="6" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="I877" s="6" t="inlineStr">
+        <is>
+          <t>09/12/2027</t>
+        </is>
+      </c>
+      <c r="J877" s="6" t="inlineStr"/>
+      <c r="K877" s="6" t="inlineStr"/>
+      <c r="L877" s="6" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="M877" s="6" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="N877" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="O877" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="P877" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q877" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R877" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S877" s="6" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T877" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U877" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V877" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W877" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X877" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y877" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z877" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA877" s="6" t="n"/>
+      <c r="AB877" s="6" t="n"/>
+      <c r="AC877" s="6" t="n"/>
+      <c r="AD877" s="6" t="n"/>
+      <c r="AE877" s="6" t="n"/>
+      <c r="AF877" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 2.0 (HYDRO WHEY)</t>
+        </is>
+      </c>
+      <c r="C878" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-2-0-hydro-whey</t>
+        </is>
+      </c>
+      <c r="D878" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E878" s="4" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="F878" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G878" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H878" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I878" s="4" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J878" s="4" t="inlineStr"/>
+      <c r="K878" s="4" t="inlineStr"/>
+      <c r="L878" s="4" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="M878" s="4" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="N878" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O878" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P878" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q878" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R878" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S878" s="4" t="n">
+        <v>9656</v>
+      </c>
+      <c r="T878" s="4" t="n">
+        <v>5962</v>
+      </c>
+      <c r="U878" s="4" t="n">
+        <v>5290</v>
+      </c>
+      <c r="V878" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé de lait [émulsifiant (lécithine de soja)], poudre de cacao dégraissé (10-12% de beurre de cacao, de fèves de Theobroma cacao), arôme, correcteur d'acidité (carbonate de potassium), chlorure de sodium, édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W878" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4702.0, "L-Arginine": 1847.0, "Acide L-spartique": 9656.0, "L-Cystéine": 2099.0, "Acide L-Glutamique": 15618.0, "Glycine": 1427.0, "L-Histidine": 1511.0, "L-Isoleucine": 5962.0, "L-Leucine": 9656.0, "L-Lysine": 8649.0, "L-Méthionine": 2099.0, "L-Phénylalanine": 2687.0, "L-Proline": 5794.0, "L-Sérine": 4366.0, "L-Thréonine": 6466.0, "L-Tryptophane": 1511.0, "L-Tyrosine": 2603.0, "L-Valine": 5290.0}</t>
+        </is>
+      </c>
+      <c r="X878" s="4" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="Y878" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z878" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA878" s="4" t="n"/>
+      <c r="AB878" s="4" t="n"/>
+      <c r="AC878" s="4" t="n"/>
+      <c r="AD878" s="4" t="n"/>
+      <c r="AE878" s="4" t="n"/>
+      <c r="AF878" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B879" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C879" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D879" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E879" s="6" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="F879" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G879" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H879" s="6" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="I879" s="6" t="inlineStr">
+        <is>
+          <t>06/10/2027</t>
+        </is>
+      </c>
+      <c r="J879" s="6" t="inlineStr"/>
+      <c r="K879" s="6" t="inlineStr"/>
+      <c r="L879" s="6" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="M879" s="6" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="N879" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O879" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P879" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q879" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R879" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S879" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T879" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U879" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V879" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W879" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X879" s="6" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="Y879" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z879" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA879" s="6" t="n"/>
+      <c r="AB879" s="6" t="n"/>
+      <c r="AC879" s="6" t="n"/>
+      <c r="AD879" s="6" t="n"/>
+      <c r="AE879" s="6" t="n"/>
+      <c r="AF879" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D880" s="4" t="inlineStr">
+        <is>
+          <t>750g</t>
+        </is>
+      </c>
+      <c r="E880" s="4" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F880" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G880" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H880" s="4" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="I880" s="4" t="n"/>
+      <c r="J880" s="4" t="inlineStr"/>
+      <c r="K880" s="4" t="inlineStr"/>
+      <c r="L880" s="4" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="M880" s="4" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="N880" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="O880" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P880" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q880" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R880" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S880" s="4" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T880" s="4" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U880" s="4" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V880" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W880" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X880" s="4" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="Y880" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z880" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA880" s="4" t="n"/>
+      <c r="AB880" s="4" t="n"/>
+      <c r="AC880" s="4" t="n"/>
+      <c r="AD880" s="4" t="n"/>
+      <c r="AE880" s="4" t="n"/>
+      <c r="AF880" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B881" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN ISOLATE</t>
+        </is>
+      </c>
+      <c r="C881" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-isolate</t>
+        </is>
+      </c>
+      <c r="D881" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E881" s="6" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="F881" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G881" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H881" s="6" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="I881" s="6" t="inlineStr">
+        <is>
+          <t>25/08/2027</t>
+        </is>
+      </c>
+      <c r="J881" s="6" t="inlineStr"/>
+      <c r="K881" s="6" t="inlineStr"/>
+      <c r="L881" s="6" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="M881" s="6" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="N881" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="O881" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P881" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q881" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R881" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S881" s="6" t="n">
+        <v>10492</v>
+      </c>
+      <c r="T881" s="6" t="n">
+        <v>6592</v>
+      </c>
+      <c r="U881" s="6" t="n">
+        <v>6221</v>
+      </c>
+      <c r="V881" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W881" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4291.0, "L-Arginine": 2507.0, "Acide L-spartique": 11142.0, "L-Cystéine": 2414.0, "Acide L-Glutamique": 17734.0, "Glycine": 1764.0, "L-Histidine": 1300.0, "L-Isoleucine": 6592.0, "L-Leucine": 10492.0, "L-Lysine": 9099.0, "L-Méthionine": 2136.0, "L-Phénylalanine": 3064.0, "L-Proline": 6778.0, "L-Sérine": 4457.0, "L-Thréonine": 7149.0, "L-Tryptophane": 1671.0, "L-Tyrosine": 2786.0, "L-Valine": 6221.0}</t>
+        </is>
+      </c>
+      <c r="X881" s="6" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="Y881" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z881" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA881" s="6" t="n"/>
+      <c r="AB881" s="6" t="n"/>
+      <c r="AC881" s="6" t="n"/>
+      <c r="AD881" s="6" t="n"/>
+      <c r="AE881" s="6" t="n"/>
+      <c r="AF881" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D882" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E882" s="4" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="F882" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G882" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H882" s="4" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="I882" s="4" t="inlineStr">
+        <is>
+          <t>20/03/2028</t>
+        </is>
+      </c>
+      <c r="J882" s="4" t="inlineStr"/>
+      <c r="K882" s="4" t="inlineStr"/>
+      <c r="L882" s="4" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="M882" s="4" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="N882" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="O882" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="P882" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q882" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R882" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S882" s="4" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T882" s="4" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U882" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V882" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W882" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X882" s="4" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="Y882" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z882" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA882" s="4" t="n"/>
+      <c r="AB882" s="4" t="n"/>
+      <c r="AC882" s="4" t="n"/>
+      <c r="AD882" s="4" t="n"/>
+      <c r="AE882" s="4" t="n"/>
+      <c r="AF882" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B883" s="5" t="inlineStr">
+        <is>
+          <t>EVOLATE 2.0 SANS ÉDULCORANTS (WHEY ISOLATE CFM)</t>
+        </is>
+      </c>
+      <c r="C883" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evolate-2-0-sans-edulcorants-whey-isolate-cfm</t>
+        </is>
+      </c>
+      <c r="D883" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E883" s="6" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F883" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G883" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H883" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="I883" s="6" t="inlineStr">
+        <is>
+          <t>29/01/2028</t>
+        </is>
+      </c>
+      <c r="J883" s="6" t="inlineStr"/>
+      <c r="K883" s="6" t="inlineStr"/>
+      <c r="L883" s="6" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="M883" s="6" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N883" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="O883" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="P883" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q883" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R883" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S883" s="6" t="n">
+        <v>9358</v>
+      </c>
+      <c r="T883" s="6" t="n">
+        <v>5879</v>
+      </c>
+      <c r="U883" s="6" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V883" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, framboise en poudre, arômes naturels, émulsifiant (lécithine de tournesol), complexe d'enzymes pour denrées alimentaires [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, agent épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W883" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4389.0, "L-Arginine": 2236.0, "Acide L-spartique": 9937.0, "L-Cystéine": 2153.0, "Acide L-Glutamique": 15817.0, "Glycine": 1573.0, "L-Histidine": 1159.0, "L-Isoleucine": 5879.0, "L-Leucine": 9358.0, "L-Lysine": 8115.0, "L-Méthionine": 1905.0, "L-Phénylalanine": 2733.0, "L-Proline": 6045.0, "L-Sérine": 3975.0, "L-Thréonine": 6376.0, "L-Tryptophane": 1490.0, "L-Tyrosine": 2485.0, "L-Valine": 5548.0}</t>
+        </is>
+      </c>
+      <c r="X883" s="6" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="Y883" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z883" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA883" s="6" t="n"/>
+      <c r="AB883" s="6" t="n"/>
+      <c r="AC883" s="6" t="n"/>
+      <c r="AD883" s="6" t="n"/>
+      <c r="AE883" s="6" t="n"/>
+      <c r="AF883" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C884" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D884" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E884" s="4" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="F884" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G884" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H884" s="4" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="I884" s="4" t="inlineStr">
+        <is>
+          <t>23/04/2027</t>
+        </is>
+      </c>
+      <c r="J884" s="4" t="inlineStr"/>
+      <c r="K884" s="4" t="inlineStr"/>
+      <c r="L884" s="4" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="M884" s="4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="N884" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O884" s="4" t="n">
+        <v>430</v>
+      </c>
+      <c r="P884" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q884" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R884" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S884" s="4" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T884" s="4" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U884" s="4" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V884" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W884" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X884" s="4" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="Y884" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z884" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA884" s="4" t="n"/>
+      <c r="AB884" s="4" t="n"/>
+      <c r="AC884" s="4" t="n"/>
+      <c r="AD884" s="4" t="n"/>
+      <c r="AE884" s="4" t="n"/>
+      <c r="AF884" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B885" s="5" t="inlineStr">
+        <is>
+          <t>EVOBASIC WHEY</t>
+        </is>
+      </c>
+      <c r="C885" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evobasic-whey</t>
+        </is>
+      </c>
+      <c r="D885" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E885" s="6" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="F885" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G885" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H885" s="6" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I885" s="6" t="inlineStr">
+        <is>
+          <t>10/04/2028</t>
+        </is>
+      </c>
+      <c r="J885" s="6" t="inlineStr"/>
+      <c r="K885" s="6" t="inlineStr"/>
+      <c r="L885" s="6" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="M885" s="6" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N885" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O885" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="P885" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q885" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R885" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S885" s="6" t="n">
+        <v>8224</v>
+      </c>
+      <c r="T885" s="6" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U885" s="6" t="n">
+        <v>4215</v>
+      </c>
+      <c r="V885" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao)], correcteur d'acidité (carbonate de potassium), arômes, chlorure de sodium, arôme naturel, édulcorant (sucralose), lactase (100000 ALU/g, d'Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W885" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3732.0, "L-Arginine": 2695.0, "Acide L-spartique": 7533.0, "L-Cystéine": 1520.0, "Acide L-Glutamique": 11955.0, "Glycine": 1659.0, "L-Histidine": 1659.0, "L-Isoleucine": 3939.0, "L-Leucine": 8224.0, "L-Lysine": 6773.0, "L-Méthionine": 1659.0, "L-Phénylalanine": 2626.0, "L-Proline": 4146.0, "L-Sérine": 4215.0, "L-Thréonine": 4699.0, "L-Tryptophane": 1244.0, "L-Tyrosine": 2557.0, "L-Valine": 4215.0}</t>
+        </is>
+      </c>
+      <c r="X885" s="6" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Y885" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z885" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA885" s="6" t="n"/>
+      <c r="AB885" s="6" t="n"/>
+      <c r="AC885" s="6" t="n"/>
+      <c r="AD885" s="6" t="n"/>
+      <c r="AE885" s="6" t="n"/>
+      <c r="AF885" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C886" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D886" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E886" s="4" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F886" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G886" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H886" s="4" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="I886" s="4" t="inlineStr">
+        <is>
+          <t>23/09/2027</t>
+        </is>
+      </c>
+      <c r="J886" s="4" t="inlineStr"/>
+      <c r="K886" s="4" t="inlineStr"/>
+      <c r="L886" s="4" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="M886" s="4" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N886" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O886" s="4" t="n">
+        <v>449</v>
+      </c>
+      <c r="P886" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q886" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="R886" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S886" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T886" s="4" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U886" s="4" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V886" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W886" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X886" s="4" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="Y886" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z886" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA886" s="4" t="n"/>
+      <c r="AB886" s="4" t="n"/>
+      <c r="AC886" s="4" t="n"/>
+      <c r="AD886" s="4" t="n"/>
+      <c r="AE886" s="4" t="n"/>
+      <c r="AF886" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B887" s="5" t="inlineStr">
+        <is>
+          <t>KETO WHEY PROTEIN</t>
+        </is>
+      </c>
+      <c r="C887" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/keto-series/keto-whey-protein</t>
+        </is>
+      </c>
+      <c r="D887" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E887" s="6" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F887" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G887" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H887" s="6" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="I887" s="6" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="J887" s="6" t="inlineStr"/>
+      <c r="K887" s="6" t="inlineStr"/>
+      <c r="L887" s="6" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="M887" s="6" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="N887" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="O887" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="P887" s="6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q887" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="R887" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S887" s="6" t="n">
+        <v>7113</v>
+      </c>
+      <c r="T887" s="6" t="n">
+        <v>4469</v>
+      </c>
+      <c r="U887" s="6" t="n">
+        <v>4218</v>
+      </c>
+      <c r="V887" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum de lait, triglycérides à chaîne moyenne microencapsulés [triglycérides à chaîne moyenne (d'huile de coco), caséinate de sodium (lait), émulsifiant (monoglycérides et diglycérides d'acides gras)], cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme naturel, émulsifiant (lécithine de tournesol), épaississant (gomme de xanthane), chlorure de sodium, complexe d'enzymes digestives [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase, cellulase], correcteur d'acidité (carbonate de potassium), édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W887" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3336.0, "L-Arginine": 1700.0, "Acide L-spartique": 7554.0, "L-Cystéine": 1637.0, "Acide L-Glutamique": 12023.0, "Glycine": 1196.0, "L-Histidine": 881.0, "L-Isoleucine": 4469.0, "L-Leucine": 7113.0, "L-Lysine": 6169.0, "L-Méthionine": 1448.0, "L-Phénylalanine": 2077.0, "L-Proline": 4595.0, "L-Sérine": 3022.0, "L-Thréonine": 4847.0, "L-Tryptophane": 1133.0, "L-Tyrosine": 1889.0, "L-Valine": 4218.0}</t>
+        </is>
+      </c>
+      <c r="X887" s="6" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="Y887" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z887" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA887" s="6" t="n"/>
+      <c r="AB887" s="6" t="n"/>
+      <c r="AC887" s="6" t="n"/>
+      <c r="AD887" s="6" t="n"/>
+      <c r="AE887" s="6" t="n"/>
+      <c r="AF887" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C888" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D888" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E888" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F888" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G888" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H888" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I888" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J888" s="4" t="inlineStr"/>
+      <c r="K888" s="4" t="inlineStr"/>
+      <c r="L888" s="4" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="M888" s="4" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N888" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O888" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P888" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q888" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R888" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S888" s="4" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T888" s="4" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U888" s="4" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V888" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W888" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X888" s="4" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="Y888" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z888" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA888" s="4" t="n"/>
+      <c r="AB888" s="4" t="n"/>
+      <c r="AC888" s="4" t="n"/>
+      <c r="AD888" s="4" t="n"/>
+      <c r="AE888" s="4" t="n"/>
+      <c r="AF888" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B889" s="5" t="inlineStr">
+        <is>
+          <t>EVOEXCEL 2.0 (WHEY PROTEIN ISOLATE + CONCENTRATE)</t>
+        </is>
+      </c>
+      <c r="C889" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evoexcel-2-0-whey-protein-isolate-concentrate</t>
+        </is>
+      </c>
+      <c r="D889" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E889" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F889" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G889" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H889" s="6" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I889" s="6" t="inlineStr">
+        <is>
+          <t>09/04/2028</t>
+        </is>
+      </c>
+      <c r="J889" s="6" t="inlineStr"/>
+      <c r="K889" s="6" t="inlineStr"/>
+      <c r="L889" s="6" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="M889" s="6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N889" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O889" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P889" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q889" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R889" s="6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S889" s="6" t="n">
+        <v>9214</v>
+      </c>
+      <c r="T889" s="6" t="n">
+        <v>5654</v>
+      </c>
+      <c r="U889" s="6" t="n">
+        <v>5307</v>
+      </c>
+      <c r="V889" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, protéine concentrée de lactosérum de lait, arômes, émulsifiant (lécithine de tournesol), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], chlorure de sodium, colostrum bovin (protéines de lait), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W889" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4365.0, "L-Arginine": 2170.0, "Acide L-spartique": 9695.0, "L-Cystéine": 1998.0, "Acide L-Glutamique": 15445.0, "Glycine": 1547.0, "L-Histidine": 1313.0, "L-Isoleucine": 5654.0, "L-Leucine": 9214.0, "L-Lysine": 8051.0, "L-Méthionine": 1870.0, "L-Phénylalanine": 2715.0, "L-Proline": 5681.0, "L-Sérine": 4081.0, "L-Thréonine": 6231.0, "L-Tryptophane": 1433.0, "L-Tyrosine": 2416.0, "L-Valine": 5307.0}</t>
+        </is>
+      </c>
+      <c r="X889" s="6" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="Y889" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z889" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA889" s="6" t="n"/>
+      <c r="AB889" s="6" t="n"/>
+      <c r="AC889" s="6" t="n"/>
+      <c r="AD889" s="6" t="n"/>
+      <c r="AE889" s="6" t="n"/>
+      <c r="AF889" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D890" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E890" s="4" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="F890" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G890" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H890" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I890" s="4" t="inlineStr">
+        <is>
+          <t>21/04/2028</t>
+        </is>
+      </c>
+      <c r="J890" s="4" t="inlineStr"/>
+      <c r="K890" s="4" t="inlineStr"/>
+      <c r="L890" s="4" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="M890" s="4" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="N890" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O890" s="4" t="n">
+        <v>388</v>
+      </c>
+      <c r="P890" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q890" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R890" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S890" s="4" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T890" s="4" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U890" s="4" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V890" s="4" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W890" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 4789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 3904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X890" s="4" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="Y890" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z890" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA890" s="4" t="n"/>
+      <c r="AB890" s="4" t="n"/>
+      <c r="AC890" s="4" t="n"/>
+      <c r="AD890" s="4" t="n"/>
+      <c r="AE890" s="4" t="n"/>
+      <c r="AF890" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B891" s="5" t="inlineStr">
+        <is>
+          <t>EVOWHEY &amp; OATS</t>
+        </is>
+      </c>
+      <c r="C891" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evowhey-oats</t>
+        </is>
+      </c>
+      <c r="D891" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E891" s="6" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F891" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G891" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H891" s="6" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="I891" s="6" t="n"/>
+      <c r="J891" s="6" t="inlineStr"/>
+      <c r="K891" s="6" t="inlineStr"/>
+      <c r="L891" s="6" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M891" s="6" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="N891" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O891" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="P891" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q891" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R891" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S891" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="T891" s="6" t="n">
+        <v>2682</v>
+      </c>
+      <c r="U891" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="V891" s="6" t="inlineStr">
+        <is>
+          <t>Farine d'avoine (gluten), protéine concentrée de lactosérum de lait [émulsifiant (lécithine de tournesol)], arôme, arôme naturel, chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose).</t>
+        </is>
+      </c>
+      <c r="W891" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2320.0, "L-Arginine": 1414.0, "Acide L-spartique": 4789.0, "L-Cystéine": 1065.0, "Acide L-Glutamique": 8059.0, "Glycine": 1094.0, "L-Histidine": 856.0, "L-Isoleucine": 2682.0, "L-Leucine": 4577.0, "L-Lysine": 3904.0, "L-Méthionine": 964.0, "L-Phénylalanine": 1565.0, "L-Proline": 2643.0, "L-Sérine": 2352.0, "L-Thréonine": 3006.0, "L-Tryptophane": 748.0, "L-Tyrosine": 1317.0, "L-Valine": 2571.0}</t>
+        </is>
+      </c>
+      <c r="X891" s="6" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="Y891" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z891" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA891" s="6" t="n"/>
+      <c r="AB891" s="6" t="n"/>
+      <c r="AC891" s="6" t="n"/>
+      <c r="AD891" s="6" t="n"/>
+      <c r="AE891" s="6" t="n"/>
+      <c r="AF891" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>EVOHYDRO 30HD</t>
+        </is>
+      </c>
+      <c r="C892" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evohydro-30hd</t>
+        </is>
+      </c>
+      <c r="D892" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E892" s="4" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="F892" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G892" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H892" s="4" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I892" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J892" s="4" t="inlineStr"/>
+      <c r="K892" s="4" t="inlineStr"/>
+      <c r="L892" s="4" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M892" s="4" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="N892" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O892" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="P892" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q892" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R892" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S892" s="4" t="n">
+        <v>7170</v>
+      </c>
+      <c r="T892" s="4" t="n">
+        <v>3857</v>
+      </c>
+      <c r="U892" s="4" t="n">
+        <v>3903</v>
+      </c>
+      <c r="V892" s="4" t="inlineStr">
+        <is>
+          <t>Protéine de lactosérum hydrolysée provenant de lait (degré d'hydrolyse 30%), cacao en poudre dégraissé (10-12% de beurre de cacao, provenant des graines de Theobroma cacao), arôme, arôme naturel, chlorure de sodium, régulateur d'acidité (carbonate de potassium), édulcorant (sucralose), lactase (100000 ALU/g, enzyme de qualité alimentaire provenant de Aspergillus oryzae).</t>
+        </is>
+      </c>
+      <c r="W892" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3267.0, "L-Arginine": 1833.0, "Acide L-spartique": 7292.0, "L-Cystéine": 1633.0, "Acide L-Glutamique": 11671.0, "Glycine": 1273.0, "L-Histidine": 1235.0, "L-Isoleucine": 3857.0, "L-Leucine": 7170.0, "L-Lysine": 6211.0, "L-Méthionine": 1235.0, "L-Phénylalanine": 2185.0, "L-Proline": 3865.0, "L-Sérine": 3619.0, "L-Thréonine": 4938.0, "L-Tryptophane": 951.0, "L-Tyrosine": 2070.0, "L-Valine": 3903.0}</t>
+        </is>
+      </c>
+      <c r="X892" s="4" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="Y892" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z892" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA892" s="4" t="n"/>
+      <c r="AB892" s="4" t="n"/>
+      <c r="AC892" s="4" t="n"/>
+      <c r="AD892" s="4" t="n"/>
+      <c r="AE892" s="4" t="n"/>
+      <c r="AF892" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B893" s="5" t="inlineStr">
+        <is>
+          <t>EVOPEPT 2.0 (PeptoPro®)</t>
+        </is>
+      </c>
+      <c r="C893" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopept-peptopro</t>
+        </is>
+      </c>
+      <c r="D893" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E893" s="6" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="F893" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G893" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H893" s="6" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="I893" s="6" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J893" s="6" t="inlineStr"/>
+      <c r="K893" s="6" t="inlineStr"/>
+      <c r="L893" s="6" t="n">
+        <v>107.27</v>
+      </c>
+      <c r="M893" s="6" t="n">
+        <v>3.218</v>
+      </c>
+      <c r="N893" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O893" s="6" t="n">
+        <v>318</v>
+      </c>
+      <c r="P893" s="6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q893" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R893" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S893" s="6" t="n">
+        <v>6681</v>
+      </c>
+      <c r="T893" s="6" t="n">
+        <v>3385</v>
+      </c>
+      <c r="U893" s="6" t="n">
+        <v>4543</v>
+      </c>
+      <c r="V893" s="6" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait), arôme, acidifiant (acide citrique), arôme naturel, correcteur d'acidité (phosphate monopotassique), édulcorant (sucralose), colorant (rouge betterave), colorant (anthocyanes), extrait de carthame (Carthamus tinctorius).</t>
+        </is>
+      </c>
+      <c r="W893" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2049.0, "L-Arginine": 2673.0, "Acide L-spartique": 4454.0, "L-Cystéine": 89.0, "Acide L-Glutamique": 15234.0, "Glycine": 1247.0, "L-Histidine": 1960.0, "L-Isoleucine": 3385.0, "L-Leucine": 6681.0, "L-Lysine": 5256.0, "L-Méthionine": 2316.0, "L-Phénylalanine": 3296.0, "L-Proline": 7572.0, "L-Sérine": 3652.0, "L-Thréonine": 2583.0, "L-Tryptophane": 713.0, "L-Tyrosine": 3920.0, "L-Valine": 4543.0}</t>
+        </is>
+      </c>
+      <c r="X893" s="6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y893" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z893" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA893" s="6" t="n"/>
+      <c r="AB893" s="6" t="n"/>
+      <c r="AC893" s="6" t="n"/>
+      <c r="AD893" s="6" t="n"/>
+      <c r="AE893" s="6" t="n"/>
+      <c r="AF893" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C894" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D894" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E894" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F894" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G894" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H894" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I894" s="4" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J894" s="4" t="inlineStr"/>
+      <c r="K894" s="4" t="inlineStr"/>
+      <c r="L894" s="4" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="M894" s="4" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="N894" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="O894" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="P894" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q894" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R894" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S894" s="4" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T894" s="4" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U894" s="4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V894" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W894" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X894" s="4" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="Y894" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z894" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA894" s="4" t="n"/>
+      <c r="AB894" s="4" t="n"/>
+      <c r="AC894" s="4" t="n"/>
+      <c r="AD894" s="4" t="n"/>
+      <c r="AE894" s="4" t="n"/>
+      <c r="AF894" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B895" s="5" t="inlineStr">
+        <is>
+          <t>GOLDEN PROTEIN</t>
+        </is>
+      </c>
+      <c r="C895" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/golden-protein</t>
+        </is>
+      </c>
+      <c r="D895" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E895" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="F895" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G895" s="6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H895" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I895" s="6" t="inlineStr">
+        <is>
+          <t>13/02/2028</t>
+        </is>
+      </c>
+      <c r="J895" s="6" t="inlineStr"/>
+      <c r="K895" s="6" t="inlineStr"/>
+      <c r="L895" s="6" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="M895" s="6" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="N895" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="O895" s="6" t="n">
+        <v>431</v>
+      </c>
+      <c r="P895" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q895" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="R895" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S895" s="6" t="n">
+        <v>5893</v>
+      </c>
+      <c r="T895" s="6" t="n">
+        <v>3463</v>
+      </c>
+      <c r="U895" s="6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="V895" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, extrait de pulpe de noix de coco (de Cocos nucifera), extrait de curcuma (4:1, provenant de racine et rhizome de Curcuma longa, 3% curcumine), arômes naturels, cannelle (de Cinnamomum zeylanicum), épaississant (gomme xanthane), chlorure de sodium, extrait de gingembre (10:1, de racine de Zingiber officinale, 5% gingérol), extrait de poivre noir (50:1, de fruit de Piper nigrum, 98,5% pipérine).</t>
+        </is>
+      </c>
+      <c r="W895" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2843.0, "L-Arginine": 1344.0, "Acide L-spartique": 6100.0, "L-Cystéine": 1137.0, "Acide L-Glutamique": 9718.0, "Glycine": 982.0, "L-Histidine": 1034.0, "L-Isoleucine": 3463.0, "L-Leucine": 5893.0, "L-Lysine": 5221.0, "L-Méthionine": 1189.0, "L-Phénylalanine": 1758.0, "L-Proline": 3308.0, "L-Sérine": 2791.0, "L-Thréonine": 3929.0, "L-Tryptophane": 879.0, "L-Tyrosine": 1499.0, "L-Valine": 3205.0}</t>
+        </is>
+      </c>
+      <c r="X895" s="6" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="Y895" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z895" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA895" s="6" t="n"/>
+      <c r="AB895" s="6" t="n"/>
+      <c r="AC895" s="6" t="n"/>
+      <c r="AD895" s="6" t="n"/>
+      <c r="AE895" s="6" t="n"/>
+      <c r="AF895" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C896" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D896" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E896" s="4" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F896" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G896" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H896" s="4" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="I896" s="4" t="n"/>
+      <c r="J896" s="4" t="inlineStr"/>
+      <c r="K896" s="4" t="inlineStr"/>
+      <c r="L896" s="4" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="M896" s="4" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="N896" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O896" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="P896" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q896" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R896" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S896" s="4" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T896" s="4" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U896" s="4" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V896" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W896" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X896" s="4" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="Y896" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z896" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA896" s="4" t="n"/>
+      <c r="AB896" s="4" t="n"/>
+      <c r="AC896" s="4" t="n"/>
+      <c r="AD896" s="4" t="n"/>
+      <c r="AE896" s="4" t="n"/>
+      <c r="AF896" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B897" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE HYDROLYSÉE DE CLEAR WHEY</t>
+        </is>
+      </c>
+      <c r="C897" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-hydrolysee-de-clear-whey</t>
+        </is>
+      </c>
+      <c r="D897" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E897" s="6" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F897" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G897" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H897" s="6" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I897" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="J897" s="6" t="inlineStr"/>
+      <c r="K897" s="6" t="inlineStr"/>
+      <c r="L897" s="6" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="M897" s="6" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="N897" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O897" s="6" t="n">
+        <v>358</v>
+      </c>
+      <c r="P897" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q897" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R897" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S897" s="6" t="n">
+        <v>9262</v>
+      </c>
+      <c r="T897" s="6" t="n">
+        <v>5773</v>
+      </c>
+      <c r="U897" s="6" t="n">
+        <v>4940</v>
+      </c>
+      <c r="V897" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysé provenant du lait.</t>
+        </is>
+      </c>
+      <c r="W897" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4433.0, "L-Arginine": 1572.0, "Acide L-spartique": 9820.0, "L-Cystéine": 1994.0, "Acide L-Glutamique": 15061.0, "Glycine": 1358.0, "L-Histidine": 1392.0, "L-Isoleucine": 5773.0, "L-Leucine": 9262.0, "L-Lysine": 8495.0, "L-Méthionine": 1855.0, "L-Phénylalanine": 2526.0, "L-Proline": 4958.0, "L-Sérine": 3763.0, "L-Thréonine": 6091.0, "L-Tryptophane": 1658.0, "L-Tyrosine": 2439.0, "L-Valine": 4940.0}</t>
+        </is>
+      </c>
+      <c r="X897" s="6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y897" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z897" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA897" s="6" t="n"/>
+      <c r="AB897" s="6" t="n"/>
+      <c r="AC897" s="6" t="n"/>
+      <c r="AD897" s="6" t="n"/>
+      <c r="AE897" s="6" t="n"/>
+      <c r="AF897" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C898" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D898" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E898" s="4" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F898" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G898" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H898" s="4" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="I898" s="4" t="inlineStr">
+        <is>
+          <t>28/11/2027</t>
+        </is>
+      </c>
+      <c r="J898" s="4" t="inlineStr"/>
+      <c r="K898" s="4" t="inlineStr"/>
+      <c r="L898" s="4" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="M898" s="4" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="N898" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="O898" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="P898" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q898" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R898" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S898" s="4" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T898" s="4" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U898" s="4" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V898" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W898" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X898" s="4" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="Y898" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z898" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA898" s="4" t="n"/>
+      <c r="AB898" s="4" t="n"/>
+      <c r="AC898" s="4" t="n"/>
+      <c r="AD898" s="4" t="n"/>
+      <c r="AE898" s="4" t="n"/>
+      <c r="AF898" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B899" s="5" t="inlineStr">
+        <is>
+          <t>100% ISOLAT DE PROTÉINE DE LACTOSÉRUM HYDROLYSÉ</t>
+        </is>
+      </c>
+      <c r="C899" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-isolat-de-proteine-de-lactoserum-hydrolyse</t>
+        </is>
+      </c>
+      <c r="D899" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E899" s="6" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="F899" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G899" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H899" s="6" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="I899" s="6" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J899" s="6" t="inlineStr"/>
+      <c r="K899" s="6" t="inlineStr"/>
+      <c r="L899" s="6" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="M899" s="6" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N899" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="O899" s="6" t="n">
+        <v>379</v>
+      </c>
+      <c r="P899" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q899" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R899" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S899" s="6" t="n">
+        <v>10580</v>
+      </c>
+      <c r="T899" s="6" t="n">
+        <v>6532</v>
+      </c>
+      <c r="U899" s="6" t="n">
+        <v>5796</v>
+      </c>
+      <c r="V899" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de lactosérum hydrolysées issu du lait [émulsifiant (lécithine de soja)].</t>
+        </is>
+      </c>
+      <c r="W899" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 5152.0, "L-Arginine": 2024.0, "Acide L-spartique": 10580.0, "L-Cystéine": 2300.0, "Acide L-Glutamique": 17112.0, "Glycine": 1564.0, "L-Histidine": 1656.0, "L-Isoleucine": 6532.0, "L-Leucine": 10580.0, "L-Lysine": 9476.0, "L-Méthionine": 2300.0, "L-Phénylalanine": 2944.0, "L-Proline": 6348.0, "L-Sérine": 4784.0, "L-Thréonine": 7084.0, "L-Tryptophane": 1656.0, "L-Tyrosine": 2852.0, "L-Valine": 5796.0}</t>
+        </is>
+      </c>
+      <c r="X899" s="6" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Y899" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z899" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA899" s="6" t="n"/>
+      <c r="AB899" s="6" t="n"/>
+      <c r="AC899" s="6" t="n"/>
+      <c r="AD899" s="6" t="n"/>
+      <c r="AE899" s="6" t="n"/>
+      <c r="AF899" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>PEPTOPRO® HYDROLYSAT DE CASÉINE EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C900" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/peptopro-hydrolysat-de-caseine-en-poudre</t>
+        </is>
+      </c>
+      <c r="D900" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E900" s="4" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="F900" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G900" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H900" s="4" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="I900" s="4" t="inlineStr">
+        <is>
+          <t>20/04/2028</t>
+        </is>
+      </c>
+      <c r="J900" s="4" t="inlineStr"/>
+      <c r="K900" s="4" t="inlineStr"/>
+      <c r="L900" s="4" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="M900" s="4" t="n">
+        <v>2.753</v>
+      </c>
+      <c r="N900" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O900" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="P900" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q900" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R900" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S900" s="4" t="n">
+        <v>7812</v>
+      </c>
+      <c r="T900" s="4" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U900" s="4" t="n">
+        <v>5312</v>
+      </c>
+      <c r="V900" s="4" t="inlineStr">
+        <is>
+          <t>Caséine hydrolysée (lait).</t>
+        </is>
+      </c>
+      <c r="W900" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2396.0, "L-Arginine": 3125.0, "Acide L-spartique": 5208.0, "L-Cystéine": 104.0, "Acide L-Glutamique": 17812.0, "Glycine": 1458.0, "L-Histidine": 2292.0, "L-Isoleucine": 3958.0, "L-Leucine": 7812.0, "L-Lysine": 6146.0, "L-Méthionine": 2708.0, "L-Phénylalanine": 3854.0, "L-Proline": 8854.0, "L-Sérine": 4271.0, "L-Thréonine": 3021.0, "L-Tryptophane": 833.0, "L-Tyrosine": 4583.0, "L-Valine": 5312.0}</t>
+        </is>
+      </c>
+      <c r="X900" s="4" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="Y900" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z900" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA900" s="4" t="n"/>
+      <c r="AB900" s="4" t="n"/>
+      <c r="AC900" s="4" t="n"/>
+      <c r="AD900" s="4" t="n"/>
+      <c r="AE900" s="4" t="n"/>
+      <c r="AF900" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B901" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C901" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D901" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E901" s="6" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="F901" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G901" s="6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H901" s="6" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="I901" s="6" t="inlineStr">
+        <is>
+          <t>13/11/2027</t>
+        </is>
+      </c>
+      <c r="J901" s="6" t="inlineStr"/>
+      <c r="K901" s="6" t="inlineStr"/>
+      <c r="L901" s="6" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="M901" s="6" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="N901" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O901" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="P901" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q901" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R901" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S901" s="6" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T901" s="6" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U901" s="6" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V901" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W901" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X901" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Y901" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z901" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA901" s="6" t="n"/>
+      <c r="AB901" s="6" t="n"/>
+      <c r="AC901" s="6" t="n"/>
+      <c r="AD901" s="6" t="n"/>
+      <c r="AE901" s="6" t="n"/>
+      <c r="AF901" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ SANS ÉDULCORANTS #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C902" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-sans-edulcorants-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D902" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E902" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F902" s="4" t="n"/>
+      <c r="G902" s="4" t="n"/>
+      <c r="H902" s="4" t="n"/>
+      <c r="I902" s="4" t="inlineStr"/>
+      <c r="J902" s="4" t="inlineStr"/>
+      <c r="K902" s="4" t="inlineStr"/>
+      <c r="L902" s="4" t="n"/>
+      <c r="M902" s="4" t="n"/>
+      <c r="N902" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O902" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="P902" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q902" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R902" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S902" s="4" t="n">
+        <v>6252</v>
+      </c>
+      <c r="T902" s="4" t="n">
+        <v>3565</v>
+      </c>
+      <c r="U902" s="4" t="n">
+        <v>3291</v>
+      </c>
+      <c r="V902" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (22,5%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W902" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2968.0, "L-Arginine": 1430.0, "Acide L-spartique": 6367.0, "L-Cystéine": 1222.0, "Acide L-Glutamique": 10061.0, "Glycine": 1042.0, "L-Histidine": 977.0, "L-Isoleucine": 3565.0, "L-Leucine": 6252.0, "L-Lysine": 5353.0, "L-Méthionine": 1064.0, "L-Phénylalanine": 1818.0, "L-Proline": 3428.0, "L-Sérine": 2946.0, "L-Thréonine": 4161.0, "L-Tryptophane": 1049.0, "L-Tyrosine": 1646.0, "L-Valine": 3291.0}</t>
+        </is>
+      </c>
+      <c r="X902" s="4" t="n"/>
+      <c r="Y902" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z902" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA902" s="4" t="n"/>
+      <c r="AB902" s="4" t="n"/>
+      <c r="AC902" s="4" t="n"/>
+      <c r="AD902" s="4" t="n"/>
+      <c r="AE902" s="4" t="n"/>
+      <c r="AF902" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B903" s="5" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C903" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D903" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E903" s="6" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="F903" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G903" s="6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H903" s="6" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="I903" s="6" t="inlineStr">
+        <is>
+          <t>17/11/2027</t>
+        </is>
+      </c>
+      <c r="J903" s="6" t="inlineStr"/>
+      <c r="K903" s="6" t="inlineStr"/>
+      <c r="L903" s="6" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="M903" s="6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N903" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="O903" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="P903" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q903" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R903" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S903" s="6" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T903" s="6" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U903" s="6" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V903" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W903" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X903" s="6" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="Y903" s="6" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z903" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA903" s="6" t="n"/>
+      <c r="AB903" s="6" t="n"/>
+      <c r="AC903" s="6" t="n"/>
+      <c r="AD903" s="6" t="n"/>
+      <c r="AE903" s="6" t="n"/>
+      <c r="AF903" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>CAFÉ PROTÉINÉ #CaféFitConQ</t>
+        </is>
+      </c>
+      <c r="C904" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/cafe-proteine-cafefitconq</t>
+        </is>
+      </c>
+      <c r="D904" s="4" t="inlineStr">
+        <is>
+          <t>1 boîte (16x35g)</t>
+        </is>
+      </c>
+      <c r="E904" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F904" s="4" t="n"/>
+      <c r="G904" s="4" t="n"/>
+      <c r="H904" s="4" t="n"/>
+      <c r="I904" s="4" t="inlineStr"/>
+      <c r="J904" s="4" t="inlineStr"/>
+      <c r="K904" s="4" t="inlineStr"/>
+      <c r="L904" s="4" t="n"/>
+      <c r="M904" s="4" t="n"/>
+      <c r="N904" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="O904" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="P904" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q904" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R904" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S904" s="4" t="n">
+        <v>7444</v>
+      </c>
+      <c r="T904" s="4" t="n">
+        <v>4375</v>
+      </c>
+      <c r="U904" s="4" t="n">
+        <v>4048</v>
+      </c>
+      <c r="V904" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, café instantané (14,8%), cacao dégraissé en poudre [cacao (10-12% de beurre de cacao, de graines de Theobroma cacao), correcteur d'acidité (carbonate de potassium)], arômes, émulsifiant (lécithine de tournesol), chlorure de sodium, édulcorant (sucralose), caféine naturelle anhydre (extraction végétale de grains de café vert), arôme naturel, épaississant (gomme xanthane).</t>
+        </is>
+      </c>
+      <c r="W904" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3592.0, "L-Arginine": 1698.0, "Acide L-spartique": 7705.0, "L-Cystéine": 1436.0, "Acide L-Glutamique": 12276.0, "Glycine": 1241.0, "L-Histidine": 1306.0, "L-Isoleucine": 4375.0, "L-Leucine": 7444.0, "L-Lysine": 6595.0, "L-Méthionine": 1502.0, "L-Phénylalanine": 2220.0, "L-Proline": 4179.0, "L-Sérine": 3526.0, "L-Thréonine": 4962.0, "L-Tryptophane": 1110.0, "L-Tyrosine": 1894.0, "L-Valine": 4048.0}</t>
+        </is>
+      </c>
+      <c r="X904" s="4" t="n"/>
+      <c r="Y904" s="4" t="inlineStr">
+        <is>
+          <t>Aliments enrichis</t>
+        </is>
+      </c>
+      <c r="Z904" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA904" s="4" t="n"/>
+      <c r="AB904" s="4" t="n"/>
+      <c r="AC904" s="4" t="n"/>
+      <c r="AD904" s="4" t="n"/>
+      <c r="AE904" s="4" t="n"/>
+      <c r="AF904" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B905" s="5" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C905" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D905" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E905" s="6" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F905" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G905" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H905" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I905" s="6" t="inlineStr">
+        <is>
+          <t>30/03/2028</t>
+        </is>
+      </c>
+      <c r="J905" s="6" t="inlineStr"/>
+      <c r="K905" s="6" t="inlineStr"/>
+      <c r="L905" s="6" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M905" s="6" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="N905" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="O905" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="P905" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q905" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R905" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S905" s="6" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T905" s="6" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U905" s="6" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V905" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W905" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X905" s="6" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Y905" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z905" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA905" s="6" t="n"/>
+      <c r="AB905" s="6" t="n"/>
+      <c r="AC905" s="6" t="n"/>
+      <c r="AD905" s="6" t="n"/>
+      <c r="AE905" s="6" t="n"/>
+      <c r="AF905" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>100% WHEY PROTEIN CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C906" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/100-whey-protein-concentrate</t>
+        </is>
+      </c>
+      <c r="D906" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E906" s="4" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F906" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G906" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H906" s="4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="I906" s="4" t="inlineStr">
+        <is>
+          <t>14/11/2027</t>
+        </is>
+      </c>
+      <c r="J906" s="4" t="inlineStr"/>
+      <c r="K906" s="4" t="inlineStr"/>
+      <c r="L906" s="4" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="M906" s="4" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="N906" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="O906" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="P906" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q906" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R906" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S906" s="4" t="n">
+        <v>9312</v>
+      </c>
+      <c r="T906" s="4" t="n">
+        <v>5473</v>
+      </c>
+      <c r="U906" s="4" t="n">
+        <v>5064</v>
+      </c>
+      <c r="V906" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W906" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4493.0, "L-Arginine": 2124.0, "Acide L-spartique": 9639.0, "L-Cystéine": 1797.0, "Acide L-Glutamique": 15357.0, "Glycine": 1552.0, "L-Histidine": 1634.0, "L-Isoleucine": 5473.0, "L-Leucine": 9312.0, "L-Lysine": 8250.0, "L-Méthionine": 1879.0, "L-Phénylalanine": 2777.0, "L-Proline": 5228.0, "L-Sérine": 4411.0, "L-Thréonine": 6208.0, "L-Tryptophane": 1389.0, "L-Tyrosine": 2369.0, "L-Valine": 5064.0}</t>
+        </is>
+      </c>
+      <c r="X906" s="4" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="Y906" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z906" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA906" s="4" t="n"/>
+      <c r="AB906" s="4" t="n"/>
+      <c r="AC906" s="4" t="n"/>
+      <c r="AD906" s="4" t="n"/>
+      <c r="AE906" s="4" t="n"/>
+      <c r="AF906" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B907" s="5" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D907" s="6" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E907" s="6" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="F907" s="6" t="n"/>
+      <c r="G907" s="6" t="n"/>
+      <c r="H907" s="6" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="I907" s="6" t="inlineStr"/>
+      <c r="J907" s="6" t="inlineStr"/>
+      <c r="K907" s="6" t="inlineStr"/>
+      <c r="L907" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="M907" s="6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N907" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="O907" s="6" t="n">
+        <v>385</v>
+      </c>
+      <c r="P907" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q907" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R907" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S907" s="6" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T907" s="6" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U907" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V907" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W907" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X907" s="6" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="Y907" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z907" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA907" s="6" t="n"/>
+      <c r="AB907" s="6" t="n"/>
+      <c r="AC907" s="6" t="n"/>
+      <c r="AD907" s="6" t="n"/>
+      <c r="AE907" s="6" t="n"/>
+      <c r="AF907" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>EVONATURAL WHEY</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonatural-whey</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E908" s="4" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F908" s="4" t="n"/>
+      <c r="G908" s="4" t="n"/>
+      <c r="H908" s="4" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="I908" s="4" t="inlineStr"/>
+      <c r="J908" s="4" t="inlineStr"/>
+      <c r="K908" s="4" t="inlineStr"/>
+      <c r="L908" s="4" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="M908" s="4" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="N908" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="O908" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="P908" s="4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q908" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R908" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S908" s="4" t="n">
+        <v>8167</v>
+      </c>
+      <c r="T908" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="U908" s="4" t="n">
+        <v>4351</v>
+      </c>
+      <c r="V908" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum de lait, cannelle (de Cinnamoum zeylanicum), arôme naturel, chlorure de sodium, édulcorant (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W908" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4045.0, "L-Arginine": 1985.0, "Acide L-spartique": 8931.0, "L-Cystéine": 611.0, "Acide L-Glutamique": 13281.0, "Glycine": 1679.0, "L-Histidine": 1221.0, "L-Isoleucine": 4656.0, "L-Leucine": 8167.0, "L-Lysine": 6946.0, "L-Méthionine": 1527.0, "L-Phénylalanine": 2443.0, "L-Proline": 4809.0, "L-Sérine": 4122.0, "L-Thréonine": 5572.0, "L-Tryptophane": 1374.0, "L-Tyrosine": 2366.0, "L-Valine": 4351.0}</t>
+        </is>
+      </c>
+      <c r="X908" s="4" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="Y908" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z908" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA908" s="4" t="n"/>
+      <c r="AB908" s="4" t="n"/>
+      <c r="AC908" s="4" t="n"/>
+      <c r="AD908" s="4" t="n"/>
+      <c r="AE908" s="4" t="n"/>
+      <c r="AF908" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B909" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C909" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D909" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E909" s="6" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F909" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G909" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H909" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I909" s="6" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J909" s="6" t="inlineStr"/>
+      <c r="K909" s="6" t="inlineStr"/>
+      <c r="L909" s="6" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="M909" s="6" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="N909" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="O909" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="P909" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q909" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R909" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S909" s="6" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T909" s="6" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U909" s="6" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V909" s="6" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W909" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X909" s="6" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="Y909" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z909" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA909" s="6" t="n"/>
+      <c r="AB909" s="6" t="n"/>
+      <c r="AC909" s="6" t="n"/>
+      <c r="AD909" s="6" t="n"/>
+      <c r="AE909" s="6" t="n"/>
+      <c r="AF909" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE WHEY</t>
+        </is>
+      </c>
+      <c r="C910" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-whey</t>
+        </is>
+      </c>
+      <c r="D910" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E910" s="4" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="F910" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G910" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H910" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I910" s="4" t="inlineStr">
+        <is>
+          <t>14/04/2028</t>
+        </is>
+      </c>
+      <c r="J910" s="4" t="inlineStr"/>
+      <c r="K910" s="4" t="inlineStr"/>
+      <c r="L910" s="4" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="M910" s="4" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="N910" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="O910" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="P910" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q910" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R910" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S910" s="4" t="n">
+        <v>10068</v>
+      </c>
+      <c r="T910" s="4" t="n">
+        <v>4449</v>
+      </c>
+      <c r="U910" s="4" t="n">
+        <v>4137</v>
+      </c>
+      <c r="V910" s="4" t="inlineStr">
+        <is>
+          <t>Concentré de protéines de lactosérum lait [émulsifiant (lécithine de tournesol)], arôme (lait), calcium provenant de lait, cannelle (de Cinnamomum zeylanicum), chlorure de sodium, épaississant (gomme xanthane), édulcorant (sucralose), arôme naturel, antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W910" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3981.0, "L-Arginine": 2420.0, "Acide L-spartique": 9210.0, "L-Cystéine": 2185.0, "Acide L-Glutamique": 14283.0, "Glycine": 1483.0, "L-Histidine": 1717.0, "L-Isoleucine": 4449.0, "L-Leucine": 10068.0, "L-Lysine": 8351.0, "L-Méthionine": 1873.0, "L-Phénylalanine": 3044.0, "L-Proline": 3981.0, "L-Sérine": 3668.0, "L-Thréonine": 4215.0, "L-Tryptophane": 1639.0, "L-Tyrosine": 2888.0, "L-Valine": 4137.0}</t>
+        </is>
+      </c>
+      <c r="X910" s="4" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="Y910" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z910" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA910" s="4" t="n"/>
+      <c r="AB910" s="4" t="n"/>
+      <c r="AC910" s="4" t="n"/>
+      <c r="AD910" s="4" t="n"/>
+      <c r="AE910" s="4" t="n"/>
+      <c r="AF910" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B911" s="5" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C911" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D911" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E911" s="6" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="F911" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G911" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H911" s="6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I911" s="6" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J911" s="6" t="inlineStr"/>
+      <c r="K911" s="6" t="inlineStr"/>
+      <c r="L911" s="6" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M911" s="6" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N911" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="O911" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="P911" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q911" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R911" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S911" s="6" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T911" s="6" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U911" s="6" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V911" s="6" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W911" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X911" s="6" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y911" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z911" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA911" s="6" t="n"/>
+      <c r="AB911" s="6" t="n"/>
+      <c r="AC911" s="6" t="n"/>
+      <c r="AD911" s="6" t="n"/>
+      <c r="AE911" s="6" t="n"/>
+      <c r="AF911" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>NATIVE WHEY CONCENTRATE</t>
+        </is>
+      </c>
+      <c r="C912" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/native-whey-concentrate</t>
+        </is>
+      </c>
+      <c r="D912" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E912" s="4" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="F912" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G912" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H912" s="4" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="I912" s="4" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="J912" s="4" t="inlineStr"/>
+      <c r="K912" s="4" t="inlineStr"/>
+      <c r="L912" s="4" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="M912" s="4" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N912" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="O912" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="P912" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q912" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R912" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S912" s="4" t="n">
+        <v>10449</v>
+      </c>
+      <c r="T912" s="4" t="n">
+        <v>4617</v>
+      </c>
+      <c r="U912" s="4" t="n">
+        <v>4293</v>
+      </c>
+      <c r="V912" s="4" t="inlineStr">
+        <is>
+          <t>Protéine concentrée de lactosérum [émulsifiant (lécithine de tournesol)], antiagglomérant (phosphate tricalcique).</t>
+        </is>
+      </c>
+      <c r="W912" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 4131.0, "L-Arginine": 2511.0, "Acide L-spartique": 9558.0, "L-Cystéine": 2268.0, "Acide L-Glutamique": 14823.0, "Glycine": 1539.0, "L-Histidine": 1782.0, "L-Isoleucine": 4617.0, "L-Leucine": 10449.0, "L-Lysine": 8667.0, "L-Méthionine": 1944.0, "L-Phénylalanine": 3159.0, "L-Proline": 4131.0, "L-Sérine": 3807.0, "L-Thréonine": 4374.0, "L-Tryptophane": 1701.0, "L-Tyrosine": 2997.0, "L-Valine": 4293.0}</t>
+        </is>
+      </c>
+      <c r="X912" s="4" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="Y912" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z912" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA912" s="4" t="n"/>
+      <c r="AB912" s="4" t="n"/>
+      <c r="AC912" s="4" t="n"/>
+      <c r="AD912" s="4" t="n"/>
+      <c r="AE912" s="4" t="n"/>
+      <c r="AF912" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B913" s="5" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C913" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D913" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E913" s="6" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="F913" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G913" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H913" s="6" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="I913" s="6" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J913" s="6" t="inlineStr"/>
+      <c r="K913" s="6" t="inlineStr"/>
+      <c r="L913" s="6" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="M913" s="6" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="N913" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="O913" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="P913" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q913" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R913" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S913" s="6" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T913" s="6" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U913" s="6" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V913" s="6" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W913" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X913" s="6" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="Y913" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z913" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA913" s="6" t="n"/>
+      <c r="AB913" s="6" t="n"/>
+      <c r="AC913" s="6" t="n"/>
+      <c r="AD913" s="6" t="n"/>
+      <c r="AE913" s="6" t="n"/>
+      <c r="AF913" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>EVONATIVE CASEIN (Lacprodan® Micelpure™)</t>
+        </is>
+      </c>
+      <c r="C914" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evonative-casein-lacprodan-micelpure</t>
+        </is>
+      </c>
+      <c r="D914" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E914" s="4" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="F914" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G914" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H914" s="4" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="I914" s="4" t="inlineStr">
+        <is>
+          <t>23/02/2028</t>
+        </is>
+      </c>
+      <c r="J914" s="4" t="inlineStr"/>
+      <c r="K914" s="4" t="inlineStr"/>
+      <c r="L914" s="4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="M914" s="4" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="N914" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="O914" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="P914" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q914" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R914" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S914" s="4" t="n">
+        <v>7926</v>
+      </c>
+      <c r="T914" s="4" t="n">
+        <v>4211</v>
+      </c>
+      <c r="U914" s="4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="V914" s="4" t="inlineStr">
+        <is>
+          <t>Caséine micellaire (lait) cacao dégraissé en poudre (10-12% de beurre de cacao, de graines de Theobroma cacao), arôme, épaississant (gomme xanthane), chlorure de sodium, correcteur d'acidité (carbonate de potassium), arôme naturel, édulcorant (sucralose), émulsifiant (lécithine de tournesol).</t>
+        </is>
+      </c>
+      <c r="W914" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2642.0, "L-Arginine": 3055.0, "Acide L-spartique": 6110.0, "L-Cystéine": 413.0, "Acide L-Glutamique": 18577.0, "Glycine": 1569.0, "L-Histidine": 2394.0, "L-Isoleucine": 4211.0, "L-Leucine": 7926.0, "L-Lysine": 6770.0, "L-Méthionine": 2477.0, "L-Phénylalanine": 4211.0, "L-Proline": 8339.0, "L-Sérine": 5037.0, "L-Thréonine": 3716.0, "L-Tryptophane": 1073.0, "L-Tyrosine": 4541.0, "L-Valine": 5449.0}</t>
+        </is>
+      </c>
+      <c r="X914" s="4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="Y914" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z914" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA914" s="4" t="n"/>
+      <c r="AB914" s="4" t="n"/>
+      <c r="AC914" s="4" t="n"/>
+      <c r="AD914" s="4" t="n"/>
+      <c r="AE914" s="4" t="n"/>
+      <c r="AF914" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B915" s="5" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C915" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D915" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E915" s="6" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="F915" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G915" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H915" s="6" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="I915" s="6" t="inlineStr">
+        <is>
+          <t>23/01/2028</t>
+        </is>
+      </c>
+      <c r="J915" s="6" t="inlineStr"/>
+      <c r="K915" s="6" t="inlineStr"/>
+      <c r="L915" s="6" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="M915" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="N915" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="O915" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="P915" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q915" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R915" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S915" s="6" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T915" s="6" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U915" s="6" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V915" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W915" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X915" s="6" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="Y915" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z915" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA915" s="6" t="n"/>
+      <c r="AB915" s="6" t="n"/>
+      <c r="AC915" s="6" t="n"/>
+      <c r="AD915" s="6" t="n"/>
+      <c r="AE915" s="6" t="n"/>
+      <c r="AF915" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>EVOPRO (MIX PROTÉINES PREMIUM) + DIGEZYME®</t>
+        </is>
+      </c>
+      <c r="C916" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evopro-mix-proteines-premium-digezyme</t>
+        </is>
+      </c>
+      <c r="D916" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E916" s="4" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="F916" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G916" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H916" s="4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="I916" s="4" t="inlineStr">
+        <is>
+          <t>08/09/2027</t>
+        </is>
+      </c>
+      <c r="J916" s="4" t="inlineStr"/>
+      <c r="K916" s="4" t="inlineStr"/>
+      <c r="L916" s="4" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="M916" s="4" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="N916" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="O916" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="P916" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q916" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R916" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S916" s="4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="T916" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="U916" s="4" t="n">
+        <v>5683</v>
+      </c>
+      <c r="V916" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lactosérum de lait, caséine micellaire (lait), arôme, épaississant (gomme de cellulose), chlorure de sodium, épaississant (gomme xanthane), complexe d’enzymes [alpha-amylase, protéase, bêta-D-galactosidase (lactase), lipase et cellulase], émulsifiant (lécithine de tournesol), colorant (caramel ammoniacal), édulcorant (sucralose), arôme naturel.</t>
+        </is>
+      </c>
+      <c r="W916" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3763.0, "L-Arginine": 2756.0, "Acide L-spartique": 8656.0, "L-Cystéine": 1672.0, "Acide L-Glutamique": 17596.0, "Glycine": 1647.0, "L-Histidine": 1754.0, "L-Isoleucine": 5406.0, "L-Leucine": 9089.0, "L-Lysine": 7913.0, "L-Méthionine": 2202.0, "L-Phénylalanine": 3525.0, "L-Proline": 7367.0, "L-Sérine": 4494.0, "L-Thréonine": 5344.0, "L-Tryptophane": 1394.0, "L-Tyrosine": 3557.0, "L-Valine": 5683.0}</t>
+        </is>
+      </c>
+      <c r="X916" s="4" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="Y916" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z916" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA916" s="4" t="n"/>
+      <c r="AB916" s="4" t="n"/>
+      <c r="AC916" s="4" t="n"/>
+      <c r="AD916" s="4" t="n"/>
+      <c r="AE916" s="4" t="n"/>
+      <c r="AF916" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B917" s="5" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C917" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D917" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E917" s="6" t="n"/>
+      <c r="F917" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G917" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H917" s="6" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="I917" s="6" t="inlineStr">
+        <is>
+          <t>05/02/2028</t>
+        </is>
+      </c>
+      <c r="J917" s="6" t="inlineStr"/>
+      <c r="K917" s="6" t="inlineStr"/>
+      <c r="L917" s="6" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="M917" s="6" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="N917" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O917" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="P917" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q917" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R917" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S917" s="6" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T917" s="6" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U917" s="6" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V917" s="6" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W917" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X917" s="6" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="Y917" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z917" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA917" s="6" t="n"/>
+      <c r="AB917" s="6" t="n"/>
+      <c r="AC917" s="6" t="n"/>
+      <c r="AD917" s="6" t="n"/>
+      <c r="AE917" s="6" t="n"/>
+      <c r="AF917" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>PUDDING PROTÉINÉ 2.0</t>
+        </is>
+      </c>
+      <c r="C918" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/food-series/pudding-proteine-2-0</t>
+        </is>
+      </c>
+      <c r="D918" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E918" s="4" t="n"/>
+      <c r="F918" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G918" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H918" s="4" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="I918" s="4" t="n"/>
+      <c r="J918" s="4" t="inlineStr"/>
+      <c r="K918" s="4" t="inlineStr"/>
+      <c r="L918" s="4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M918" s="4" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="N918" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O918" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="P918" s="4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q918" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R918" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S918" s="4" t="n">
+        <v>7009</v>
+      </c>
+      <c r="T918" s="4" t="n">
+        <v>3937</v>
+      </c>
+      <c r="U918" s="4" t="n">
+        <v>4581</v>
+      </c>
+      <c r="V918" s="4" t="inlineStr">
+        <is>
+          <t>Caséinate de calcium (lait), isolat de protéines de lait, concentré de protéines de lactosérum de lait, amidon modifié (phosphate de diamidon hydroxypropylé), amidon de pomme de terre, arômes, gélifiant (carraghénane), chlorure de sodium, émulsifiant (lécithine de tournesol), édulcorant (sucralose), colorant (bêta-carotène).</t>
+        </is>
+      </c>
+      <c r="W918" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2552.0, "L-Arginine": 2497.0, "Acide L-spartique": 5861.0, "L-Cystéine": 835.0, "Acide L-Glutamique": 15076.0, "Glycine": 1348.0, "L-Histidine": 1813.0, "L-Isoleucine": 3937.0, "L-Leucine": 7009.0, "L-Lysine": 6026.0, "L-Méthionine": 1926.0, "L-Phénylalanine": 3342.0, "L-Proline": 6830.0, "L-Sérine": 4006.0, "L-Thréonine": 3581.0, "L-Tryptophane": 1036.0, "L-Tyrosine": 3588.0, "L-Valine": 4581.0}</t>
+        </is>
+      </c>
+      <c r="X918" s="4" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="Y918" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z918" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA918" s="4" t="n"/>
+      <c r="AB918" s="4" t="n"/>
+      <c r="AC918" s="4" t="n"/>
+      <c r="AD918" s="4" t="n"/>
+      <c r="AE918" s="4" t="n"/>
+      <c r="AF918" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D919" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E919" s="6" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F919" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G919" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H919" s="6" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="I919" s="6" t="inlineStr">
+        <is>
+          <t>19/02/2028</t>
+        </is>
+      </c>
+      <c r="J919" s="6" t="inlineStr"/>
+      <c r="K919" s="6" t="inlineStr"/>
+      <c r="L919" s="6" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="M919" s="6" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="N919" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="O919" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="P919" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q919" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R919" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S919" s="6" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T919" s="6" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U919" s="6" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V919" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W919" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X919" s="6" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="Y919" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z919" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA919" s="6" t="n"/>
+      <c r="AB919" s="6" t="n"/>
+      <c r="AC919" s="6" t="n"/>
+      <c r="AD919" s="6" t="n"/>
+      <c r="AE919" s="6" t="n"/>
+      <c r="AF919" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>EVODIET VEGAN</t>
+        </is>
+      </c>
+      <c r="C920" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/sport-series/evodiet-vegan</t>
+        </is>
+      </c>
+      <c r="D920" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E920" s="4" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="F920" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G920" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H920" s="4" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="I920" s="4" t="inlineStr">
+        <is>
+          <t>30/10/2027</t>
+        </is>
+      </c>
+      <c r="J920" s="4" t="inlineStr"/>
+      <c r="K920" s="4" t="inlineStr"/>
+      <c r="L920" s="4" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="M920" s="4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N920" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="O920" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="P920" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q920" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R920" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S920" s="4" t="n">
+        <v>5784</v>
+      </c>
+      <c r="T920" s="4" t="n">
+        <v>2928</v>
+      </c>
+      <c r="U920" s="4" t="n">
+        <v>3642</v>
+      </c>
+      <c r="V920" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, inuline, glucomannane (de bulbe d'Amorphophallus konjac).</t>
+        </is>
+      </c>
+      <c r="W920" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2999.0, "L-Arginine": 5212.0, "Acide L-spartique": 8069.0, "L-Cystéine": 1071.0, "Acide L-Glutamique": 13709.0, "Glycine": 2999.0, "L-Histidine": 1856.0, "L-Isoleucine": 2928.0, "L-Leucine": 5784.0, "L-Lysine": 4784.0, "L-Méthionine": 1071.0, "L-Phénylalanine": 3856.0, "L-Proline": 3713.0, "L-Sérine": 3713.0, "L-Thréonine": 2713.0, "L-Tryptophane": 785.0, "L-Tyrosine": 2499.0, "L-Valine": 3642.0}</t>
+        </is>
+      </c>
+      <c r="X920" s="4" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="Y920" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z920" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA920" s="4" t="n"/>
+      <c r="AB920" s="4" t="n"/>
+      <c r="AC920" s="4" t="n"/>
+      <c r="AD920" s="4" t="n"/>
+      <c r="AE920" s="4" t="n"/>
+      <c r="AF920" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B921" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D921" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E921" s="6" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="F921" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G921" s="6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H921" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I921" s="6" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J921" s="6" t="inlineStr"/>
+      <c r="K921" s="6" t="inlineStr"/>
+      <c r="L921" s="6" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="M921" s="6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N921" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O921" s="6" t="n">
+        <v>384</v>
+      </c>
+      <c r="P921" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q921" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R921" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S921" s="6" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T921" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U921" s="6" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V921" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W921" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X921" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y921" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z921" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA921" s="6" t="n"/>
+      <c r="AB921" s="6" t="n"/>
+      <c r="AC921" s="6" t="n"/>
+      <c r="AD921" s="6" t="n"/>
+      <c r="AE921" s="6" t="n"/>
+      <c r="AF921" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE SOJA 2.0</t>
+        </is>
+      </c>
+      <c r="C922" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/isolat-de-proteine-de-soja-2-0</t>
+        </is>
+      </c>
+      <c r="D922" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E922" s="4" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F922" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G922" s="4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H922" s="4" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="I922" s="4" t="inlineStr">
+        <is>
+          <t>10/12/2027</t>
+        </is>
+      </c>
+      <c r="J922" s="4" t="inlineStr"/>
+      <c r="K922" s="4" t="inlineStr"/>
+      <c r="L922" s="4" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="M922" s="4" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N922" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O922" s="4" t="n">
+        <v>384</v>
+      </c>
+      <c r="P922" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q922" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R922" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S922" s="4" t="n">
+        <v>7441</v>
+      </c>
+      <c r="T922" s="4" t="n">
+        <v>3835</v>
+      </c>
+      <c r="U922" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V922" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéines de soja, chlorure de sodium, arôme, arôme naturel, épaississant (gomme xanthane), édulcorant (sucralose), edulcorante (glycosides de stéviol).</t>
+        </is>
+      </c>
+      <c r="W922" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 3617.0, "L-Arginine": 6562.0, "Acide L-spartique": 9829.0, "L-Cystéine": 17678.0, "Acide L-Glutamique": 16888.0, "Glycine": 3514.0, "L-Histidine": 2480.0, "L-Isoleucine": 3835.0, "L-Leucine": 7441.0, "L-Lysine": 5498.0, "L-Méthionine": 1395.0, "L-Phénylalanine": 4661.0, "L-Proline": 4547.0, "L-Sérine": 4258.0, "L-Thréonine": 3358.0, "L-Tryptophane": 1240.0, "L-Tyrosine": 2749.0, "L-Valine": 4031.0}</t>
+        </is>
+      </c>
+      <c r="X922" s="4" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="Y922" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z922" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA922" s="4" t="n"/>
+      <c r="AB922" s="4" t="n"/>
+      <c r="AC922" s="4" t="n"/>
+      <c r="AD922" s="4" t="n"/>
+      <c r="AE922" s="4" t="n"/>
+      <c r="AF922" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D923" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E923" s="6" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="F923" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G923" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H923" s="6" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="I923" s="6" t="inlineStr">
+        <is>
+          <t>16/03/2028</t>
+        </is>
+      </c>
+      <c r="J923" s="6" t="inlineStr"/>
+      <c r="K923" s="6" t="inlineStr"/>
+      <c r="L923" s="6" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="M923" s="6" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="N923" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O923" s="6" t="n">
+        <v>381</v>
+      </c>
+      <c r="P923" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q923" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R923" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S923" s="6" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T923" s="6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U923" s="6" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V923" s="6" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W923" s="6" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X923" s="6" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="Y923" s="6" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z923" s="6" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA923" s="6" t="n"/>
+      <c r="AB923" s="6" t="n"/>
+      <c r="AC923" s="6" t="n"/>
+      <c r="AD923" s="6" t="n"/>
+      <c r="AE923" s="6" t="n"/>
+      <c r="AF923" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>ISOLAT DE PROTÉINE DE LAIT</t>
+        </is>
+      </c>
+      <c r="C924" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/isolat-de-proteine-de-lait</t>
+        </is>
+      </c>
+      <c r="D924" s="4" t="inlineStr">
+        <is>
+          <t>2Kg</t>
+        </is>
+      </c>
+      <c r="E924" s="4" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="F924" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G924" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H924" s="4" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="I924" s="4" t="inlineStr">
+        <is>
+          <t>31/10/2027</t>
+        </is>
+      </c>
+      <c r="J924" s="4" t="inlineStr"/>
+      <c r="K924" s="4" t="inlineStr"/>
+      <c r="L924" s="4" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="M924" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N924" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="O924" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="P924" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q924" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R924" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S924" s="4" t="n">
+        <v>8686</v>
+      </c>
+      <c r="T924" s="4" t="n">
+        <v>4795</v>
+      </c>
+      <c r="U924" s="4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="V924" s="4" t="inlineStr">
+        <is>
+          <t>Isolat de protéine de lait.</t>
+        </is>
+      </c>
+      <c r="W924" s="4" t="inlineStr">
+        <is>
+          <t>{"L-Alanine": 2986.0, "L-Arginine": 3348.0, "Acide L-spartique": 7057.0, "L-Cystéine": 1086.0, "Acide L-Glutamique": 19543.0, "Glycine": 1719.0, "L-Histidine": 2443.0, "L-Isoleucine": 4795.0, "L-Leucine": 8686.0, "L-Lysine": 7600.0, "L-Méthionine": 2533.0, "L-Phénylalanine": 4433.0, "L-Proline": 8867.0, "L-Sérine": 5067.0, "L-Thréonine": 4071.0, "L-Tryptophane": 1267.0, "L-Tyrosine": 4795.0, "L-Valine": 5790.0}</t>
+        </is>
+      </c>
+      <c r="X924" s="4" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="Y924" s="4" t="inlineStr">
+        <is>
+          <t>Whey</t>
+        </is>
+      </c>
+      <c r="Z924" s="4" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="AA924" s="4" t="n"/>
+      <c r="AB924" s="4" t="n"/>
+      <c r="AC924" s="4" t="n"/>
+      <c r="AD924" s="4" t="n"/>
+      <c r="AE924" s="4" t="n"/>
+      <c r="AF924" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B925" s="5" t="inlineStr">
+        <is>
+          <t>PREMIUM OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/premium-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D925" s="6" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E925" s="6" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="F925" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G925" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H925" s="6" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="I925" s="6" t="inlineStr">
+        <is>
+          <t>12/01/2029</t>
+        </is>
+      </c>
+      <c r="J925" s="6" t="inlineStr"/>
+      <c r="K925" s="6" t="inlineStr"/>
+      <c r="L925" s="6" t="n"/>
+      <c r="M925" s="6" t="n"/>
+      <c r="N925" s="6" t="n"/>
+      <c r="O925" s="6" t="n"/>
+      <c r="P925" s="6" t="n"/>
+      <c r="Q925" s="6" t="n"/>
+      <c r="R925" s="6" t="n"/>
+      <c r="S925" s="6" t="n"/>
+      <c r="T925" s="6" t="n"/>
+      <c r="U925" s="6" t="n"/>
+      <c r="V925" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 50 % acide eicosapentaénoïque (EPA), 25 % acide docosahexaénoïque (DHA)], gélatine, humectant (glycérine).</t>
+        </is>
+      </c>
+      <c r="W925" s="6" t="inlineStr"/>
+      <c r="X925" s="6" t="n"/>
+      <c r="Y925" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z925" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA925" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB925" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC925" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AD925" s="6" t="n"/>
+      <c r="AE925" s="6" t="n"/>
+      <c r="AF925" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>PREMIUM OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C926" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/premium-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D926" s="4" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E926" s="4" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="F926" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="G926" s="4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H926" s="4" t="n">
+        <v>193.58</v>
+      </c>
+      <c r="I926" s="4" t="n"/>
+      <c r="J926" s="4" t="inlineStr"/>
+      <c r="K926" s="4" t="inlineStr"/>
+      <c r="L926" s="4" t="n"/>
+      <c r="M926" s="4" t="n"/>
+      <c r="N926" s="4" t="n"/>
+      <c r="O926" s="4" t="n"/>
+      <c r="P926" s="4" t="n"/>
+      <c r="Q926" s="4" t="n"/>
+      <c r="R926" s="4" t="n"/>
+      <c r="S926" s="4" t="n"/>
+      <c r="T926" s="4" t="n"/>
+      <c r="U926" s="4" t="n"/>
+      <c r="V926" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 50 % acide eicosapentaénoïque (EPA), 25 % acide docosahexaénoïque (DHA)], gélatine, humectant (glycérine).</t>
+        </is>
+      </c>
+      <c r="W926" s="4" t="inlineStr"/>
+      <c r="X926" s="4" t="n"/>
+      <c r="Y926" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z926" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA926" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB926" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC926" s="4" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AD926" s="4" t="n"/>
+      <c r="AE926" s="4" t="n"/>
+      <c r="AF926" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B927" s="5" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D927" s="6" t="inlineStr">
+        <is>
+          <t>30 softgels</t>
+        </is>
+      </c>
+      <c r="E927" s="6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F927" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G927" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H927" s="6" t="n">
+        <v>107.67</v>
+      </c>
+      <c r="I927" s="6" t="inlineStr">
+        <is>
+          <t>20/10/2028</t>
+        </is>
+      </c>
+      <c r="J927" s="6" t="inlineStr"/>
+      <c r="K927" s="6" t="inlineStr"/>
+      <c r="L927" s="6" t="n"/>
+      <c r="M927" s="6" t="n"/>
+      <c r="N927" s="6" t="n"/>
+      <c r="O927" s="6" t="n"/>
+      <c r="P927" s="6" t="n"/>
+      <c r="Q927" s="6" t="n"/>
+      <c r="R927" s="6" t="n"/>
+      <c r="S927" s="6" t="n"/>
+      <c r="T927" s="6" t="n"/>
+      <c r="U927" s="6" t="n"/>
+      <c r="V927" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W927" s="6" t="inlineStr"/>
+      <c r="X927" s="6" t="n"/>
+      <c r="Y927" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z927" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA927" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB927" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC927" s="6" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AD927" s="6" t="n"/>
+      <c r="AE927" s="6" t="n"/>
+      <c r="AF927" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C928" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D928" s="4" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E928" s="4" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="F928" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G928" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H928" s="4" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="I928" s="4" t="inlineStr">
+        <is>
+          <t>30/04/2028</t>
+        </is>
+      </c>
+      <c r="J928" s="4" t="inlineStr"/>
+      <c r="K928" s="4" t="inlineStr"/>
+      <c r="L928" s="4" t="n"/>
+      <c r="M928" s="4" t="n"/>
+      <c r="N928" s="4" t="n"/>
+      <c r="O928" s="4" t="n"/>
+      <c r="P928" s="4" t="n"/>
+      <c r="Q928" s="4" t="n"/>
+      <c r="R928" s="4" t="n"/>
+      <c r="S928" s="4" t="n"/>
+      <c r="T928" s="4" t="n"/>
+      <c r="U928" s="4" t="n"/>
+      <c r="V928" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W928" s="4" t="inlineStr"/>
+      <c r="X928" s="4" t="n"/>
+      <c r="Y928" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z928" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA928" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB928" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC928" s="4" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AD928" s="4" t="n"/>
+      <c r="AE928" s="4" t="n"/>
+      <c r="AF928" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B929" s="5" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D929" s="6" t="inlineStr">
+        <is>
+          <t>180 softgels</t>
+        </is>
+      </c>
+      <c r="E929" s="6" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="F929" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G929" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H929" s="6" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="I929" s="6" t="n"/>
+      <c r="J929" s="6" t="inlineStr"/>
+      <c r="K929" s="6" t="inlineStr"/>
+      <c r="L929" s="6" t="n"/>
+      <c r="M929" s="6" t="n"/>
+      <c r="N929" s="6" t="n"/>
+      <c r="O929" s="6" t="n"/>
+      <c r="P929" s="6" t="n"/>
+      <c r="Q929" s="6" t="n"/>
+      <c r="R929" s="6" t="n"/>
+      <c r="S929" s="6" t="n"/>
+      <c r="T929" s="6" t="n"/>
+      <c r="U929" s="6" t="n"/>
+      <c r="V929" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W929" s="6" t="inlineStr"/>
+      <c r="X929" s="6" t="n"/>
+      <c r="Y929" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z929" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA929" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB929" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC929" s="6" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AD929" s="6" t="n"/>
+      <c r="AE929" s="6" t="n"/>
+      <c r="AF929" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>OMEGA-3 HUILE DE POISSON 1000mg</t>
+        </is>
+      </c>
+      <c r="C930" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/omega-3-huile-de-poisson-1000mg</t>
+        </is>
+      </c>
+      <c r="D930" s="4" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E930" s="4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F930" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="G930" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H930" s="4" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="I930" s="4" t="n"/>
+      <c r="J930" s="4" t="inlineStr"/>
+      <c r="K930" s="4" t="inlineStr"/>
+      <c r="L930" s="4" t="n"/>
+      <c r="M930" s="4" t="n"/>
+      <c r="N930" s="4" t="n"/>
+      <c r="O930" s="4" t="n"/>
+      <c r="P930" s="4" t="n"/>
+      <c r="Q930" s="4" t="n"/>
+      <c r="R930" s="4" t="n"/>
+      <c r="S930" s="4" t="n"/>
+      <c r="T930" s="4" t="n"/>
+      <c r="U930" s="4" t="n"/>
+      <c r="V930" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [18% d'acide eicosapentaenoïque (EPA), 12% d'acide docosahexaenoïque (DHA)], gélatine, humectant (glycérine), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W930" s="4" t="inlineStr"/>
+      <c r="X930" s="4" t="n"/>
+      <c r="Y930" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z930" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA930" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB930" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AC930" s="4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AD930" s="4" t="n"/>
+      <c r="AE930" s="4" t="n"/>
+      <c r="AF930" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B931" s="5" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D931" s="6" t="inlineStr">
+        <is>
+          <t>30 softgels</t>
+        </is>
+      </c>
+      <c r="E931" s="6" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="F931" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G931" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H931" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="I931" s="6" t="inlineStr">
+        <is>
+          <t>02/12/2028</t>
+        </is>
+      </c>
+      <c r="J931" s="6" t="inlineStr"/>
+      <c r="K931" s="6" t="inlineStr"/>
+      <c r="L931" s="6" t="n"/>
+      <c r="M931" s="6" t="n"/>
+      <c r="N931" s="6" t="n"/>
+      <c r="O931" s="6" t="n"/>
+      <c r="P931" s="6" t="n"/>
+      <c r="Q931" s="6" t="n"/>
+      <c r="R931" s="6" t="n"/>
+      <c r="S931" s="6" t="n"/>
+      <c r="T931" s="6" t="n"/>
+      <c r="U931" s="6" t="n"/>
+      <c r="V931" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W931" s="6" t="inlineStr"/>
+      <c r="X931" s="6" t="n"/>
+      <c r="Y931" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z931" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA931" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB931" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC931" s="6" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AD931" s="6" t="n"/>
+      <c r="AE931" s="6" t="n"/>
+      <c r="AF931" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C932" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D932" s="4" t="inlineStr">
+        <is>
+          <t>120 softgels</t>
+        </is>
+      </c>
+      <c r="E932" s="4" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F932" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G932" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H932" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="I932" s="4" t="inlineStr">
+        <is>
+          <t>01/10/2028</t>
+        </is>
+      </c>
+      <c r="J932" s="4" t="inlineStr"/>
+      <c r="K932" s="4" t="inlineStr"/>
+      <c r="L932" s="4" t="n"/>
+      <c r="M932" s="4" t="n"/>
+      <c r="N932" s="4" t="n"/>
+      <c r="O932" s="4" t="n"/>
+      <c r="P932" s="4" t="n"/>
+      <c r="Q932" s="4" t="n"/>
+      <c r="R932" s="4" t="n"/>
+      <c r="S932" s="4" t="n"/>
+      <c r="T932" s="4" t="n"/>
+      <c r="U932" s="4" t="n"/>
+      <c r="V932" s="4" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W932" s="4" t="inlineStr"/>
+      <c r="X932" s="4" t="n"/>
+      <c r="Y932" s="4" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z932" s="4" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA932" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB932" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC932" s="4" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AD932" s="4" t="n"/>
+      <c r="AE932" s="4" t="n"/>
+      <c r="AF932" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B933" s="5" t="inlineStr">
+        <is>
+          <t>ULTRA OMEGA-3 TG (IFOS) 1000mg</t>
+        </is>
+      </c>
+      <c r="C933" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/essential-series/ultra-omega-3-tg-ifos-1000mg</t>
+        </is>
+      </c>
+      <c r="D933" s="6" t="inlineStr">
+        <is>
+          <t>240 softgels</t>
+        </is>
+      </c>
+      <c r="E933" s="6" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="F933" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="G933" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H933" s="6" t="n">
+        <v>119.12</v>
+      </c>
+      <c r="I933" s="6" t="inlineStr">
+        <is>
+          <t>03/12/2028</t>
+        </is>
+      </c>
+      <c r="J933" s="6" t="inlineStr"/>
+      <c r="K933" s="6" t="inlineStr"/>
+      <c r="L933" s="6" t="n"/>
+      <c r="M933" s="6" t="n"/>
+      <c r="N933" s="6" t="n"/>
+      <c r="O933" s="6" t="n"/>
+      <c r="P933" s="6" t="n"/>
+      <c r="Q933" s="6" t="n"/>
+      <c r="R933" s="6" t="n"/>
+      <c r="S933" s="6" t="n"/>
+      <c r="T933" s="6" t="n"/>
+      <c r="U933" s="6" t="n"/>
+      <c r="V933" s="6" t="inlineStr">
+        <is>
+          <t>Huile de poisson [triglycérides (TG), 35% acide eicosapentéonique (EPA), 25% acide docosahexaéonique (DHA)], gélatine, humectant (glycérol), D-alpha-tocophérol (vitamine E naturelle).</t>
+        </is>
+      </c>
+      <c r="W933" s="6" t="inlineStr"/>
+      <c r="X933" s="6" t="n"/>
+      <c r="Y933" s="6" t="inlineStr">
+        <is>
+          <t>Oméga-3</t>
+        </is>
+      </c>
+      <c r="Z933" s="6" t="inlineStr">
+        <is>
+          <t>omega3</t>
+        </is>
+      </c>
+      <c r="AA933" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB933" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC933" s="6" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AD933" s="6" t="n"/>
+      <c r="AE933" s="6" t="n"/>
+      <c r="AF933" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C934" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D934" s="4" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
+      <c r="E934" s="4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F934" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G934" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H934" s="4" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="I934" s="4" t="n"/>
+      <c r="J934" s="4" t="inlineStr"/>
+      <c r="K934" s="4" t="inlineStr"/>
+      <c r="L934" s="4" t="n"/>
+      <c r="M934" s="4" t="n"/>
+      <c r="N934" s="4" t="n"/>
+      <c r="O934" s="4" t="n"/>
+      <c r="P934" s="4" t="n"/>
+      <c r="Q934" s="4" t="n"/>
+      <c r="R934" s="4" t="n"/>
+      <c r="S934" s="4" t="n"/>
+      <c r="T934" s="4" t="n"/>
+      <c r="U934" s="4" t="n"/>
+      <c r="V934" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W934" s="4" t="inlineStr"/>
+      <c r="X934" s="4" t="n"/>
+      <c r="Y934" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z934" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA934" s="4" t="n"/>
+      <c r="AB934" s="4" t="n"/>
+      <c r="AC934" s="4" t="n"/>
+      <c r="AD934" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE934" s="4" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AF934" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B935" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C935" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D935" s="6" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="E935" s="6" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F935" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="G935" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H935" s="6" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="I935" s="6" t="n"/>
+      <c r="J935" s="6" t="inlineStr"/>
+      <c r="K935" s="6" t="inlineStr"/>
+      <c r="L935" s="6" t="n"/>
+      <c r="M935" s="6" t="n"/>
+      <c r="N935" s="6" t="n"/>
+      <c r="O935" s="6" t="n"/>
+      <c r="P935" s="6" t="n"/>
+      <c r="Q935" s="6" t="n"/>
+      <c r="R935" s="6" t="n"/>
+      <c r="S935" s="6" t="n"/>
+      <c r="T935" s="6" t="n"/>
+      <c r="U935" s="6" t="n"/>
+      <c r="V935" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W935" s="6" t="inlineStr"/>
+      <c r="X935" s="6" t="n"/>
+      <c r="Y935" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z935" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA935" s="6" t="n"/>
+      <c r="AB935" s="6" t="n"/>
+      <c r="AC935" s="6" t="n"/>
+      <c r="AD935" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE935" s="6" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="AF935" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C936" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D936" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E936" s="4" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="F936" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="G936" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H936" s="4" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="I936" s="4" t="inlineStr">
+        <is>
+          <t>24/03/2028</t>
+        </is>
+      </c>
+      <c r="J936" s="4" t="inlineStr"/>
+      <c r="K936" s="4" t="inlineStr"/>
+      <c r="L936" s="4" t="n"/>
+      <c r="M936" s="4" t="n"/>
+      <c r="N936" s="4" t="n"/>
+      <c r="O936" s="4" t="n"/>
+      <c r="P936" s="4" t="n"/>
+      <c r="Q936" s="4" t="n"/>
+      <c r="R936" s="4" t="n"/>
+      <c r="S936" s="4" t="n"/>
+      <c r="T936" s="4" t="n"/>
+      <c r="U936" s="4" t="n"/>
+      <c r="V936" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W936" s="4" t="inlineStr"/>
+      <c r="X936" s="4" t="n"/>
+      <c r="Y936" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z936" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA936" s="4" t="n"/>
+      <c r="AB936" s="4" t="n"/>
+      <c r="AC936" s="4" t="n"/>
+      <c r="AD936" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE936" s="4" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AF936" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B937" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C937" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D937" s="6" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="E937" s="6" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="F937" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="G937" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H937" s="6" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="I937" s="6" t="n"/>
+      <c r="J937" s="6" t="inlineStr"/>
+      <c r="K937" s="6" t="inlineStr"/>
+      <c r="L937" s="6" t="n"/>
+      <c r="M937" s="6" t="n"/>
+      <c r="N937" s="6" t="n"/>
+      <c r="O937" s="6" t="n"/>
+      <c r="P937" s="6" t="n"/>
+      <c r="Q937" s="6" t="n"/>
+      <c r="R937" s="6" t="n"/>
+      <c r="S937" s="6" t="n"/>
+      <c r="T937" s="6" t="n"/>
+      <c r="U937" s="6" t="n"/>
+      <c r="V937" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W937" s="6" t="inlineStr"/>
+      <c r="X937" s="6" t="n"/>
+      <c r="Y937" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z937" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA937" s="6" t="n"/>
+      <c r="AB937" s="6" t="n"/>
+      <c r="AC937" s="6" t="n"/>
+      <c r="AD937" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE937" s="6" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="AF937" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE EXCELL (100% Creapure®) EN POUDRE</t>
+        </is>
+      </c>
+      <c r="C938" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-excell-100-creapure-en-poudre</t>
+        </is>
+      </c>
+      <c r="D938" s="4" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E938" s="4" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="F938" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="G938" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H938" s="4" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="I938" s="4" t="n"/>
+      <c r="J938" s="4" t="inlineStr"/>
+      <c r="K938" s="4" t="inlineStr"/>
+      <c r="L938" s="4" t="n"/>
+      <c r="M938" s="4" t="n"/>
+      <c r="N938" s="4" t="n"/>
+      <c r="O938" s="4" t="n"/>
+      <c r="P938" s="4" t="n"/>
+      <c r="Q938" s="4" t="n"/>
+      <c r="R938" s="4" t="n"/>
+      <c r="S938" s="4" t="n"/>
+      <c r="T938" s="4" t="n"/>
+      <c r="U938" s="4" t="n"/>
+      <c r="V938" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W938" s="4" t="inlineStr"/>
+      <c r="X938" s="4" t="n"/>
+      <c r="Y938" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z938" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA938" s="4" t="n"/>
+      <c r="AB938" s="4" t="n"/>
+      <c r="AC938" s="4" t="n"/>
+      <c r="AD938" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE938" s="4" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="AF938" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B939" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C939" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D939" s="6" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
+      <c r="E939" s="6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F939" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G939" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H939" s="6" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I939" s="6" t="inlineStr">
+        <is>
+          <t>14/01/2028</t>
+        </is>
+      </c>
+      <c r="J939" s="6" t="inlineStr"/>
+      <c r="K939" s="6" t="inlineStr"/>
+      <c r="L939" s="6" t="n"/>
+      <c r="M939" s="6" t="n"/>
+      <c r="N939" s="6" t="n"/>
+      <c r="O939" s="6" t="n"/>
+      <c r="P939" s="6" t="n"/>
+      <c r="Q939" s="6" t="n"/>
+      <c r="R939" s="6" t="n"/>
+      <c r="S939" s="6" t="n"/>
+      <c r="T939" s="6" t="n"/>
+      <c r="U939" s="6" t="n"/>
+      <c r="V939" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W939" s="6" t="inlineStr"/>
+      <c r="X939" s="6" t="n"/>
+      <c r="Y939" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z939" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA939" s="6" t="n"/>
+      <c r="AB939" s="6" t="n"/>
+      <c r="AC939" s="6" t="n"/>
+      <c r="AD939" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE939" s="6" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AF939" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C940" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D940" s="4" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="E940" s="4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F940" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="G940" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H940" s="4" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="I940" s="4" t="n"/>
+      <c r="J940" s="4" t="inlineStr"/>
+      <c r="K940" s="4" t="inlineStr"/>
+      <c r="L940" s="4" t="n"/>
+      <c r="M940" s="4" t="n"/>
+      <c r="N940" s="4" t="n"/>
+      <c r="O940" s="4" t="n"/>
+      <c r="P940" s="4" t="n"/>
+      <c r="Q940" s="4" t="n"/>
+      <c r="R940" s="4" t="n"/>
+      <c r="S940" s="4" t="n"/>
+      <c r="T940" s="4" t="n"/>
+      <c r="U940" s="4" t="n"/>
+      <c r="V940" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W940" s="4" t="inlineStr"/>
+      <c r="X940" s="4" t="n"/>
+      <c r="Y940" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z940" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA940" s="4" t="n"/>
+      <c r="AB940" s="4" t="n"/>
+      <c r="AC940" s="4" t="n"/>
+      <c r="AD940" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE940" s="4" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="AF940" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B941" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C941" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D941" s="6" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E941" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F941" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="G941" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H941" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I941" s="6" t="inlineStr">
+        <is>
+          <t>27/03/2028</t>
+        </is>
+      </c>
+      <c r="J941" s="6" t="inlineStr"/>
+      <c r="K941" s="6" t="inlineStr"/>
+      <c r="L941" s="6" t="n"/>
+      <c r="M941" s="6" t="n"/>
+      <c r="N941" s="6" t="n"/>
+      <c r="O941" s="6" t="n"/>
+      <c r="P941" s="6" t="n"/>
+      <c r="Q941" s="6" t="n"/>
+      <c r="R941" s="6" t="n"/>
+      <c r="S941" s="6" t="n"/>
+      <c r="T941" s="6" t="n"/>
+      <c r="U941" s="6" t="n"/>
+      <c r="V941" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W941" s="6" t="inlineStr"/>
+      <c r="X941" s="6" t="n"/>
+      <c r="Y941" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z941" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA941" s="6" t="n"/>
+      <c r="AB941" s="6" t="n"/>
+      <c r="AC941" s="6" t="n"/>
+      <c r="AD941" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE941" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AF941" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C942" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>600g</t>
+        </is>
+      </c>
+      <c r="E942" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F942" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="G942" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H942" s="4" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I942" s="4" t="n"/>
+      <c r="J942" s="4" t="inlineStr"/>
+      <c r="K942" s="4" t="inlineStr"/>
+      <c r="L942" s="4" t="n"/>
+      <c r="M942" s="4" t="n"/>
+      <c r="N942" s="4" t="n"/>
+      <c r="O942" s="4" t="n"/>
+      <c r="P942" s="4" t="n"/>
+      <c r="Q942" s="4" t="n"/>
+      <c r="R942" s="4" t="n"/>
+      <c r="S942" s="4" t="n"/>
+      <c r="T942" s="4" t="n"/>
+      <c r="U942" s="4" t="n"/>
+      <c r="V942" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W942" s="4" t="inlineStr"/>
+      <c r="X942" s="4" t="n"/>
+      <c r="Y942" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z942" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA942" s="4" t="n"/>
+      <c r="AB942" s="4" t="n"/>
+      <c r="AC942" s="4" t="n"/>
+      <c r="AD942" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE942" s="4" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AF942" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B943" s="5" t="inlineStr">
+        <is>
+          <t>CRÉATINE MONOHYDRATE EN POUDRE (200 MESH)</t>
+        </is>
+      </c>
+      <c r="C943" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/creatine-monohydratee-en-poudre-200-mesh</t>
+        </is>
+      </c>
+      <c r="D943" s="6" t="inlineStr">
+        <is>
+          <t>1Kg</t>
+        </is>
+      </c>
+      <c r="E943" s="6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F943" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="G943" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H943" s="6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="I943" s="6" t="inlineStr">
+        <is>
+          <t>12/12/2027</t>
+        </is>
+      </c>
+      <c r="J943" s="6" t="inlineStr"/>
+      <c r="K943" s="6" t="inlineStr"/>
+      <c r="L943" s="6" t="n"/>
+      <c r="M943" s="6" t="n"/>
+      <c r="N943" s="6" t="n"/>
+      <c r="O943" s="6" t="n"/>
+      <c r="P943" s="6" t="n"/>
+      <c r="Q943" s="6" t="n"/>
+      <c r="R943" s="6" t="n"/>
+      <c r="S943" s="6" t="n"/>
+      <c r="T943" s="6" t="n"/>
+      <c r="U943" s="6" t="n"/>
+      <c r="V943" s="6" t="inlineStr">
+        <is>
+          <t>Monohydrate de Créatine.</t>
+        </is>
+      </c>
+      <c r="W943" s="6" t="inlineStr"/>
+      <c r="X943" s="6" t="n"/>
+      <c r="Y943" s="6" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z943" s="6" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA943" s="6" t="n"/>
+      <c r="AB943" s="6" t="n"/>
+      <c r="AC943" s="6" t="n"/>
+      <c r="AD943" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE943" s="6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AF943" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>MONOHYDRATE DE CRÉATINE ULTRA-FIN EN POUDRE (500 MESH)</t>
+        </is>
+      </c>
+      <c r="C944" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hsnstore.fr/marques/raw-series/monohydrate-de-creatine-ultra-fin-en-poudre-500-mesh</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="E944" s="4" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F944" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="G944" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H944" s="4" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="I944" s="4" t="inlineStr">
+        <is>
+          <t>17/02/2028</t>
+        </is>
+      </c>
+      <c r="J944" s="4" t="inlineStr"/>
+      <c r="K944" s="4" t="inlineStr"/>
+      <c r="L944" s="4" t="n"/>
+      <c r="M944" s="4" t="n"/>
+      <c r="N944" s="4" t="n"/>
+      <c r="O944" s="4" t="n"/>
+      <c r="P944" s="4" t="n"/>
+      <c r="Q944" s="4" t="n"/>
+      <c r="R944" s="4" t="n"/>
+      <c r="S944" s="4" t="n"/>
+      <c r="T944" s="4" t="n"/>
+      <c r="U944" s="4" t="n"/>
+      <c r="V944" s="4" t="inlineStr">
+        <is>
+          <t>Monohydrate de créatine.</t>
+        </is>
+      </c>
+      <c r="W944" s="4" t="inlineStr"/>
+      <c r="X944" s="4" t="n"/>
+      <c r="Y944" s="4" t="inlineStr">
+        <is>
+          <t>Créatine</t>
+        </is>
+      </c>
+      <c r="Z944" s="4" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
+      <c r="AA944" s="4" t="n"/>
+      <c r="AB944" s="4" t="n"/>
+      <c r="AC944" s="4" t="n"/>
+      <c r="AD944" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE944" s="4" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="AF944" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
